--- a/AI List of FacturX_ZugFERD_XML_Tags_EN.xlsx
+++ b/AI List of FacturX_ZugFERD_XML_Tags_EN.xlsx
@@ -10,12 +10,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full XML Structure" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profiles" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Codes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="XML MINIMUM Example" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="XML EXTENDED Example" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Full XML Structure'!$A$2:$G$264</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Full XML Structure'!$A$2:$G$260</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Profiles'!$A$2:$H$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Reference Codes'!$A$2:$D$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Reference Codes'!$A$2:$D$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -681,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G264"/>
+  <dimension ref="A1:G260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Factur-X / ZugFERD profile identifier</t>
+          <t>Profile identifier</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>380=Invoice | 381=Credit note | 384=Corrective invoice | 389=Self-billing</t>
+          <t>380=Invoice | 381=Credit note | 384=Corrective | 389=Self-billing</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>format="102" → YYYYMMDD  e.g. 20240315</t>
+          <t>format="102" → YYYYMMDD</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>E.g. en, fr, de</t>
+          <t>E.g. fr, en, de</t>
         </is>
       </c>
     </row>
@@ -1595,22 +1595,12 @@
       </c>
       <c r="G30" s="4" t="inlineStr"/>
     </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>── ram:IncludedSupplyChainTradeLineItem ──</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>Invoice Line Items</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr"/>
-      <c r="D31" s="8" t="inlineStr"/>
-      <c r="E31" s="8" t="inlineStr"/>
-      <c r="F31" s="8" t="inlineStr"/>
-      <c r="G31" s="8" t="inlineStr"/>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>ram:IncludedSupplyChainTradeLineItem</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="14" t="inlineStr">
@@ -2057,7 +2047,7 @@
       </c>
       <c r="G44" s="22" t="inlineStr">
         <is>
-          <t>E.g. FR, DE, US</t>
+          <t>E.g. FR, DE, GB, US</t>
         </is>
       </c>
     </row>
@@ -2527,7 +2517,7 @@
       </c>
       <c r="G58" s="22" t="inlineStr">
         <is>
-          <t>UN/ECE Rec 20 unitCode – e.g. C62=piece, HUR=hour, KGM=kg</t>
+          <t>UN/ECE Rec 20 – e.g. C62=piece, HUR=hour, KGM=kg</t>
         </is>
       </c>
     </row>
@@ -3280,22 +3270,12 @@
         <v/>
       </c>
     </row>
-    <row r="81" ht="16" customHeight="1">
-      <c r="A81" s="7" t="inlineStr">
-        <is>
-          <t>── ram:ApplicableHeaderTradeAgreement ──</t>
-        </is>
-      </c>
-      <c r="B81" s="8" t="inlineStr">
-        <is>
-          <t>Header Trade Agreement</t>
-        </is>
-      </c>
-      <c r="C81" s="8" t="inlineStr"/>
-      <c r="D81" s="8" t="inlineStr"/>
-      <c r="E81" s="8" t="inlineStr"/>
-      <c r="F81" s="8" t="inlineStr"/>
-      <c r="G81" s="8" t="inlineStr"/>
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>ram:ApplicableHeaderTradeAgreement</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="16" customHeight="1">
       <c r="A82" s="14" t="inlineStr">
@@ -3363,7 +3343,7 @@
       </c>
       <c r="G83" s="11" t="inlineStr">
         <is>
-          <t>Mandatory in MINIMUM profile. E.g. service code, purchase order ref</t>
+          <t>Mandatory in MINIMUM profile</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3413,7 @@
       </c>
       <c r="G85" s="22" t="inlineStr">
         <is>
-          <t>schemeID="0088" GS1 | "0002" SIREN</t>
+          <t>schemeID="0088" GS1 | "0060" DUNS</t>
         </is>
       </c>
     </row>
@@ -4274,7 +4254,7 @@
       </c>
       <c r="G110" s="22" t="inlineStr">
         <is>
-          <t>schemeID="VA" → VAT number (e.g. GB123456789) | "FC" → registration number</t>
+          <t>schemeID="VA" → VAT number | "FC" → registration number</t>
         </is>
       </c>
     </row>
@@ -5771,22 +5751,12 @@
       </c>
       <c r="G155" s="22" t="inlineStr"/>
     </row>
-    <row r="156" ht="16" customHeight="1">
-      <c r="A156" s="14" t="inlineStr">
-        <is>
-          <t>── ram:ApplicableHeaderTradeDelivery ──</t>
-        </is>
-      </c>
-      <c r="B156" s="15" t="inlineStr">
-        <is>
-          <t>Header Trade Delivery</t>
-        </is>
-      </c>
-      <c r="C156" s="15" t="inlineStr"/>
-      <c r="D156" s="15" t="inlineStr"/>
-      <c r="E156" s="15" t="inlineStr"/>
-      <c r="F156" s="15" t="inlineStr"/>
-      <c r="G156" s="15" t="inlineStr"/>
+    <row r="156" ht="18" customHeight="1">
+      <c r="A156" s="6" t="inlineStr">
+        <is>
+          <t>ram:ApplicableHeaderTradeDelivery</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="16" customHeight="1">
       <c r="A157" s="7" t="inlineStr">
@@ -5857,17 +5827,17 @@
     <row r="159" ht="16" customHeight="1">
       <c r="A159" s="21" t="inlineStr">
         <is>
-          <t>ram:GlobalID @schemeID</t>
+          <t>ram:ID</t>
         </is>
       </c>
       <c r="B159" s="22" t="inlineStr">
         <is>
-          <t>Delivery location global identifier</t>
+          <t>Delivery location identifier</t>
         </is>
       </c>
       <c r="C159" s="22" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="D159" s="24" t="inlineStr">
@@ -5890,12 +5860,12 @@
     <row r="160" ht="16" customHeight="1">
       <c r="A160" s="21" t="inlineStr">
         <is>
-          <t>ram:ID</t>
+          <t>ram:Name</t>
         </is>
       </c>
       <c r="B160" s="22" t="inlineStr">
         <is>
-          <t>Delivery location identifier</t>
+          <t>Delivery recipient name</t>
         </is>
       </c>
       <c r="C160" s="22" t="inlineStr">
@@ -5915,7 +5885,7 @@
       </c>
       <c r="F160" s="22" t="inlineStr">
         <is>
-          <t>EXTENDED</t>
+          <t>BASIC WL</t>
         </is>
       </c>
       <c r="G160" s="22" t="inlineStr"/>
@@ -5923,55 +5893,55 @@
     <row r="161" ht="16" customHeight="1">
       <c r="A161" s="21" t="inlineStr">
         <is>
-          <t>ram:Name</t>
+          <t>ram:PostalTradeAddress</t>
         </is>
       </c>
       <c r="B161" s="22" t="inlineStr">
         <is>
-          <t>Delivery recipient name</t>
+          <t>Delivery address</t>
         </is>
       </c>
       <c r="C161" s="22" t="inlineStr">
         <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="D161" s="27" t="inlineStr">
+        <is>
+          <t>Conditional</t>
+        </is>
+      </c>
+      <c r="E161" s="22" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="F161" s="22" t="inlineStr">
+        <is>
+          <t>BASIC WL</t>
+        </is>
+      </c>
+      <c r="G161" s="22" t="inlineStr"/>
+    </row>
+    <row r="162" ht="16" customHeight="1">
+      <c r="A162" s="25" t="inlineStr">
+        <is>
+          <t>ram:PostcodeCode</t>
+        </is>
+      </c>
+      <c r="B162" s="22" t="inlineStr">
+        <is>
+          <t>Delivery postcode</t>
+        </is>
+      </c>
+      <c r="C162" s="22" t="inlineStr">
+        <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D161" s="24" t="inlineStr">
+      <c r="D162" s="24" t="inlineStr">
         <is>
           <t>Optional</t>
-        </is>
-      </c>
-      <c r="E161" s="22" t="inlineStr">
-        <is>
-          <t>0..1</t>
-        </is>
-      </c>
-      <c r="F161" s="22" t="inlineStr">
-        <is>
-          <t>BASIC WL</t>
-        </is>
-      </c>
-      <c r="G161" s="22" t="inlineStr"/>
-    </row>
-    <row r="162" ht="16" customHeight="1">
-      <c r="A162" s="21" t="inlineStr">
-        <is>
-          <t>ram:PostalTradeAddress</t>
-        </is>
-      </c>
-      <c r="B162" s="22" t="inlineStr">
-        <is>
-          <t>Delivery address</t>
-        </is>
-      </c>
-      <c r="C162" s="22" t="inlineStr">
-        <is>
-          <t>Complex</t>
-        </is>
-      </c>
-      <c r="D162" s="27" t="inlineStr">
-        <is>
-          <t>Conditional</t>
         </is>
       </c>
       <c r="E162" s="22" t="inlineStr">
@@ -5989,12 +5959,12 @@
     <row r="163" ht="16" customHeight="1">
       <c r="A163" s="25" t="inlineStr">
         <is>
-          <t>ram:PostcodeCode</t>
+          <t>ram:LineOne</t>
         </is>
       </c>
       <c r="B163" s="22" t="inlineStr">
         <is>
-          <t>Delivery postcode</t>
+          <t>Delivery address line 1</t>
         </is>
       </c>
       <c r="C163" s="22" t="inlineStr">
@@ -6022,12 +5992,12 @@
     <row r="164" ht="16" customHeight="1">
       <c r="A164" s="25" t="inlineStr">
         <is>
-          <t>ram:LineOne</t>
+          <t>ram:LineTwo</t>
         </is>
       </c>
       <c r="B164" s="22" t="inlineStr">
         <is>
-          <t>Delivery address line 1</t>
+          <t>Delivery address line 2</t>
         </is>
       </c>
       <c r="C164" s="22" t="inlineStr">
@@ -6047,7 +6017,7 @@
       </c>
       <c r="F164" s="22" t="inlineStr">
         <is>
-          <t>BASIC WL</t>
+          <t>EXTENDED</t>
         </is>
       </c>
       <c r="G164" s="22" t="inlineStr"/>
@@ -6055,12 +6025,12 @@
     <row r="165" ht="16" customHeight="1">
       <c r="A165" s="25" t="inlineStr">
         <is>
-          <t>ram:LineTwo</t>
+          <t>ram:CityName</t>
         </is>
       </c>
       <c r="B165" s="22" t="inlineStr">
         <is>
-          <t>Delivery address line 2</t>
+          <t>Delivery city</t>
         </is>
       </c>
       <c r="C165" s="22" t="inlineStr">
@@ -6080,7 +6050,7 @@
       </c>
       <c r="F165" s="22" t="inlineStr">
         <is>
-          <t>EXTENDED</t>
+          <t>BASIC WL</t>
         </is>
       </c>
       <c r="G165" s="22" t="inlineStr"/>
@@ -6088,429 +6058,419 @@
     <row r="166" ht="16" customHeight="1">
       <c r="A166" s="25" t="inlineStr">
         <is>
-          <t>ram:CityName</t>
+          <t>ram:CountryID</t>
         </is>
       </c>
       <c r="B166" s="22" t="inlineStr">
         <is>
-          <t>Delivery city</t>
+          <t>Delivery country</t>
         </is>
       </c>
       <c r="C166" s="22" t="inlineStr">
         <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="D166" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E166" s="22" t="inlineStr">
+        <is>
+          <t>1..1</t>
+        </is>
+      </c>
+      <c r="F166" s="22" t="inlineStr">
+        <is>
+          <t>BASIC WL</t>
+        </is>
+      </c>
+      <c r="G166" s="22" t="inlineStr"/>
+    </row>
+    <row r="167" ht="16" customHeight="1">
+      <c r="A167" s="10" t="inlineStr">
+        <is>
+          <t>ram:ActualDeliverySupplyChainEvent</t>
+        </is>
+      </c>
+      <c r="B167" s="11" t="inlineStr">
+        <is>
+          <t>Actual delivery event</t>
+        </is>
+      </c>
+      <c r="C167" s="11" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="D167" s="19" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="E167" s="11" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="F167" s="11" t="inlineStr">
+        <is>
+          <t>BASIC WL</t>
+        </is>
+      </c>
+      <c r="G167" s="11" t="inlineStr"/>
+    </row>
+    <row r="168" ht="16" customHeight="1">
+      <c r="A168" s="21" t="inlineStr">
+        <is>
+          <t>ram:OccurrenceDateTime</t>
+        </is>
+      </c>
+      <c r="B168" s="22" t="inlineStr">
+        <is>
+          <t>Actual delivery date</t>
+        </is>
+      </c>
+      <c r="C168" s="22" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="D168" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E168" s="22" t="inlineStr">
+        <is>
+          <t>1..1</t>
+        </is>
+      </c>
+      <c r="F168" s="22" t="inlineStr">
+        <is>
+          <t>BASIC WL</t>
+        </is>
+      </c>
+      <c r="G168" s="22" t="inlineStr"/>
+    </row>
+    <row r="169" ht="16" customHeight="1">
+      <c r="A169" s="25" t="inlineStr">
+        <is>
+          <t>udt:DateTimeString @format="102"</t>
+        </is>
+      </c>
+      <c r="B169" s="22" t="inlineStr">
+        <is>
+          <t>Delivery date</t>
+        </is>
+      </c>
+      <c r="C169" s="22" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D169" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E169" s="22" t="inlineStr">
+        <is>
+          <t>1..1</t>
+        </is>
+      </c>
+      <c r="F169" s="22" t="inlineStr">
+        <is>
+          <t>BASIC WL</t>
+        </is>
+      </c>
+      <c r="G169" s="22" t="inlineStr">
+        <is>
+          <t>YYYYMMDD</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="16" customHeight="1">
+      <c r="A170" s="10" t="inlineStr">
+        <is>
+          <t>ram:DeliveryNoteReferencedDocument</t>
+        </is>
+      </c>
+      <c r="B170" s="11" t="inlineStr">
+        <is>
+          <t>Delivery note reference</t>
+        </is>
+      </c>
+      <c r="C170" s="11" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="D170" s="19" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="E170" s="11" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="F170" s="11" t="inlineStr">
+        <is>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="G170" s="11" t="inlineStr"/>
+    </row>
+    <row r="171" ht="16" customHeight="1">
+      <c r="A171" s="21" t="inlineStr">
+        <is>
+          <t>ram:IssuerAssignedID</t>
+        </is>
+      </c>
+      <c r="B171" s="22" t="inlineStr">
+        <is>
+          <t>Delivery note number</t>
+        </is>
+      </c>
+      <c r="C171" s="22" t="inlineStr">
+        <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D166" s="24" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="E166" s="22" t="inlineStr">
-        <is>
-          <t>0..1</t>
-        </is>
-      </c>
-      <c r="F166" s="22" t="inlineStr">
-        <is>
-          <t>BASIC WL</t>
-        </is>
-      </c>
-      <c r="G166" s="22" t="inlineStr"/>
-    </row>
-    <row r="167" ht="16" customHeight="1">
-      <c r="A167" s="25" t="inlineStr">
-        <is>
-          <t>ram:CountryID</t>
-        </is>
-      </c>
-      <c r="B167" s="22" t="inlineStr">
-        <is>
-          <t>Delivery country</t>
-        </is>
-      </c>
-      <c r="C167" s="22" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="D167" s="23" t="inlineStr">
+      <c r="D171" s="23" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="E167" s="22" t="inlineStr">
+      <c r="E171" s="22" t="inlineStr">
         <is>
           <t>1..1</t>
         </is>
       </c>
-      <c r="F167" s="22" t="inlineStr">
-        <is>
-          <t>BASIC WL</t>
-        </is>
-      </c>
-      <c r="G167" s="22" t="inlineStr"/>
-    </row>
-    <row r="168" ht="16" customHeight="1">
-      <c r="A168" s="10" t="inlineStr">
-        <is>
-          <t>ram:ActualDeliverySupplyChainEvent</t>
-        </is>
-      </c>
-      <c r="B168" s="11" t="inlineStr">
-        <is>
-          <t>Actual delivery event</t>
-        </is>
-      </c>
-      <c r="C168" s="11" t="inlineStr">
-        <is>
-          <t>Complex</t>
-        </is>
-      </c>
-      <c r="D168" s="19" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="E168" s="11" t="inlineStr">
-        <is>
-          <t>0..1</t>
-        </is>
-      </c>
-      <c r="F168" s="11" t="inlineStr">
-        <is>
-          <t>BASIC WL</t>
-        </is>
-      </c>
-      <c r="G168" s="11" t="inlineStr"/>
-    </row>
-    <row r="169" ht="16" customHeight="1">
-      <c r="A169" s="21" t="inlineStr">
-        <is>
-          <t>ram:OccurrenceDateTime</t>
-        </is>
-      </c>
-      <c r="B169" s="22" t="inlineStr">
-        <is>
-          <t>Actual delivery date</t>
-        </is>
-      </c>
-      <c r="C169" s="22" t="inlineStr">
-        <is>
-          <t>Complex</t>
-        </is>
-      </c>
-      <c r="D169" s="23" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="E169" s="22" t="inlineStr">
-        <is>
-          <t>1..1</t>
-        </is>
-      </c>
-      <c r="F169" s="22" t="inlineStr">
-        <is>
-          <t>BASIC WL</t>
-        </is>
-      </c>
-      <c r="G169" s="22" t="inlineStr"/>
-    </row>
-    <row r="170" ht="16" customHeight="1">
-      <c r="A170" s="25" t="inlineStr">
-        <is>
-          <t>udt:DateTimeString @format="102"</t>
-        </is>
-      </c>
-      <c r="B170" s="22" t="inlineStr">
-        <is>
-          <t>Delivery date</t>
-        </is>
-      </c>
-      <c r="C170" s="22" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D170" s="23" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="E170" s="22" t="inlineStr">
-        <is>
-          <t>1..1</t>
-        </is>
-      </c>
-      <c r="F170" s="22" t="inlineStr">
-        <is>
-          <t>BASIC WL</t>
-        </is>
-      </c>
-      <c r="G170" s="22" t="inlineStr">
-        <is>
-          <t>YYYYMMDD</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="16" customHeight="1">
-      <c r="A171" s="10" t="inlineStr">
-        <is>
-          <t>ram:DeliveryNoteReferencedDocument</t>
-        </is>
-      </c>
-      <c r="B171" s="11" t="inlineStr">
-        <is>
-          <t>Delivery note reference</t>
-        </is>
-      </c>
-      <c r="C171" s="11" t="inlineStr">
-        <is>
-          <t>Complex</t>
-        </is>
-      </c>
-      <c r="D171" s="19" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="E171" s="11" t="inlineStr">
-        <is>
-          <t>0..1</t>
-        </is>
-      </c>
-      <c r="F171" s="11" t="inlineStr">
+      <c r="F171" s="22" t="inlineStr">
         <is>
           <t>EXTENDED</t>
         </is>
       </c>
-      <c r="G171" s="11" t="inlineStr"/>
+      <c r="G171" s="22" t="inlineStr"/>
     </row>
     <row r="172" ht="16" customHeight="1">
       <c r="A172" s="21" t="inlineStr">
         <is>
+          <t>ram:FormattedIssueDateTime</t>
+        </is>
+      </c>
+      <c r="B172" s="22" t="inlineStr">
+        <is>
+          <t>Delivery note date</t>
+        </is>
+      </c>
+      <c r="C172" s="22" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="D172" s="24" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="E172" s="22" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="F172" s="22" t="inlineStr">
+        <is>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="G172" s="22" t="inlineStr"/>
+    </row>
+    <row r="173" ht="16" customHeight="1">
+      <c r="A173" s="25" t="inlineStr">
+        <is>
+          <t>qdt:DateTimeString @format="102"</t>
+        </is>
+      </c>
+      <c r="B173" s="22" t="inlineStr">
+        <is>
+          <t>Delivery note date</t>
+        </is>
+      </c>
+      <c r="C173" s="22" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D173" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E173" s="22" t="inlineStr">
+        <is>
+          <t>1..1</t>
+        </is>
+      </c>
+      <c r="F173" s="22" t="inlineStr">
+        <is>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="G173" s="22" t="inlineStr"/>
+    </row>
+    <row r="174" ht="16" customHeight="1">
+      <c r="A174" s="10" t="inlineStr">
+        <is>
+          <t>ram:DespatchAdviceReferencedDocument</t>
+        </is>
+      </c>
+      <c r="B174" s="11" t="inlineStr">
+        <is>
+          <t>Despatch advice reference</t>
+        </is>
+      </c>
+      <c r="C174" s="11" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="D174" s="19" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="E174" s="11" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="F174" s="11" t="inlineStr">
+        <is>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="G174" s="11" t="inlineStr"/>
+    </row>
+    <row r="175" ht="16" customHeight="1">
+      <c r="A175" s="21" t="inlineStr">
+        <is>
           <t>ram:IssuerAssignedID</t>
         </is>
       </c>
-      <c r="B172" s="22" t="inlineStr">
-        <is>
-          <t>Delivery note number</t>
-        </is>
-      </c>
-      <c r="C172" s="22" t="inlineStr">
+      <c r="B175" s="22" t="inlineStr">
+        <is>
+          <t>Despatch advice number</t>
+        </is>
+      </c>
+      <c r="C175" s="22" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D172" s="23" t="inlineStr">
+      <c r="D175" s="23" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="E172" s="22" t="inlineStr">
+      <c r="E175" s="22" t="inlineStr">
         <is>
           <t>1..1</t>
         </is>
       </c>
-      <c r="F172" s="22" t="inlineStr">
+      <c r="F175" s="22" t="inlineStr">
         <is>
           <t>EXTENDED</t>
         </is>
       </c>
-      <c r="G172" s="22" t="inlineStr"/>
-    </row>
-    <row r="173" ht="16" customHeight="1">
-      <c r="A173" s="21" t="inlineStr">
-        <is>
-          <t>ram:FormattedIssueDateTime</t>
-        </is>
-      </c>
-      <c r="B173" s="22" t="inlineStr">
-        <is>
-          <t>Delivery note date</t>
-        </is>
-      </c>
-      <c r="C173" s="22" t="inlineStr">
-        <is>
-          <t>Complex</t>
-        </is>
-      </c>
-      <c r="D173" s="24" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="E173" s="22" t="inlineStr">
-        <is>
-          <t>0..1</t>
-        </is>
-      </c>
-      <c r="F173" s="22" t="inlineStr">
-        <is>
-          <t>EXTENDED</t>
-        </is>
-      </c>
-      <c r="G173" s="22" t="inlineStr"/>
-    </row>
-    <row r="174" ht="16" customHeight="1">
-      <c r="A174" s="25" t="inlineStr">
-        <is>
-          <t>qdt:DateTimeString @format="102"</t>
-        </is>
-      </c>
-      <c r="B174" s="22" t="inlineStr">
-        <is>
-          <t>Delivery note date</t>
-        </is>
-      </c>
-      <c r="C174" s="22" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D174" s="23" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="E174" s="22" t="inlineStr">
-        <is>
-          <t>1..1</t>
-        </is>
-      </c>
-      <c r="F174" s="22" t="inlineStr">
-        <is>
-          <t>EXTENDED</t>
-        </is>
-      </c>
-      <c r="G174" s="22" t="inlineStr"/>
-    </row>
-    <row r="175" ht="16" customHeight="1">
-      <c r="A175" s="10" t="inlineStr">
-        <is>
-          <t>ram:DespatchAdviceReferencedDocument</t>
-        </is>
-      </c>
-      <c r="B175" s="11" t="inlineStr">
-        <is>
-          <t>Despatch advice reference</t>
-        </is>
-      </c>
-      <c r="C175" s="11" t="inlineStr">
-        <is>
-          <t>Complex</t>
-        </is>
-      </c>
-      <c r="D175" s="19" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="E175" s="11" t="inlineStr">
-        <is>
-          <t>0..1</t>
-        </is>
-      </c>
-      <c r="F175" s="11" t="inlineStr">
-        <is>
-          <t>EXTENDED</t>
-        </is>
-      </c>
-      <c r="G175" s="11" t="inlineStr"/>
-    </row>
-    <row r="176" ht="16" customHeight="1">
-      <c r="A176" s="21" t="inlineStr">
-        <is>
-          <t>ram:IssuerAssignedID</t>
-        </is>
-      </c>
-      <c r="B176" s="22" t="inlineStr">
-        <is>
-          <t>Despatch advice number</t>
-        </is>
-      </c>
-      <c r="C176" s="22" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="D176" s="23" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="E176" s="22" t="inlineStr">
-        <is>
-          <t>1..1</t>
-        </is>
-      </c>
-      <c r="F176" s="22" t="inlineStr">
-        <is>
-          <t>EXTENDED</t>
-        </is>
-      </c>
-      <c r="G176" s="22" t="inlineStr"/>
+      <c r="G175" s="22" t="inlineStr"/>
+    </row>
+    <row r="176" ht="18" customHeight="1">
+      <c r="A176" s="6" t="inlineStr">
+        <is>
+          <t>ram:ApplicableHeaderTradeSettlement</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="16" customHeight="1">
       <c r="A177" s="7" t="inlineStr">
         <is>
-          <t>── ram:ApplicableHeaderTradeSettlement ──</t>
+          <t>ram:ApplicableHeaderTradeSettlement</t>
         </is>
       </c>
       <c r="B177" s="8" t="inlineStr">
         <is>
-          <t>Header Trade Settlement</t>
-        </is>
-      </c>
-      <c r="C177" s="8" t="inlineStr"/>
-      <c r="D177" s="8" t="inlineStr"/>
-      <c r="E177" s="8" t="inlineStr"/>
-      <c r="F177" s="8" t="inlineStr"/>
+          <t>Header-level settlement</t>
+        </is>
+      </c>
+      <c r="C177" s="8" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="D177" s="5" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E177" s="8" t="inlineStr">
+        <is>
+          <t>1..1</t>
+        </is>
+      </c>
+      <c r="F177" s="8" t="inlineStr">
+        <is>
+          <t>MINIMUM</t>
+        </is>
+      </c>
       <c r="G177" s="8" t="inlineStr"/>
     </row>
     <row r="178" ht="16" customHeight="1">
-      <c r="A178" s="14" t="inlineStr">
-        <is>
-          <t>ram:ApplicableHeaderTradeSettlement</t>
-        </is>
-      </c>
-      <c r="B178" s="15" t="inlineStr">
-        <is>
-          <t>Header-level settlement</t>
-        </is>
-      </c>
-      <c r="C178" s="15" t="inlineStr">
-        <is>
-          <t>Complex</t>
-        </is>
-      </c>
-      <c r="D178" s="17" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="E178" s="15" t="inlineStr">
-        <is>
-          <t>1..1</t>
-        </is>
-      </c>
-      <c r="F178" s="15" t="inlineStr">
-        <is>
-          <t>MINIMUM</t>
-        </is>
-      </c>
-      <c r="G178" s="15" t="inlineStr"/>
+      <c r="A178" s="10" t="inlineStr">
+        <is>
+          <t>ram:CreditorReferenceID</t>
+        </is>
+      </c>
+      <c r="B178" s="11" t="inlineStr">
+        <is>
+          <t>Creditor reference (SEPA)</t>
+        </is>
+      </c>
+      <c r="C178" s="11" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D178" s="19" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="E178" s="11" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="F178" s="11" t="inlineStr">
+        <is>
+          <t>EN 16931</t>
+        </is>
+      </c>
+      <c r="G178" s="11" t="inlineStr"/>
     </row>
     <row r="179" ht="16" customHeight="1">
       <c r="A179" s="10" t="inlineStr">
         <is>
-          <t>ram:CreditorReferenceID</t>
+          <t>ram:PaymentReference</t>
         </is>
       </c>
       <c r="B179" s="11" t="inlineStr">
         <is>
-          <t>Creditor reference (SEPA)</t>
+          <t>Payment reference (remittance info)</t>
         </is>
       </c>
       <c r="C179" s="11" t="inlineStr">
@@ -6530,7 +6490,7 @@
       </c>
       <c r="F179" s="11" t="inlineStr">
         <is>
-          <t>EN 16931</t>
+          <t>BASIC WL</t>
         </is>
       </c>
       <c r="G179" s="11" t="inlineStr"/>
@@ -6538,17 +6498,17 @@
     <row r="180" ht="16" customHeight="1">
       <c r="A180" s="10" t="inlineStr">
         <is>
-          <t>ram:PaymentReference</t>
+          <t>ram:TaxCurrencyCode</t>
         </is>
       </c>
       <c r="B180" s="11" t="inlineStr">
         <is>
-          <t>Payment reference (remittance info)</t>
+          <t>VAT accounting currency</t>
         </is>
       </c>
       <c r="C180" s="11" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="D180" s="19" t="inlineStr">
@@ -6563,20 +6523,24 @@
       </c>
       <c r="F180" s="11" t="inlineStr">
         <is>
-          <t>BASIC WL</t>
-        </is>
-      </c>
-      <c r="G180" s="11" t="inlineStr"/>
+          <t>EN 16931</t>
+        </is>
+      </c>
+      <c r="G180" s="11" t="inlineStr">
+        <is>
+          <t>ISO 4217 – if different from invoice currency</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="16" customHeight="1">
       <c r="A181" s="10" t="inlineStr">
         <is>
-          <t>ram:TaxCurrencyCode</t>
+          <t>ram:InvoiceCurrencyCode</t>
         </is>
       </c>
       <c r="B181" s="11" t="inlineStr">
         <is>
-          <t>VAT accounting currency</t>
+          <t>Invoice currency</t>
         </is>
       </c>
       <c r="C181" s="11" t="inlineStr">
@@ -6584,159 +6548,155 @@
           <t>Code</t>
         </is>
       </c>
-      <c r="D181" s="19" t="inlineStr">
-        <is>
-          <t>Optional</t>
+      <c r="D181" s="13" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="E181" s="11" t="inlineStr">
         <is>
-          <t>0..1</t>
+          <t>1..1</t>
         </is>
       </c>
       <c r="F181" s="11" t="inlineStr">
         <is>
-          <t>EN 16931</t>
+          <t>MINIMUM</t>
         </is>
       </c>
       <c r="G181" s="11" t="inlineStr">
         <is>
-          <t>ISO 4217 – if different from invoice currency</t>
+          <t>ISO 4217 – e.g. EUR, GBP, USD</t>
         </is>
       </c>
     </row>
     <row r="182" ht="16" customHeight="1">
       <c r="A182" s="10" t="inlineStr">
         <is>
-          <t>ram:InvoiceCurrencyCode</t>
+          <t>ram:InvoiceIssuerReference</t>
         </is>
       </c>
       <c r="B182" s="11" t="inlineStr">
         <is>
-          <t>Invoice currency</t>
+          <t>Seller internal reference</t>
         </is>
       </c>
       <c r="C182" s="11" t="inlineStr">
         <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="D182" s="13" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D182" s="19" t="inlineStr">
+        <is>
+          <t>Optional</t>
         </is>
       </c>
       <c r="E182" s="11" t="inlineStr">
         <is>
-          <t>1..1</t>
+          <t>0..1</t>
         </is>
       </c>
       <c r="F182" s="11" t="inlineStr">
         <is>
-          <t>MINIMUM</t>
-        </is>
-      </c>
-      <c r="G182" s="11" t="inlineStr">
-        <is>
-          <t>ISO 4217 – e.g. EUR, GBP, USD</t>
-        </is>
-      </c>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="G182" s="11" t="inlineStr"/>
     </row>
     <row r="183" ht="16" customHeight="1">
       <c r="A183" s="10" t="inlineStr">
         <is>
-          <t>ram:InvoiceIssuerReference</t>
+          <t>ram:PayeeTradeParty</t>
         </is>
       </c>
       <c r="B183" s="11" t="inlineStr">
         <is>
-          <t>Seller internal reference</t>
+          <t>Payee (if different from seller)</t>
         </is>
       </c>
       <c r="C183" s="11" t="inlineStr">
         <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="D183" s="19" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="E183" s="11" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="F183" s="11" t="inlineStr">
+        <is>
+          <t>EN 16931</t>
+        </is>
+      </c>
+      <c r="G183" s="11" t="inlineStr"/>
+    </row>
+    <row r="184" ht="16" customHeight="1">
+      <c r="A184" s="21" t="inlineStr">
+        <is>
+          <t>ram:ID</t>
+        </is>
+      </c>
+      <c r="B184" s="22" t="inlineStr">
+        <is>
+          <t>Payee internal identifier</t>
+        </is>
+      </c>
+      <c r="C184" s="22" t="inlineStr">
+        <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D183" s="19" t="inlineStr">
+      <c r="D184" s="24" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="E183" s="11" t="inlineStr">
+      <c r="E184" s="22" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="F183" s="11" t="inlineStr">
-        <is>
-          <t>EXTENDED</t>
-        </is>
-      </c>
-      <c r="G183" s="11" t="inlineStr"/>
-    </row>
-    <row r="184" ht="16" customHeight="1">
-      <c r="A184" s="10" t="inlineStr">
-        <is>
-          <t>ram:PayeeTradeParty</t>
-        </is>
-      </c>
-      <c r="B184" s="11" t="inlineStr">
-        <is>
-          <t>Payee (if different from seller)</t>
-        </is>
-      </c>
-      <c r="C184" s="11" t="inlineStr">
-        <is>
-          <t>Complex</t>
-        </is>
-      </c>
-      <c r="D184" s="19" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="E184" s="11" t="inlineStr">
-        <is>
-          <t>0..1</t>
-        </is>
-      </c>
-      <c r="F184" s="11" t="inlineStr">
+      <c r="F184" s="22" t="inlineStr">
         <is>
           <t>EN 16931</t>
         </is>
       </c>
-      <c r="G184" s="11" t="inlineStr"/>
+      <c r="G184" s="22" t="inlineStr"/>
     </row>
     <row r="185" ht="16" customHeight="1">
       <c r="A185" s="21" t="inlineStr">
         <is>
-          <t>ram:GlobalID @schemeID</t>
+          <t>ram:Name</t>
         </is>
       </c>
       <c r="B185" s="22" t="inlineStr">
         <is>
-          <t>Payee global identifier</t>
+          <t>Payee name</t>
         </is>
       </c>
       <c r="C185" s="22" t="inlineStr">
         <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="D185" s="24" t="inlineStr">
-        <is>
-          <t>Optional</t>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D185" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="E185" s="22" t="inlineStr">
         <is>
-          <t>0..1</t>
+          <t>1..1</t>
         </is>
       </c>
       <c r="F185" s="22" t="inlineStr">
         <is>
-          <t>EXTENDED</t>
+          <t>EN 16931</t>
         </is>
       </c>
       <c r="G185" s="22" t="inlineStr"/>
@@ -6744,229 +6704,229 @@
     <row r="186" ht="16" customHeight="1">
       <c r="A186" s="21" t="inlineStr">
         <is>
-          <t>ram:ID</t>
+          <t>ram:SpecifiedLegalOrganization</t>
         </is>
       </c>
       <c r="B186" s="22" t="inlineStr">
         <is>
-          <t>Payee internal identifier</t>
+          <t>Payee legal registration</t>
         </is>
       </c>
       <c r="C186" s="22" t="inlineStr">
         <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="D186" s="24" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="E186" s="22" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="F186" s="22" t="inlineStr">
+        <is>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="G186" s="22" t="inlineStr"/>
+    </row>
+    <row r="187" ht="16" customHeight="1">
+      <c r="A187" s="25" t="inlineStr">
+        <is>
+          <t>ram:ID @schemeID</t>
+        </is>
+      </c>
+      <c r="B187" s="22" t="inlineStr">
+        <is>
+          <t>Payee registration number</t>
+        </is>
+      </c>
+      <c r="C187" s="22" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="D187" s="24" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="E187" s="22" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="F187" s="22" t="inlineStr">
+        <is>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="G187" s="22" t="inlineStr"/>
+    </row>
+    <row r="188" ht="16" customHeight="1">
+      <c r="A188" s="10" t="inlineStr">
+        <is>
+          <t>ram:SpecifiedTradeSettlementPaymentMeans</t>
+        </is>
+      </c>
+      <c r="B188" s="11" t="inlineStr">
+        <is>
+          <t>Payment means</t>
+        </is>
+      </c>
+      <c r="C188" s="11" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="D188" s="19" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="E188" s="11" t="inlineStr">
+        <is>
+          <t>0..n</t>
+        </is>
+      </c>
+      <c r="F188" s="11" t="inlineStr">
+        <is>
+          <t>BASIC WL</t>
+        </is>
+      </c>
+      <c r="G188" s="11" t="inlineStr"/>
+    </row>
+    <row r="189" ht="16" customHeight="1">
+      <c r="A189" s="21" t="inlineStr">
+        <is>
+          <t>ram:TypeCode</t>
+        </is>
+      </c>
+      <c r="B189" s="22" t="inlineStr">
+        <is>
+          <t>Payment means type code</t>
+        </is>
+      </c>
+      <c r="C189" s="22" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="D189" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E189" s="22" t="inlineStr">
+        <is>
+          <t>1..1</t>
+        </is>
+      </c>
+      <c r="F189" s="22" t="inlineStr">
+        <is>
+          <t>BASIC WL</t>
+        </is>
+      </c>
+      <c r="G189" s="22" t="inlineStr">
+        <is>
+          <t>10=cash | 20=cheque | 30=credit transfer | 42=bank | 48=card | 49=direct debit | 58=SEPA CT | 59=SEPA DD</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="16" customHeight="1">
+      <c r="A190" s="21" t="inlineStr">
+        <is>
+          <t>ram:Information</t>
+        </is>
+      </c>
+      <c r="B190" s="22" t="inlineStr">
+        <is>
+          <t>Payment means information</t>
+        </is>
+      </c>
+      <c r="C190" s="22" t="inlineStr">
+        <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D186" s="24" t="inlineStr">
+      <c r="D190" s="24" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="E186" s="22" t="inlineStr">
+      <c r="E190" s="22" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="F186" s="22" t="inlineStr">
-        <is>
-          <t>EN 16931</t>
-        </is>
-      </c>
-      <c r="G186" s="22" t="inlineStr"/>
-    </row>
-    <row r="187" ht="16" customHeight="1">
-      <c r="A187" s="21" t="inlineStr">
-        <is>
-          <t>ram:Name</t>
-        </is>
-      </c>
-      <c r="B187" s="22" t="inlineStr">
-        <is>
-          <t>Payee name</t>
-        </is>
-      </c>
-      <c r="C187" s="22" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="D187" s="23" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="E187" s="22" t="inlineStr">
-        <is>
-          <t>1..1</t>
-        </is>
-      </c>
-      <c r="F187" s="22" t="inlineStr">
-        <is>
-          <t>EN 16931</t>
-        </is>
-      </c>
-      <c r="G187" s="22" t="inlineStr"/>
-    </row>
-    <row r="188" ht="16" customHeight="1">
-      <c r="A188" s="21" t="inlineStr">
-        <is>
-          <t>ram:SpecifiedLegalOrganization</t>
-        </is>
-      </c>
-      <c r="B188" s="22" t="inlineStr">
-        <is>
-          <t>Payee legal registration</t>
-        </is>
-      </c>
-      <c r="C188" s="22" t="inlineStr">
-        <is>
-          <t>Complex</t>
-        </is>
-      </c>
-      <c r="D188" s="24" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="E188" s="22" t="inlineStr">
-        <is>
-          <t>0..1</t>
-        </is>
-      </c>
-      <c r="F188" s="22" t="inlineStr">
+      <c r="F190" s="22" t="inlineStr">
         <is>
           <t>EXTENDED</t>
         </is>
       </c>
-      <c r="G188" s="22" t="inlineStr"/>
-    </row>
-    <row r="189" ht="16" customHeight="1">
-      <c r="A189" s="25" t="inlineStr">
-        <is>
-          <t>ram:ID @schemeID</t>
-        </is>
-      </c>
-      <c r="B189" s="22" t="inlineStr">
-        <is>
-          <t>Payee registration number</t>
-        </is>
-      </c>
-      <c r="C189" s="22" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="D189" s="24" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="E189" s="22" t="inlineStr">
-        <is>
-          <t>0..1</t>
-        </is>
-      </c>
-      <c r="F189" s="22" t="inlineStr">
-        <is>
-          <t>EXTENDED</t>
-        </is>
-      </c>
-      <c r="G189" s="22" t="inlineStr"/>
-    </row>
-    <row r="190" ht="16" customHeight="1">
-      <c r="A190" s="10" t="inlineStr">
-        <is>
-          <t>ram:SpecifiedTradeSettlementPaymentMeans</t>
-        </is>
-      </c>
-      <c r="B190" s="11" t="inlineStr">
-        <is>
-          <t>Payment means</t>
-        </is>
-      </c>
-      <c r="C190" s="11" t="inlineStr">
-        <is>
-          <t>Complex</t>
-        </is>
-      </c>
-      <c r="D190" s="19" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="E190" s="11" t="inlineStr">
-        <is>
-          <t>0..n</t>
-        </is>
-      </c>
-      <c r="F190" s="11" t="inlineStr">
-        <is>
-          <t>BASIC WL</t>
-        </is>
-      </c>
-      <c r="G190" s="11" t="inlineStr"/>
+      <c r="G190" s="22" t="inlineStr"/>
     </row>
     <row r="191" ht="16" customHeight="1">
       <c r="A191" s="21" t="inlineStr">
         <is>
-          <t>ram:TypeCode</t>
+          <t>ram:PayerPartyDebtorFinancialAccount</t>
         </is>
       </c>
       <c r="B191" s="22" t="inlineStr">
         <is>
-          <t>Payment means type code</t>
+          <t>Debtor bank account</t>
         </is>
       </c>
       <c r="C191" s="22" t="inlineStr">
         <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="D191" s="23" t="inlineStr">
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="D191" s="24" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="E191" s="22" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="F191" s="22" t="inlineStr">
+        <is>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="G191" s="22" t="inlineStr"/>
+    </row>
+    <row r="192" ht="16" customHeight="1">
+      <c r="A192" s="25" t="inlineStr">
+        <is>
+          <t>ram:IBANID</t>
+        </is>
+      </c>
+      <c r="B192" s="22" t="inlineStr">
+        <is>
+          <t>Debtor IBAN</t>
+        </is>
+      </c>
+      <c r="C192" s="22" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D192" s="23" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="E191" s="22" t="inlineStr">
+      <c r="E192" s="22" t="inlineStr">
         <is>
           <t>1..1</t>
-        </is>
-      </c>
-      <c r="F191" s="22" t="inlineStr">
-        <is>
-          <t>BASIC WL</t>
-        </is>
-      </c>
-      <c r="G191" s="22" t="inlineStr">
-        <is>
-          <t>10=cash | 20=cheque | 30=credit transfer | 42=bank account | 48=card | 49=direct debit | 57=wire | 58=SEPA CT | 59=SEPA DD</t>
-        </is>
-      </c>
-    </row>
-    <row r="192" ht="16" customHeight="1">
-      <c r="A192" s="21" t="inlineStr">
-        <is>
-          <t>ram:Information</t>
-        </is>
-      </c>
-      <c r="B192" s="22" t="inlineStr">
-        <is>
-          <t>Payment means information</t>
-        </is>
-      </c>
-      <c r="C192" s="22" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="D192" s="24" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="E192" s="22" t="inlineStr">
-        <is>
-          <t>0..1</t>
         </is>
       </c>
       <c r="F192" s="22" t="inlineStr">
@@ -6979,12 +6939,12 @@
     <row r="193" ht="16" customHeight="1">
       <c r="A193" s="21" t="inlineStr">
         <is>
-          <t>ram:PayerPartyDebtorFinancialAccount</t>
+          <t>ram:PayeePartyCreditorFinancialAccount</t>
         </is>
       </c>
       <c r="B193" s="22" t="inlineStr">
         <is>
-          <t>Debtor bank account</t>
+          <t>Creditor bank account (IBAN)</t>
         </is>
       </c>
       <c r="C193" s="22" t="inlineStr">
@@ -6992,9 +6952,9 @@
           <t>Complex</t>
         </is>
       </c>
-      <c r="D193" s="24" t="inlineStr">
-        <is>
-          <t>Optional</t>
+      <c r="D193" s="27" t="inlineStr">
+        <is>
+          <t>Conditional</t>
         </is>
       </c>
       <c r="E193" s="22" t="inlineStr">
@@ -7004,7 +6964,7 @@
       </c>
       <c r="F193" s="22" t="inlineStr">
         <is>
-          <t>EXTENDED</t>
+          <t>BASIC WL</t>
         </is>
       </c>
       <c r="G193" s="22" t="inlineStr"/>
@@ -7017,7 +6977,7 @@
       </c>
       <c r="B194" s="22" t="inlineStr">
         <is>
-          <t>Debtor IBAN</t>
+          <t>Creditor IBAN</t>
         </is>
       </c>
       <c r="C194" s="22" t="inlineStr">
@@ -7037,90 +6997,90 @@
       </c>
       <c r="F194" s="22" t="inlineStr">
         <is>
+          <t>BASIC WL</t>
+        </is>
+      </c>
+      <c r="G194" s="22" t="inlineStr">
+        <is>
+          <t>E.g. GB29NWBK60161331926819</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="16" customHeight="1">
+      <c r="A195" s="25" t="inlineStr">
+        <is>
+          <t>ram:ProprietaryID</t>
+        </is>
+      </c>
+      <c r="B195" s="22" t="inlineStr">
+        <is>
+          <t>Proprietary account identifier</t>
+        </is>
+      </c>
+      <c r="C195" s="22" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D195" s="24" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="E195" s="22" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="F195" s="22" t="inlineStr">
+        <is>
           <t>EXTENDED</t>
         </is>
       </c>
-      <c r="G194" s="22" t="inlineStr"/>
-    </row>
-    <row r="195" ht="16" customHeight="1">
-      <c r="A195" s="21" t="inlineStr">
-        <is>
-          <t>ram:PayeePartyCreditorFinancialAccount</t>
-        </is>
-      </c>
-      <c r="B195" s="22" t="inlineStr">
-        <is>
-          <t>Creditor bank account (IBAN)</t>
-        </is>
-      </c>
-      <c r="C195" s="22" t="inlineStr">
+      <c r="G195" s="22" t="inlineStr"/>
+    </row>
+    <row r="196" ht="16" customHeight="1">
+      <c r="A196" s="21" t="inlineStr">
+        <is>
+          <t>ram:PayeeSpecifiedCreditorFinancialInstitution</t>
+        </is>
+      </c>
+      <c r="B196" s="22" t="inlineStr">
+        <is>
+          <t>Creditor financial institution</t>
+        </is>
+      </c>
+      <c r="C196" s="22" t="inlineStr">
         <is>
           <t>Complex</t>
         </is>
       </c>
-      <c r="D195" s="27" t="inlineStr">
-        <is>
-          <t>Conditional</t>
-        </is>
-      </c>
-      <c r="E195" s="22" t="inlineStr">
+      <c r="D196" s="24" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="E196" s="22" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="F195" s="22" t="inlineStr">
+      <c r="F196" s="22" t="inlineStr">
         <is>
           <t>BASIC WL</t>
         </is>
       </c>
-      <c r="G195" s="22" t="inlineStr"/>
-    </row>
-    <row r="196" ht="16" customHeight="1">
-      <c r="A196" s="25" t="inlineStr">
-        <is>
-          <t>ram:IBANID</t>
-        </is>
-      </c>
-      <c r="B196" s="22" t="inlineStr">
-        <is>
-          <t>Creditor IBAN</t>
-        </is>
-      </c>
-      <c r="C196" s="22" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="D196" s="23" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="E196" s="22" t="inlineStr">
-        <is>
-          <t>1..1</t>
-        </is>
-      </c>
-      <c r="F196" s="22" t="inlineStr">
-        <is>
-          <t>BASIC WL</t>
-        </is>
-      </c>
-      <c r="G196" s="22" t="inlineStr">
-        <is>
-          <t>E.g. GB29NWBK60161331926819</t>
-        </is>
-      </c>
+      <c r="G196" s="22" t="inlineStr"/>
     </row>
     <row r="197" ht="16" customHeight="1">
       <c r="A197" s="25" t="inlineStr">
         <is>
-          <t>ram:ProprietaryID</t>
+          <t>ram:BICID</t>
         </is>
       </c>
       <c r="B197" s="22" t="inlineStr">
         <is>
-          <t>Proprietary account identifier</t>
+          <t>BIC / SWIFT code</t>
         </is>
       </c>
       <c r="C197" s="22" t="inlineStr">
@@ -7140,147 +7100,151 @@
       </c>
       <c r="F197" s="22" t="inlineStr">
         <is>
-          <t>EXTENDED</t>
-        </is>
-      </c>
-      <c r="G197" s="22" t="inlineStr"/>
+          <t>BASIC WL</t>
+        </is>
+      </c>
+      <c r="G197" s="22" t="inlineStr">
+        <is>
+          <t>E.g. NWBKGB2L</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="16" customHeight="1">
-      <c r="A198" s="21" t="inlineStr">
-        <is>
-          <t>ram:PayeeSpecifiedCreditorFinancialInstitution</t>
-        </is>
-      </c>
-      <c r="B198" s="22" t="inlineStr">
-        <is>
-          <t>Creditor financial institution</t>
-        </is>
-      </c>
-      <c r="C198" s="22" t="inlineStr">
+      <c r="A198" s="10" t="inlineStr">
+        <is>
+          <t>ram:ApplicableTradeTax</t>
+        </is>
+      </c>
+      <c r="B198" s="11" t="inlineStr">
+        <is>
+          <t>VAT breakdown (header level)</t>
+        </is>
+      </c>
+      <c r="C198" s="11" t="inlineStr">
         <is>
           <t>Complex</t>
         </is>
       </c>
-      <c r="D198" s="24" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="E198" s="22" t="inlineStr">
-        <is>
-          <t>0..1</t>
-        </is>
-      </c>
-      <c r="F198" s="22" t="inlineStr">
-        <is>
-          <t>BASIC WL</t>
-        </is>
-      </c>
-      <c r="G198" s="22" t="inlineStr"/>
+      <c r="D198" s="13" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E198" s="11" t="inlineStr">
+        <is>
+          <t>1..n</t>
+        </is>
+      </c>
+      <c r="F198" s="11" t="inlineStr">
+        <is>
+          <t>MINIMUM</t>
+        </is>
+      </c>
+      <c r="G198" s="11" t="inlineStr">
+        <is>
+          <t>One block per distinct VAT rate</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="16" customHeight="1">
-      <c r="A199" s="25" t="inlineStr">
-        <is>
-          <t>ram:BICID</t>
+      <c r="A199" s="21" t="inlineStr">
+        <is>
+          <t>ram:CalculatedAmount</t>
         </is>
       </c>
       <c r="B199" s="22" t="inlineStr">
         <is>
-          <t>BIC / SWIFT code</t>
+          <t>Calculated VAT amount</t>
         </is>
       </c>
       <c r="C199" s="22" t="inlineStr">
         <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="D199" s="24" t="inlineStr">
-        <is>
-          <t>Optional</t>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="D199" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="E199" s="22" t="inlineStr">
         <is>
-          <t>0..1</t>
+          <t>1..1</t>
         </is>
       </c>
       <c r="F199" s="22" t="inlineStr">
         <is>
-          <t>BASIC WL</t>
-        </is>
-      </c>
-      <c r="G199" s="22" t="inlineStr">
-        <is>
-          <t>E.g. NWBKGB2L</t>
-        </is>
-      </c>
+          <t>MINIMUM</t>
+        </is>
+      </c>
+      <c r="G199" s="22" t="inlineStr"/>
     </row>
     <row r="200" ht="16" customHeight="1">
-      <c r="A200" s="10" t="inlineStr">
-        <is>
-          <t>ram:ApplicableTradeTax</t>
-        </is>
-      </c>
-      <c r="B200" s="11" t="inlineStr">
-        <is>
-          <t>VAT breakdown (header level)</t>
-        </is>
-      </c>
-      <c r="C200" s="11" t="inlineStr">
-        <is>
-          <t>Complex</t>
-        </is>
-      </c>
-      <c r="D200" s="13" t="inlineStr">
+      <c r="A200" s="21" t="inlineStr">
+        <is>
+          <t>ram:TypeCode</t>
+        </is>
+      </c>
+      <c r="B200" s="22" t="inlineStr">
+        <is>
+          <t>Tax type code</t>
+        </is>
+      </c>
+      <c r="C200" s="22" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="D200" s="23" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="E200" s="11" t="inlineStr">
-        <is>
-          <t>1..n</t>
-        </is>
-      </c>
-      <c r="F200" s="11" t="inlineStr">
+      <c r="E200" s="22" t="inlineStr">
+        <is>
+          <t>1..1</t>
+        </is>
+      </c>
+      <c r="F200" s="22" t="inlineStr">
         <is>
           <t>MINIMUM</t>
         </is>
       </c>
-      <c r="G200" s="11" t="inlineStr">
-        <is>
-          <t>One block per distinct VAT rate</t>
+      <c r="G200" s="22" t="inlineStr">
+        <is>
+          <t>Always VAT</t>
         </is>
       </c>
     </row>
     <row r="201" ht="16" customHeight="1">
       <c r="A201" s="21" t="inlineStr">
         <is>
-          <t>ram:CalculatedAmount</t>
+          <t>ram:ExemptionReason</t>
         </is>
       </c>
       <c r="B201" s="22" t="inlineStr">
         <is>
-          <t>Calculated VAT amount</t>
+          <t>VAT exemption reason (text)</t>
         </is>
       </c>
       <c r="C201" s="22" t="inlineStr">
         <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="D201" s="23" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D201" s="27" t="inlineStr">
+        <is>
+          <t>Conditional</t>
         </is>
       </c>
       <c r="E201" s="22" t="inlineStr">
         <is>
-          <t>1..1</t>
+          <t>0..1</t>
         </is>
       </c>
       <c r="F201" s="22" t="inlineStr">
         <is>
-          <t>MINIMUM</t>
+          <t>BASIC WL</t>
         </is>
       </c>
       <c r="G201" s="22" t="inlineStr"/>
@@ -7288,17 +7252,17 @@
     <row r="202" ht="16" customHeight="1">
       <c r="A202" s="21" t="inlineStr">
         <is>
-          <t>ram:TypeCode</t>
+          <t>ram:BasisAmount</t>
         </is>
       </c>
       <c r="B202" s="22" t="inlineStr">
         <is>
-          <t>Tax type code</t>
+          <t>Taxable base amount for this rate</t>
         </is>
       </c>
       <c r="C202" s="22" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="D202" s="23" t="inlineStr">
@@ -7316,97 +7280,101 @@
           <t>MINIMUM</t>
         </is>
       </c>
-      <c r="G202" s="22" t="inlineStr">
-        <is>
-          <t>Always VAT</t>
-        </is>
-      </c>
+      <c r="G202" s="22" t="inlineStr"/>
     </row>
     <row r="203" ht="16" customHeight="1">
       <c r="A203" s="21" t="inlineStr">
         <is>
-          <t>ram:ExemptionReason</t>
+          <t>ram:CategoryCode</t>
         </is>
       </c>
       <c r="B203" s="22" t="inlineStr">
         <is>
-          <t>VAT exemption reason (text)</t>
+          <t>VAT category code (header)</t>
         </is>
       </c>
       <c r="C203" s="22" t="inlineStr">
         <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="D203" s="27" t="inlineStr">
-        <is>
-          <t>Conditional</t>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="D203" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="E203" s="22" t="inlineStr">
         <is>
-          <t>0..1</t>
+          <t>1..1</t>
         </is>
       </c>
       <c r="F203" s="22" t="inlineStr">
         <is>
-          <t>BASIC WL</t>
-        </is>
-      </c>
-      <c r="G203" s="22" t="inlineStr"/>
+          <t>MINIMUM</t>
+        </is>
+      </c>
+      <c r="G203" s="22" t="inlineStr">
+        <is>
+          <t>S | Z | E | AE | K | G | O</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="16" customHeight="1">
       <c r="A204" s="21" t="inlineStr">
         <is>
-          <t>ram:BasisAmount</t>
+          <t>ram:ExemptionReasonCode</t>
         </is>
       </c>
       <c r="B204" s="22" t="inlineStr">
         <is>
-          <t>Taxable base amount for this rate</t>
+          <t>VAT exemption reason code</t>
         </is>
       </c>
       <c r="C204" s="22" t="inlineStr">
         <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="D204" s="23" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="D204" s="27" t="inlineStr">
+        <is>
+          <t>Conditional</t>
         </is>
       </c>
       <c r="E204" s="22" t="inlineStr">
         <is>
-          <t>1..1</t>
+          <t>0..1</t>
         </is>
       </c>
       <c r="F204" s="22" t="inlineStr">
         <is>
-          <t>MINIMUM</t>
-        </is>
-      </c>
-      <c r="G204" s="22" t="inlineStr"/>
+          <t>EN 16931</t>
+        </is>
+      </c>
+      <c r="G204" s="22" t="inlineStr">
+        <is>
+          <t>VATEX-EU-AE, VATEX-EU-O…</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="16" customHeight="1">
       <c r="A205" s="21" t="inlineStr">
         <is>
-          <t>ram:LineTotalBasisAmount</t>
+          <t>ram:TaxPointDate</t>
         </is>
       </c>
       <c r="B205" s="22" t="inlineStr">
         <is>
-          <t>Sum of line amounts for this rate</t>
+          <t>VAT point date</t>
         </is>
       </c>
       <c r="C205" s="22" t="inlineStr">
         <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="D205" s="24" t="inlineStr">
-        <is>
-          <t>Optional</t>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="D205" s="27" t="inlineStr">
+        <is>
+          <t>Conditional</t>
         </is>
       </c>
       <c r="E205" s="22" t="inlineStr">
@@ -7416,40 +7384,40 @@
       </c>
       <c r="F205" s="22" t="inlineStr">
         <is>
-          <t>EXTENDED</t>
+          <t>EN 16931</t>
         </is>
       </c>
       <c r="G205" s="22" t="inlineStr"/>
     </row>
     <row r="206" ht="16" customHeight="1">
-      <c r="A206" s="21" t="inlineStr">
-        <is>
-          <t>ram:AllowanceChargeBasisAmount</t>
+      <c r="A206" s="25" t="inlineStr">
+        <is>
+          <t>udt:DateString @format="102"</t>
         </is>
       </c>
       <c r="B206" s="22" t="inlineStr">
         <is>
-          <t>Allowances/charges for this rate</t>
+          <t>Tax point date</t>
         </is>
       </c>
       <c r="C206" s="22" t="inlineStr">
         <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="D206" s="24" t="inlineStr">
-        <is>
-          <t>Optional</t>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D206" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="E206" s="22" t="inlineStr">
         <is>
-          <t>0..1</t>
+          <t>1..1</t>
         </is>
       </c>
       <c r="F206" s="22" t="inlineStr">
         <is>
-          <t>EXTENDED</t>
+          <t>EN 16931</t>
         </is>
       </c>
       <c r="G206" s="22" t="inlineStr"/>
@@ -7457,12 +7425,12 @@
     <row r="207" ht="16" customHeight="1">
       <c r="A207" s="21" t="inlineStr">
         <is>
-          <t>ram:CategoryCode</t>
+          <t>ram:DueDateTypeCode</t>
         </is>
       </c>
       <c r="B207" s="22" t="inlineStr">
         <is>
-          <t>VAT category code (header)</t>
+          <t>Tax point date code</t>
         </is>
       </c>
       <c r="C207" s="22" t="inlineStr">
@@ -7470,41 +7438,41 @@
           <t>Code</t>
         </is>
       </c>
-      <c r="D207" s="23" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
+      <c r="D207" s="27" t="inlineStr">
+        <is>
+          <t>Conditional</t>
         </is>
       </c>
       <c r="E207" s="22" t="inlineStr">
         <is>
-          <t>1..1</t>
+          <t>0..1</t>
         </is>
       </c>
       <c r="F207" s="22" t="inlineStr">
         <is>
-          <t>MINIMUM</t>
+          <t>EN 16931</t>
         </is>
       </c>
       <c r="G207" s="22" t="inlineStr">
         <is>
-          <t>S | Z | E | AE | K | G | O</t>
+          <t>5=delivery | 29=payment | 72=invoice date</t>
         </is>
       </c>
     </row>
     <row r="208" ht="16" customHeight="1">
       <c r="A208" s="21" t="inlineStr">
         <is>
-          <t>ram:ExemptionReasonCode</t>
+          <t>ram:RateApplicablePercent</t>
         </is>
       </c>
       <c r="B208" s="22" t="inlineStr">
         <is>
-          <t>VAT exemption reason code</t>
+          <t>VAT rate (%)</t>
         </is>
       </c>
       <c r="C208" s="22" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="D208" s="27" t="inlineStr">
@@ -7519,132 +7487,128 @@
       </c>
       <c r="F208" s="22" t="inlineStr">
         <is>
-          <t>EN 16931</t>
+          <t>MINIMUM</t>
         </is>
       </c>
       <c r="G208" s="22" t="inlineStr">
         <is>
-          <t>VATEX-EU-AE, VATEX-EU-O…</t>
+          <t>E.g. 20.00</t>
         </is>
       </c>
     </row>
     <row r="209" ht="16" customHeight="1">
-      <c r="A209" s="21" t="inlineStr">
-        <is>
-          <t>ram:TaxPointDate</t>
-        </is>
-      </c>
-      <c r="B209" s="22" t="inlineStr">
-        <is>
-          <t>VAT point date</t>
-        </is>
-      </c>
-      <c r="C209" s="22" t="inlineStr">
+      <c r="A209" s="10" t="inlineStr">
+        <is>
+          <t>ram:BillingSpecifiedPeriod</t>
+        </is>
+      </c>
+      <c r="B209" s="11" t="inlineStr">
+        <is>
+          <t>Invoicing period</t>
+        </is>
+      </c>
+      <c r="C209" s="11" t="inlineStr">
         <is>
           <t>Complex</t>
         </is>
       </c>
-      <c r="D209" s="27" t="inlineStr">
+      <c r="D209" s="19" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="E209" s="11" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="F209" s="11" t="inlineStr">
+        <is>
+          <t>BASIC WL</t>
+        </is>
+      </c>
+      <c r="G209" s="11" t="inlineStr"/>
+    </row>
+    <row r="210" ht="16" customHeight="1">
+      <c r="A210" s="21" t="inlineStr">
+        <is>
+          <t>ram:StartDateTime</t>
+        </is>
+      </c>
+      <c r="B210" s="22" t="inlineStr">
+        <is>
+          <t>Period start date</t>
+        </is>
+      </c>
+      <c r="C210" s="22" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="D210" s="27" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
       </c>
-      <c r="E209" s="22" t="inlineStr">
+      <c r="E210" s="22" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="F209" s="22" t="inlineStr">
-        <is>
-          <t>EN 16931</t>
-        </is>
-      </c>
-      <c r="G209" s="22" t="inlineStr"/>
-    </row>
-    <row r="210" ht="16" customHeight="1">
-      <c r="A210" s="25" t="inlineStr">
-        <is>
-          <t>udt:DateString @format="102"</t>
-        </is>
-      </c>
-      <c r="B210" s="22" t="inlineStr">
-        <is>
-          <t>Tax point date</t>
-        </is>
-      </c>
-      <c r="C210" s="22" t="inlineStr">
+      <c r="F210" s="22" t="inlineStr">
+        <is>
+          <t>BASIC WL</t>
+        </is>
+      </c>
+      <c r="G210" s="22" t="inlineStr"/>
+    </row>
+    <row r="211" ht="16" customHeight="1">
+      <c r="A211" s="25" t="inlineStr">
+        <is>
+          <t>udt:DateTimeString @format="102"</t>
+        </is>
+      </c>
+      <c r="B211" s="22" t="inlineStr">
+        <is>
+          <t>Period start date</t>
+        </is>
+      </c>
+      <c r="C211" s="22" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="D210" s="23" t="inlineStr">
+      <c r="D211" s="23" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="E210" s="22" t="inlineStr">
+      <c r="E211" s="22" t="inlineStr">
         <is>
           <t>1..1</t>
         </is>
       </c>
-      <c r="F210" s="22" t="inlineStr">
-        <is>
-          <t>EN 16931</t>
-        </is>
-      </c>
-      <c r="G210" s="22" t="inlineStr"/>
-    </row>
-    <row r="211" ht="16" customHeight="1">
-      <c r="A211" s="21" t="inlineStr">
-        <is>
-          <t>ram:DueDateTypeCode</t>
-        </is>
-      </c>
-      <c r="B211" s="22" t="inlineStr">
-        <is>
-          <t>Tax point date code</t>
-        </is>
-      </c>
-      <c r="C211" s="22" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="D211" s="27" t="inlineStr">
-        <is>
-          <t>Conditional</t>
-        </is>
-      </c>
-      <c r="E211" s="22" t="inlineStr">
-        <is>
-          <t>0..1</t>
-        </is>
-      </c>
       <c r="F211" s="22" t="inlineStr">
         <is>
-          <t>EN 16931</t>
-        </is>
-      </c>
-      <c r="G211" s="22" t="inlineStr">
-        <is>
-          <t>5=delivery | 29=payment | 72=invoice date</t>
-        </is>
-      </c>
+          <t>BASIC WL</t>
+        </is>
+      </c>
+      <c r="G211" s="22" t="inlineStr"/>
     </row>
     <row r="212" ht="16" customHeight="1">
       <c r="A212" s="21" t="inlineStr">
         <is>
-          <t>ram:RateApplicablePercent</t>
+          <t>ram:EndDateTime</t>
         </is>
       </c>
       <c r="B212" s="22" t="inlineStr">
         <is>
-          <t>VAT rate (%)</t>
+          <t>Period end date</t>
         </is>
       </c>
       <c r="C212" s="22" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>Complex</t>
         </is>
       </c>
       <c r="D212" s="27" t="inlineStr">
@@ -7659,95 +7623,91 @@
       </c>
       <c r="F212" s="22" t="inlineStr">
         <is>
-          <t>MINIMUM</t>
-        </is>
-      </c>
-      <c r="G212" s="22" t="inlineStr">
-        <is>
-          <t>E.g. 20.00</t>
-        </is>
-      </c>
+          <t>BASIC WL</t>
+        </is>
+      </c>
+      <c r="G212" s="22" t="inlineStr"/>
     </row>
     <row r="213" ht="16" customHeight="1">
-      <c r="A213" s="10" t="inlineStr">
-        <is>
-          <t>ram:BillingSpecifiedPeriod</t>
-        </is>
-      </c>
-      <c r="B213" s="11" t="inlineStr">
-        <is>
-          <t>Invoicing period</t>
-        </is>
-      </c>
-      <c r="C213" s="11" t="inlineStr">
+      <c r="A213" s="25" t="inlineStr">
+        <is>
+          <t>udt:DateTimeString @format="102"</t>
+        </is>
+      </c>
+      <c r="B213" s="22" t="inlineStr">
+        <is>
+          <t>Period end date</t>
+        </is>
+      </c>
+      <c r="C213" s="22" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D213" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E213" s="22" t="inlineStr">
+        <is>
+          <t>1..1</t>
+        </is>
+      </c>
+      <c r="F213" s="22" t="inlineStr">
+        <is>
+          <t>BASIC WL</t>
+        </is>
+      </c>
+      <c r="G213" s="22" t="inlineStr"/>
+    </row>
+    <row r="214" ht="16" customHeight="1">
+      <c r="A214" s="10" t="inlineStr">
+        <is>
+          <t>ram:SpecifiedTradeAllowanceCharge</t>
+        </is>
+      </c>
+      <c r="B214" s="11" t="inlineStr">
+        <is>
+          <t>Document-level discount / surcharge</t>
+        </is>
+      </c>
+      <c r="C214" s="11" t="inlineStr">
         <is>
           <t>Complex</t>
         </is>
       </c>
-      <c r="D213" s="19" t="inlineStr">
+      <c r="D214" s="19" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="E213" s="11" t="inlineStr">
-        <is>
-          <t>0..1</t>
-        </is>
-      </c>
-      <c r="F213" s="11" t="inlineStr">
-        <is>
-          <t>BASIC WL</t>
-        </is>
-      </c>
-      <c r="G213" s="11" t="inlineStr"/>
-    </row>
-    <row r="214" ht="16" customHeight="1">
-      <c r="A214" s="21" t="inlineStr">
-        <is>
-          <t>ram:StartDateTime</t>
-        </is>
-      </c>
-      <c r="B214" s="22" t="inlineStr">
-        <is>
-          <t>Period start date</t>
-        </is>
-      </c>
-      <c r="C214" s="22" t="inlineStr">
-        <is>
-          <t>Complex</t>
-        </is>
-      </c>
-      <c r="D214" s="27" t="inlineStr">
-        <is>
-          <t>Conditional</t>
-        </is>
-      </c>
-      <c r="E214" s="22" t="inlineStr">
-        <is>
-          <t>0..1</t>
-        </is>
-      </c>
-      <c r="F214" s="22" t="inlineStr">
-        <is>
-          <t>BASIC WL</t>
-        </is>
-      </c>
-      <c r="G214" s="22" t="inlineStr"/>
+      <c r="E214" s="11" t="inlineStr">
+        <is>
+          <t>0..n</t>
+        </is>
+      </c>
+      <c r="F214" s="11" t="inlineStr">
+        <is>
+          <t>EN 16931</t>
+        </is>
+      </c>
+      <c r="G214" s="11" t="inlineStr"/>
     </row>
     <row r="215" ht="16" customHeight="1">
-      <c r="A215" s="25" t="inlineStr">
-        <is>
-          <t>udt:DateTimeString @format="102"</t>
+      <c r="A215" s="21" t="inlineStr">
+        <is>
+          <t>ram:ChargeIndicator</t>
         </is>
       </c>
       <c r="B215" s="22" t="inlineStr">
         <is>
-          <t>Period start date</t>
+          <t>false=discount, true=surcharge</t>
         </is>
       </c>
       <c r="C215" s="22" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Indicator</t>
         </is>
       </c>
       <c r="D215" s="23" t="inlineStr">
@@ -7762,7 +7722,7 @@
       </c>
       <c r="F215" s="22" t="inlineStr">
         <is>
-          <t>BASIC WL</t>
+          <t>EN 16931</t>
         </is>
       </c>
       <c r="G215" s="22" t="inlineStr"/>
@@ -7770,22 +7730,22 @@
     <row r="216" ht="16" customHeight="1">
       <c r="A216" s="21" t="inlineStr">
         <is>
-          <t>ram:EndDateTime</t>
+          <t>ram:SequenceNumeric</t>
         </is>
       </c>
       <c r="B216" s="22" t="inlineStr">
         <is>
-          <t>Period end date</t>
+          <t>Application sequence</t>
         </is>
       </c>
       <c r="C216" s="22" t="inlineStr">
         <is>
-          <t>Complex</t>
-        </is>
-      </c>
-      <c r="D216" s="27" t="inlineStr">
-        <is>
-          <t>Conditional</t>
+          <t>Numeric</t>
+        </is>
+      </c>
+      <c r="D216" s="24" t="inlineStr">
+        <is>
+          <t>Optional</t>
         </is>
       </c>
       <c r="E216" s="22" t="inlineStr">
@@ -7795,91 +7755,91 @@
       </c>
       <c r="F216" s="22" t="inlineStr">
         <is>
-          <t>BASIC WL</t>
+          <t>EXTENDED</t>
         </is>
       </c>
       <c r="G216" s="22" t="inlineStr"/>
     </row>
     <row r="217" ht="16" customHeight="1">
-      <c r="A217" s="25" t="inlineStr">
-        <is>
-          <t>udt:DateTimeString @format="102"</t>
+      <c r="A217" s="21" t="inlineStr">
+        <is>
+          <t>ram:CalculationPercent</t>
         </is>
       </c>
       <c r="B217" s="22" t="inlineStr">
         <is>
-          <t>Period end date</t>
+          <t>Discount/surcharge rate (%)</t>
         </is>
       </c>
       <c r="C217" s="22" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D217" s="23" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="D217" s="24" t="inlineStr">
+        <is>
+          <t>Optional</t>
         </is>
       </c>
       <c r="E217" s="22" t="inlineStr">
         <is>
-          <t>1..1</t>
+          <t>0..1</t>
         </is>
       </c>
       <c r="F217" s="22" t="inlineStr">
         <is>
-          <t>BASIC WL</t>
+          <t>EN 16931</t>
         </is>
       </c>
       <c r="G217" s="22" t="inlineStr"/>
     </row>
     <row r="218" ht="16" customHeight="1">
-      <c r="A218" s="10" t="inlineStr">
-        <is>
-          <t>ram:SpecifiedTradeAllowanceCharge</t>
-        </is>
-      </c>
-      <c r="B218" s="11" t="inlineStr">
-        <is>
-          <t>Document-level discount / surcharge</t>
-        </is>
-      </c>
-      <c r="C218" s="11" t="inlineStr">
-        <is>
-          <t>Complex</t>
-        </is>
-      </c>
-      <c r="D218" s="19" t="inlineStr">
+      <c r="A218" s="21" t="inlineStr">
+        <is>
+          <t>ram:BasisAmount</t>
+        </is>
+      </c>
+      <c r="B218" s="22" t="inlineStr">
+        <is>
+          <t>Discount/surcharge base amount</t>
+        </is>
+      </c>
+      <c r="C218" s="22" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="D218" s="24" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="E218" s="11" t="inlineStr">
-        <is>
-          <t>0..n</t>
-        </is>
-      </c>
-      <c r="F218" s="11" t="inlineStr">
+      <c r="E218" s="22" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="F218" s="22" t="inlineStr">
         <is>
           <t>EN 16931</t>
         </is>
       </c>
-      <c r="G218" s="11" t="inlineStr"/>
+      <c r="G218" s="22" t="inlineStr"/>
     </row>
     <row r="219" ht="16" customHeight="1">
       <c r="A219" s="21" t="inlineStr">
         <is>
-          <t>ram:ChargeIndicator</t>
+          <t>ram:ActualAmount</t>
         </is>
       </c>
       <c r="B219" s="22" t="inlineStr">
         <is>
-          <t>false=discount, true=surcharge</t>
+          <t>Document-level discount/surcharge amount</t>
         </is>
       </c>
       <c r="C219" s="22" t="inlineStr">
         <is>
-          <t>Indicator</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="D219" s="23" t="inlineStr">
@@ -7902,17 +7862,17 @@
     <row r="220" ht="16" customHeight="1">
       <c r="A220" s="21" t="inlineStr">
         <is>
-          <t>ram:SequenceNumeric</t>
+          <t>ram:ReasonCode</t>
         </is>
       </c>
       <c r="B220" s="22" t="inlineStr">
         <is>
-          <t>Application sequence</t>
+          <t>Discount/surcharge reason code</t>
         </is>
       </c>
       <c r="C220" s="22" t="inlineStr">
         <is>
-          <t>Numeric</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="D220" s="24" t="inlineStr">
@@ -7927,7 +7887,7 @@
       </c>
       <c r="F220" s="22" t="inlineStr">
         <is>
-          <t>EXTENDED</t>
+          <t>EN 16931</t>
         </is>
       </c>
       <c r="G220" s="22" t="inlineStr"/>
@@ -7935,17 +7895,17 @@
     <row r="221" ht="16" customHeight="1">
       <c r="A221" s="21" t="inlineStr">
         <is>
-          <t>ram:CalculationPercent</t>
+          <t>ram:Reason</t>
         </is>
       </c>
       <c r="B221" s="22" t="inlineStr">
         <is>
-          <t>Discount/surcharge rate (%)</t>
+          <t>Discount/surcharge reason text</t>
         </is>
       </c>
       <c r="C221" s="22" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="D221" s="24" t="inlineStr">
@@ -7968,469 +7928,473 @@
     <row r="222" ht="16" customHeight="1">
       <c r="A222" s="21" t="inlineStr">
         <is>
-          <t>ram:BasisAmount</t>
+          <t>ram:CategoryTradeTax</t>
         </is>
       </c>
       <c r="B222" s="22" t="inlineStr">
         <is>
-          <t>Discount/surcharge base amount</t>
+          <t>VAT linked to document-level allowance</t>
         </is>
       </c>
       <c r="C222" s="22" t="inlineStr">
         <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="D222" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E222" s="22" t="inlineStr">
+        <is>
+          <t>1..1</t>
+        </is>
+      </c>
+      <c r="F222" s="22" t="inlineStr">
+        <is>
+          <t>EN 16931</t>
+        </is>
+      </c>
+      <c r="G222" s="22" t="inlineStr"/>
+    </row>
+    <row r="223" ht="16" customHeight="1">
+      <c r="A223" s="25" t="inlineStr">
+        <is>
+          <t>ram:TypeCode</t>
+        </is>
+      </c>
+      <c r="B223" s="22" t="inlineStr">
+        <is>
+          <t>Tax type (document allowance)</t>
+        </is>
+      </c>
+      <c r="C223" s="22" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="D223" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E223" s="22" t="inlineStr">
+        <is>
+          <t>1..1</t>
+        </is>
+      </c>
+      <c r="F223" s="22" t="inlineStr">
+        <is>
+          <t>EN 16931</t>
+        </is>
+      </c>
+      <c r="G223" s="22" t="inlineStr">
+        <is>
+          <t>VAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="16" customHeight="1">
+      <c r="A224" s="25" t="inlineStr">
+        <is>
+          <t>ram:CategoryCode</t>
+        </is>
+      </c>
+      <c r="B224" s="22" t="inlineStr">
+        <is>
+          <t>VAT category (document allowance)</t>
+        </is>
+      </c>
+      <c r="C224" s="22" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="D224" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E224" s="22" t="inlineStr">
+        <is>
+          <t>1..1</t>
+        </is>
+      </c>
+      <c r="F224" s="22" t="inlineStr">
+        <is>
+          <t>EN 16931</t>
+        </is>
+      </c>
+      <c r="G224" s="22" t="inlineStr"/>
+    </row>
+    <row r="225" ht="16" customHeight="1">
+      <c r="A225" s="25" t="inlineStr">
+        <is>
+          <t>ram:RateApplicablePercent</t>
+        </is>
+      </c>
+      <c r="B225" s="22" t="inlineStr">
+        <is>
+          <t>VAT rate (document allowance)</t>
+        </is>
+      </c>
+      <c r="C225" s="22" t="inlineStr">
+        <is>
           <t>Decimal</t>
         </is>
       </c>
-      <c r="D222" s="24" t="inlineStr">
+      <c r="D225" s="27" t="inlineStr">
+        <is>
+          <t>Conditional</t>
+        </is>
+      </c>
+      <c r="E225" s="22" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="F225" s="22" t="inlineStr">
+        <is>
+          <t>EN 16931</t>
+        </is>
+      </c>
+      <c r="G225" s="22" t="inlineStr"/>
+    </row>
+    <row r="226" ht="16" customHeight="1">
+      <c r="A226" s="10" t="inlineStr">
+        <is>
+          <t>ram:SpecifiedLogisticsServiceCharge</t>
+        </is>
+      </c>
+      <c r="B226" s="11" t="inlineStr">
+        <is>
+          <t>Freight / logistics charge</t>
+        </is>
+      </c>
+      <c r="C226" s="11" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="D226" s="19" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="E222" s="22" t="inlineStr">
+      <c r="E226" s="11" t="inlineStr">
+        <is>
+          <t>0..n</t>
+        </is>
+      </c>
+      <c r="F226" s="11" t="inlineStr">
+        <is>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="G226" s="11" t="inlineStr"/>
+    </row>
+    <row r="227" ht="16" customHeight="1">
+      <c r="A227" s="21" t="inlineStr">
+        <is>
+          <t>ram:Description</t>
+        </is>
+      </c>
+      <c r="B227" s="22" t="inlineStr">
+        <is>
+          <t>Logistics charge description</t>
+        </is>
+      </c>
+      <c r="C227" s="22" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D227" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E227" s="22" t="inlineStr">
+        <is>
+          <t>1..1</t>
+        </is>
+      </c>
+      <c r="F227" s="22" t="inlineStr">
+        <is>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="G227" s="22" t="inlineStr"/>
+    </row>
+    <row r="228" ht="16" customHeight="1">
+      <c r="A228" s="21" t="inlineStr">
+        <is>
+          <t>ram:AppliedAmount</t>
+        </is>
+      </c>
+      <c r="B228" s="22" t="inlineStr">
+        <is>
+          <t>Logistics charge amount</t>
+        </is>
+      </c>
+      <c r="C228" s="22" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="D228" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E228" s="22" t="inlineStr">
+        <is>
+          <t>1..1</t>
+        </is>
+      </c>
+      <c r="F228" s="22" t="inlineStr">
+        <is>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="G228" s="22" t="inlineStr"/>
+    </row>
+    <row r="229" ht="16" customHeight="1">
+      <c r="A229" s="21" t="inlineStr">
+        <is>
+          <t>ram:AppliedTradeTax</t>
+        </is>
+      </c>
+      <c r="B229" s="22" t="inlineStr">
+        <is>
+          <t>VAT on logistics charge</t>
+        </is>
+      </c>
+      <c r="C229" s="22" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="D229" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E229" s="22" t="inlineStr">
+        <is>
+          <t>1..1</t>
+        </is>
+      </c>
+      <c r="F229" s="22" t="inlineStr">
+        <is>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="G229" s="22" t="inlineStr"/>
+    </row>
+    <row r="230" ht="16" customHeight="1">
+      <c r="A230" s="25" t="inlineStr">
+        <is>
+          <t>ram:TypeCode</t>
+        </is>
+      </c>
+      <c r="B230" s="22" t="inlineStr">
+        <is>
+          <t>Tax type (logistics charge)</t>
+        </is>
+      </c>
+      <c r="C230" s="22" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="D230" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E230" s="22" t="inlineStr">
+        <is>
+          <t>1..1</t>
+        </is>
+      </c>
+      <c r="F230" s="22" t="inlineStr">
+        <is>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="G230" s="22" t="inlineStr">
+        <is>
+          <t>VAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="16" customHeight="1">
+      <c r="A231" s="25" t="inlineStr">
+        <is>
+          <t>ram:CategoryCode</t>
+        </is>
+      </c>
+      <c r="B231" s="22" t="inlineStr">
+        <is>
+          <t>VAT category (logistics charge)</t>
+        </is>
+      </c>
+      <c r="C231" s="22" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="D231" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E231" s="22" t="inlineStr">
+        <is>
+          <t>1..1</t>
+        </is>
+      </c>
+      <c r="F231" s="22" t="inlineStr">
+        <is>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="G231" s="22" t="inlineStr"/>
+    </row>
+    <row r="232" ht="16" customHeight="1">
+      <c r="A232" s="25" t="inlineStr">
+        <is>
+          <t>ram:RateApplicablePercent</t>
+        </is>
+      </c>
+      <c r="B232" s="22" t="inlineStr">
+        <is>
+          <t>VAT rate (logistics charge)</t>
+        </is>
+      </c>
+      <c r="C232" s="22" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="D232" s="27" t="inlineStr">
+        <is>
+          <t>Conditional</t>
+        </is>
+      </c>
+      <c r="E232" s="22" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="F222" s="22" t="inlineStr">
-        <is>
-          <t>EN 16931</t>
-        </is>
-      </c>
-      <c r="G222" s="22" t="inlineStr"/>
-    </row>
-    <row r="223" ht="16" customHeight="1">
-      <c r="A223" s="21" t="inlineStr">
-        <is>
-          <t>ram:ActualAmount</t>
-        </is>
-      </c>
-      <c r="B223" s="22" t="inlineStr">
-        <is>
-          <t>Document-level discount/surcharge amount</t>
-        </is>
-      </c>
-      <c r="C223" s="22" t="inlineStr">
-        <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="D223" s="23" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="E223" s="22" t="inlineStr">
-        <is>
-          <t>1..1</t>
-        </is>
-      </c>
-      <c r="F223" s="22" t="inlineStr">
-        <is>
-          <t>EN 16931</t>
-        </is>
-      </c>
-      <c r="G223" s="22" t="inlineStr"/>
-    </row>
-    <row r="224" ht="16" customHeight="1">
-      <c r="A224" s="21" t="inlineStr">
-        <is>
-          <t>ram:ReasonCode</t>
-        </is>
-      </c>
-      <c r="B224" s="22" t="inlineStr">
-        <is>
-          <t>Discount/surcharge reason code</t>
-        </is>
-      </c>
-      <c r="C224" s="22" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="D224" s="24" t="inlineStr">
+      <c r="F232" s="22" t="inlineStr">
+        <is>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="G232" s="22" t="inlineStr"/>
+    </row>
+    <row r="233" ht="16" customHeight="1">
+      <c r="A233" s="10" t="inlineStr">
+        <is>
+          <t>ram:SpecifiedTradePaymentTerms</t>
+        </is>
+      </c>
+      <c r="B233" s="11" t="inlineStr">
+        <is>
+          <t>Payment terms</t>
+        </is>
+      </c>
+      <c r="C233" s="11" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="D233" s="19" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="E224" s="22" t="inlineStr">
+      <c r="E233" s="11" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="F224" s="22" t="inlineStr">
-        <is>
-          <t>EN 16931</t>
-        </is>
-      </c>
-      <c r="G224" s="22" t="inlineStr"/>
-    </row>
-    <row r="225" ht="16" customHeight="1">
-      <c r="A225" s="21" t="inlineStr">
-        <is>
-          <t>ram:Reason</t>
-        </is>
-      </c>
-      <c r="B225" s="22" t="inlineStr">
-        <is>
-          <t>Discount/surcharge reason text</t>
-        </is>
-      </c>
-      <c r="C225" s="22" t="inlineStr">
+      <c r="F233" s="11" t="inlineStr">
+        <is>
+          <t>BASIC WL</t>
+        </is>
+      </c>
+      <c r="G233" s="11" t="inlineStr"/>
+    </row>
+    <row r="234" ht="16" customHeight="1">
+      <c r="A234" s="21" t="inlineStr">
+        <is>
+          <t>ram:Description</t>
+        </is>
+      </c>
+      <c r="B234" s="22" t="inlineStr">
+        <is>
+          <t>Payment terms description</t>
+        </is>
+      </c>
+      <c r="C234" s="22" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D225" s="24" t="inlineStr">
+      <c r="D234" s="24" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="E225" s="22" t="inlineStr">
+      <c r="E234" s="22" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="F225" s="22" t="inlineStr">
-        <is>
-          <t>EN 16931</t>
-        </is>
-      </c>
-      <c r="G225" s="22" t="inlineStr"/>
-    </row>
-    <row r="226" ht="16" customHeight="1">
-      <c r="A226" s="21" t="inlineStr">
-        <is>
-          <t>ram:CategoryTradeTax</t>
-        </is>
-      </c>
-      <c r="B226" s="22" t="inlineStr">
-        <is>
-          <t>VAT linked to document-level allowance</t>
-        </is>
-      </c>
-      <c r="C226" s="22" t="inlineStr">
+      <c r="F234" s="22" t="inlineStr">
+        <is>
+          <t>BASIC WL</t>
+        </is>
+      </c>
+      <c r="G234" s="22" t="inlineStr">
+        <is>
+          <t>E.g. Net 30 days</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="16" customHeight="1">
+      <c r="A235" s="21" t="inlineStr">
+        <is>
+          <t>ram:DueDateDateTime</t>
+        </is>
+      </c>
+      <c r="B235" s="22" t="inlineStr">
+        <is>
+          <t>Payment due date</t>
+        </is>
+      </c>
+      <c r="C235" s="22" t="inlineStr">
         <is>
           <t>Complex</t>
         </is>
       </c>
-      <c r="D226" s="23" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="E226" s="22" t="inlineStr">
-        <is>
-          <t>1..1</t>
-        </is>
-      </c>
-      <c r="F226" s="22" t="inlineStr">
-        <is>
-          <t>EN 16931</t>
-        </is>
-      </c>
-      <c r="G226" s="22" t="inlineStr"/>
-    </row>
-    <row r="227" ht="16" customHeight="1">
-      <c r="A227" s="25" t="inlineStr">
-        <is>
-          <t>ram:TypeCode</t>
-        </is>
-      </c>
-      <c r="B227" s="22" t="inlineStr">
-        <is>
-          <t>Tax type (document allowance)</t>
-        </is>
-      </c>
-      <c r="C227" s="22" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="D227" s="23" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="E227" s="22" t="inlineStr">
-        <is>
-          <t>1..1</t>
-        </is>
-      </c>
-      <c r="F227" s="22" t="inlineStr">
-        <is>
-          <t>EN 16931</t>
-        </is>
-      </c>
-      <c r="G227" s="22" t="inlineStr">
-        <is>
-          <t>VAT</t>
-        </is>
-      </c>
-    </row>
-    <row r="228" ht="16" customHeight="1">
-      <c r="A228" s="25" t="inlineStr">
-        <is>
-          <t>ram:CategoryCode</t>
-        </is>
-      </c>
-      <c r="B228" s="22" t="inlineStr">
-        <is>
-          <t>VAT category (document allowance)</t>
-        </is>
-      </c>
-      <c r="C228" s="22" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="D228" s="23" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="E228" s="22" t="inlineStr">
-        <is>
-          <t>1..1</t>
-        </is>
-      </c>
-      <c r="F228" s="22" t="inlineStr">
-        <is>
-          <t>EN 16931</t>
-        </is>
-      </c>
-      <c r="G228" s="22" t="inlineStr"/>
-    </row>
-    <row r="229" ht="16" customHeight="1">
-      <c r="A229" s="25" t="inlineStr">
-        <is>
-          <t>ram:RateApplicablePercent</t>
-        </is>
-      </c>
-      <c r="B229" s="22" t="inlineStr">
-        <is>
-          <t>VAT rate (document allowance)</t>
-        </is>
-      </c>
-      <c r="C229" s="22" t="inlineStr">
-        <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="D229" s="27" t="inlineStr">
-        <is>
-          <t>Conditional</t>
-        </is>
-      </c>
-      <c r="E229" s="22" t="inlineStr">
+      <c r="D235" s="24" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="E235" s="22" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="F229" s="22" t="inlineStr">
-        <is>
-          <t>EN 16931</t>
-        </is>
-      </c>
-      <c r="G229" s="22" t="inlineStr"/>
-    </row>
-    <row r="230" ht="16" customHeight="1">
-      <c r="A230" s="10" t="inlineStr">
-        <is>
-          <t>ram:SpecifiedLogisticsServiceCharge</t>
-        </is>
-      </c>
-      <c r="B230" s="11" t="inlineStr">
-        <is>
-          <t>Freight / logistics charge</t>
-        </is>
-      </c>
-      <c r="C230" s="11" t="inlineStr">
-        <is>
-          <t>Complex</t>
-        </is>
-      </c>
-      <c r="D230" s="19" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="E230" s="11" t="inlineStr">
-        <is>
-          <t>0..n</t>
-        </is>
-      </c>
-      <c r="F230" s="11" t="inlineStr">
-        <is>
-          <t>EXTENDED</t>
-        </is>
-      </c>
-      <c r="G230" s="11" t="inlineStr"/>
-    </row>
-    <row r="231" ht="16" customHeight="1">
-      <c r="A231" s="21" t="inlineStr">
-        <is>
-          <t>ram:Description</t>
-        </is>
-      </c>
-      <c r="B231" s="22" t="inlineStr">
-        <is>
-          <t>Logistics charge description</t>
-        </is>
-      </c>
-      <c r="C231" s="22" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="D231" s="23" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="E231" s="22" t="inlineStr">
-        <is>
-          <t>1..1</t>
-        </is>
-      </c>
-      <c r="F231" s="22" t="inlineStr">
-        <is>
-          <t>EXTENDED</t>
-        </is>
-      </c>
-      <c r="G231" s="22" t="inlineStr"/>
-    </row>
-    <row r="232" ht="16" customHeight="1">
-      <c r="A232" s="21" t="inlineStr">
-        <is>
-          <t>ram:AppliedAmount</t>
-        </is>
-      </c>
-      <c r="B232" s="22" t="inlineStr">
-        <is>
-          <t>Logistics charge amount</t>
-        </is>
-      </c>
-      <c r="C232" s="22" t="inlineStr">
-        <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="D232" s="23" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="E232" s="22" t="inlineStr">
-        <is>
-          <t>1..1</t>
-        </is>
-      </c>
-      <c r="F232" s="22" t="inlineStr">
-        <is>
-          <t>EXTENDED</t>
-        </is>
-      </c>
-      <c r="G232" s="22" t="inlineStr"/>
-    </row>
-    <row r="233" ht="16" customHeight="1">
-      <c r="A233" s="21" t="inlineStr">
-        <is>
-          <t>ram:AppliedTradeTax</t>
-        </is>
-      </c>
-      <c r="B233" s="22" t="inlineStr">
-        <is>
-          <t>VAT on logistics charge</t>
-        </is>
-      </c>
-      <c r="C233" s="22" t="inlineStr">
-        <is>
-          <t>Complex</t>
-        </is>
-      </c>
-      <c r="D233" s="23" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="E233" s="22" t="inlineStr">
-        <is>
-          <t>1..1</t>
-        </is>
-      </c>
-      <c r="F233" s="22" t="inlineStr">
-        <is>
-          <t>EXTENDED</t>
-        </is>
-      </c>
-      <c r="G233" s="22" t="inlineStr"/>
-    </row>
-    <row r="234" ht="16" customHeight="1">
-      <c r="A234" s="25" t="inlineStr">
-        <is>
-          <t>ram:TypeCode</t>
-        </is>
-      </c>
-      <c r="B234" s="22" t="inlineStr">
-        <is>
-          <t>Tax type (logistics charge)</t>
-        </is>
-      </c>
-      <c r="C234" s="22" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="D234" s="23" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="E234" s="22" t="inlineStr">
-        <is>
-          <t>1..1</t>
-        </is>
-      </c>
-      <c r="F234" s="22" t="inlineStr">
-        <is>
-          <t>EXTENDED</t>
-        </is>
-      </c>
-      <c r="G234" s="22" t="inlineStr">
-        <is>
-          <t>VAT</t>
-        </is>
-      </c>
-    </row>
-    <row r="235" ht="16" customHeight="1">
-      <c r="A235" s="25" t="inlineStr">
-        <is>
-          <t>ram:CategoryCode</t>
-        </is>
-      </c>
-      <c r="B235" s="22" t="inlineStr">
-        <is>
-          <t>VAT category (logistics charge)</t>
-        </is>
-      </c>
-      <c r="C235" s="22" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="D235" s="23" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="E235" s="22" t="inlineStr">
-        <is>
-          <t>1..1</t>
-        </is>
-      </c>
       <c r="F235" s="22" t="inlineStr">
         <is>
-          <t>EXTENDED</t>
+          <t>BASIC WL</t>
         </is>
       </c>
       <c r="G235" s="22" t="inlineStr"/>
@@ -8438,83 +8402,83 @@
     <row r="236" ht="16" customHeight="1">
       <c r="A236" s="25" t="inlineStr">
         <is>
-          <t>ram:RateApplicablePercent</t>
+          <t>udt:DateTimeString @format="102"</t>
         </is>
       </c>
       <c r="B236" s="22" t="inlineStr">
         <is>
-          <t>VAT rate (logistics charge)</t>
+          <t>Payment due date</t>
         </is>
       </c>
       <c r="C236" s="22" t="inlineStr">
         <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="D236" s="27" t="inlineStr">
-        <is>
-          <t>Conditional</t>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D236" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="E236" s="22" t="inlineStr">
         <is>
+          <t>1..1</t>
+        </is>
+      </c>
+      <c r="F236" s="22" t="inlineStr">
+        <is>
+          <t>BASIC WL</t>
+        </is>
+      </c>
+      <c r="G236" s="22" t="inlineStr"/>
+    </row>
+    <row r="237" ht="16" customHeight="1">
+      <c r="A237" s="21" t="inlineStr">
+        <is>
+          <t>ram:DirectDebitMandateID</t>
+        </is>
+      </c>
+      <c r="B237" s="22" t="inlineStr">
+        <is>
+          <t>Direct debit mandate reference</t>
+        </is>
+      </c>
+      <c r="C237" s="22" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D237" s="24" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="E237" s="22" t="inlineStr">
+        <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="F236" s="22" t="inlineStr">
-        <is>
-          <t>EXTENDED</t>
-        </is>
-      </c>
-      <c r="G236" s="22" t="inlineStr"/>
-    </row>
-    <row r="237" ht="16" customHeight="1">
-      <c r="A237" s="10" t="inlineStr">
-        <is>
-          <t>ram:SpecifiedTradePaymentTerms</t>
-        </is>
-      </c>
-      <c r="B237" s="11" t="inlineStr">
-        <is>
-          <t>Payment terms</t>
-        </is>
-      </c>
-      <c r="C237" s="11" t="inlineStr">
-        <is>
-          <t>Complex</t>
-        </is>
-      </c>
-      <c r="D237" s="19" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="E237" s="11" t="inlineStr">
-        <is>
-          <t>0..1</t>
-        </is>
-      </c>
-      <c r="F237" s="11" t="inlineStr">
-        <is>
-          <t>BASIC WL</t>
-        </is>
-      </c>
-      <c r="G237" s="11" t="inlineStr"/>
+      <c r="F237" s="22" t="inlineStr">
+        <is>
+          <t>EN 16931</t>
+        </is>
+      </c>
+      <c r="G237" s="22" t="inlineStr"/>
     </row>
     <row r="238" ht="16" customHeight="1">
       <c r="A238" s="21" t="inlineStr">
         <is>
-          <t>ram:Description</t>
+          <t>ram:PartialPaymentAmount</t>
         </is>
       </c>
       <c r="B238" s="22" t="inlineStr">
         <is>
-          <t>Payment terms description</t>
+          <t>Partial payment amount</t>
         </is>
       </c>
       <c r="C238" s="22" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="D238" s="24" t="inlineStr">
@@ -8529,24 +8493,20 @@
       </c>
       <c r="F238" s="22" t="inlineStr">
         <is>
-          <t>BASIC WL</t>
-        </is>
-      </c>
-      <c r="G238" s="22" t="inlineStr">
-        <is>
-          <t>E.g. Net 30 days</t>
-        </is>
-      </c>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="G238" s="22" t="inlineStr"/>
     </row>
     <row r="239" ht="16" customHeight="1">
       <c r="A239" s="21" t="inlineStr">
         <is>
-          <t>ram:DueDateDateTime</t>
+          <t>ram:ApplicableTradePaymentDiscountTerms</t>
         </is>
       </c>
       <c r="B239" s="22" t="inlineStr">
         <is>
-          <t>Payment due date</t>
+          <t>Cash discount (early payment)</t>
         </is>
       </c>
       <c r="C239" s="22" t="inlineStr">
@@ -8566,7 +8526,7 @@
       </c>
       <c r="F239" s="22" t="inlineStr">
         <is>
-          <t>BASIC WL</t>
+          <t>EXTENDED</t>
         </is>
       </c>
       <c r="G239" s="22" t="inlineStr"/>
@@ -8574,309 +8534,317 @@
     <row r="240" ht="16" customHeight="1">
       <c r="A240" s="25" t="inlineStr">
         <is>
-          <t>udt:DateTimeString @format="102"</t>
+          <t>ram:BasisPeriodMeasure @unitCode</t>
         </is>
       </c>
       <c r="B240" s="22" t="inlineStr">
         <is>
-          <t>Payment due date</t>
+          <t>Discount period</t>
         </is>
       </c>
       <c r="C240" s="22" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D240" s="23" t="inlineStr">
+          <t>Measure</t>
+        </is>
+      </c>
+      <c r="D240" s="24" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="E240" s="22" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="F240" s="22" t="inlineStr">
+        <is>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="G240" s="22" t="inlineStr"/>
+    </row>
+    <row r="241" ht="16" customHeight="1">
+      <c r="A241" s="25" t="inlineStr">
+        <is>
+          <t>ram:BasisAmount</t>
+        </is>
+      </c>
+      <c r="B241" s="22" t="inlineStr">
+        <is>
+          <t>Discount base amount</t>
+        </is>
+      </c>
+      <c r="C241" s="22" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="D241" s="24" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="E241" s="22" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="F241" s="22" t="inlineStr">
+        <is>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="G241" s="22" t="inlineStr"/>
+    </row>
+    <row r="242" ht="16" customHeight="1">
+      <c r="A242" s="25" t="inlineStr">
+        <is>
+          <t>ram:CalculationPercent</t>
+        </is>
+      </c>
+      <c r="B242" s="22" t="inlineStr">
+        <is>
+          <t>Discount rate (%)</t>
+        </is>
+      </c>
+      <c r="C242" s="22" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="D242" s="24" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="E242" s="22" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="F242" s="22" t="inlineStr">
+        <is>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="G242" s="22" t="inlineStr"/>
+    </row>
+    <row r="243" ht="16" customHeight="1">
+      <c r="A243" s="25" t="inlineStr">
+        <is>
+          <t>ram:ActualDiscountAmount</t>
+        </is>
+      </c>
+      <c r="B243" s="22" t="inlineStr">
+        <is>
+          <t>Discount amount</t>
+        </is>
+      </c>
+      <c r="C243" s="22" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="D243" s="24" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="E243" s="22" t="inlineStr">
+        <is>
+          <t>0..1</t>
+        </is>
+      </c>
+      <c r="F243" s="22" t="inlineStr">
+        <is>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="G243" s="22" t="inlineStr"/>
+    </row>
+    <row r="244" ht="16" customHeight="1">
+      <c r="A244" s="10" t="inlineStr">
+        <is>
+          <t>ram:SpecifiedTradeSettlementHeaderMonetarySummation</t>
+        </is>
+      </c>
+      <c r="B244" s="11" t="inlineStr">
+        <is>
+          <t>Header monetary summation (totals)</t>
+        </is>
+      </c>
+      <c r="C244" s="11" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="D244" s="13" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="E240" s="22" t="inlineStr">
+      <c r="E244" s="11" t="inlineStr">
         <is>
           <t>1..1</t>
         </is>
       </c>
-      <c r="F240" s="22" t="inlineStr">
-        <is>
-          <t>BASIC WL</t>
-        </is>
-      </c>
-      <c r="G240" s="22" t="inlineStr"/>
-    </row>
-    <row r="241" ht="16" customHeight="1">
-      <c r="A241" s="21" t="inlineStr">
-        <is>
-          <t>ram:DirectDebitMandateID</t>
-        </is>
-      </c>
-      <c r="B241" s="22" t="inlineStr">
-        <is>
-          <t>Direct debit mandate reference</t>
-        </is>
-      </c>
-      <c r="C241" s="22" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="D241" s="24" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="E241" s="22" t="inlineStr">
+      <c r="F244" s="11" t="inlineStr">
+        <is>
+          <t>MINIMUM</t>
+        </is>
+      </c>
+      <c r="G244" s="11" t="inlineStr"/>
+    </row>
+    <row r="245" ht="16" customHeight="1">
+      <c r="A245" s="21" t="inlineStr">
+        <is>
+          <t>ram:LineTotalAmount</t>
+        </is>
+      </c>
+      <c r="B245" s="22" t="inlineStr">
+        <is>
+          <t>Sum of invoice line net amounts</t>
+        </is>
+      </c>
+      <c r="C245" s="22" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="D245" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="E245" s="22" t="inlineStr">
+        <is>
+          <t>1..1</t>
+        </is>
+      </c>
+      <c r="F245" s="22" t="inlineStr">
+        <is>
+          <t>MINIMUM</t>
+        </is>
+      </c>
+      <c r="G245" s="22" t="inlineStr"/>
+    </row>
+    <row r="246" ht="16" customHeight="1">
+      <c r="A246" s="21" t="inlineStr">
+        <is>
+          <t>ram:ChargeTotalAmount</t>
+        </is>
+      </c>
+      <c r="B246" s="22" t="inlineStr">
+        <is>
+          <t>Sum of document-level surcharges</t>
+        </is>
+      </c>
+      <c r="C246" s="22" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="D246" s="27" t="inlineStr">
+        <is>
+          <t>Conditional</t>
+        </is>
+      </c>
+      <c r="E246" s="22" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="F241" s="22" t="inlineStr">
+      <c r="F246" s="22" t="inlineStr">
         <is>
           <t>EN 16931</t>
         </is>
       </c>
-      <c r="G241" s="22" t="inlineStr"/>
-    </row>
-    <row r="242" ht="16" customHeight="1">
-      <c r="A242" s="21" t="inlineStr">
-        <is>
-          <t>ram:PartialPaymentAmount</t>
-        </is>
-      </c>
-      <c r="B242" s="22" t="inlineStr">
-        <is>
-          <t>Partial payment amount</t>
-        </is>
-      </c>
-      <c r="C242" s="22" t="inlineStr">
+      <c r="G246" s="22" t="inlineStr">
+        <is>
+          <t>0.00 if absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="16" customHeight="1">
+      <c r="A247" s="21" t="inlineStr">
+        <is>
+          <t>ram:AllowanceTotalAmount</t>
+        </is>
+      </c>
+      <c r="B247" s="22" t="inlineStr">
+        <is>
+          <t>Sum of document-level discounts</t>
+        </is>
+      </c>
+      <c r="C247" s="22" t="inlineStr">
         <is>
           <t>Decimal</t>
         </is>
       </c>
-      <c r="D242" s="24" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="E242" s="22" t="inlineStr">
+      <c r="D247" s="27" t="inlineStr">
+        <is>
+          <t>Conditional</t>
+        </is>
+      </c>
+      <c r="E247" s="22" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="F242" s="22" t="inlineStr">
-        <is>
-          <t>EXTENDED</t>
-        </is>
-      </c>
-      <c r="G242" s="22" t="inlineStr"/>
-    </row>
-    <row r="243" ht="16" customHeight="1">
-      <c r="A243" s="21" t="inlineStr">
-        <is>
-          <t>ram:ApplicableTradePaymentDiscountTerms</t>
-        </is>
-      </c>
-      <c r="B243" s="22" t="inlineStr">
-        <is>
-          <t>Cash discount (early payment)</t>
-        </is>
-      </c>
-      <c r="C243" s="22" t="inlineStr">
-        <is>
-          <t>Complex</t>
-        </is>
-      </c>
-      <c r="D243" s="24" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="E243" s="22" t="inlineStr">
-        <is>
-          <t>0..1</t>
-        </is>
-      </c>
-      <c r="F243" s="22" t="inlineStr">
-        <is>
-          <t>EXTENDED</t>
-        </is>
-      </c>
-      <c r="G243" s="22" t="inlineStr"/>
-    </row>
-    <row r="244" ht="16" customHeight="1">
-      <c r="A244" s="25" t="inlineStr">
-        <is>
-          <t>ram:BasisPeriodMeasure @unitCode</t>
-        </is>
-      </c>
-      <c r="B244" s="22" t="inlineStr">
-        <is>
-          <t>Discount period</t>
-        </is>
-      </c>
-      <c r="C244" s="22" t="inlineStr">
-        <is>
-          <t>Measure</t>
-        </is>
-      </c>
-      <c r="D244" s="24" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="E244" s="22" t="inlineStr">
-        <is>
-          <t>0..1</t>
-        </is>
-      </c>
-      <c r="F244" s="22" t="inlineStr">
-        <is>
-          <t>EXTENDED</t>
-        </is>
-      </c>
-      <c r="G244" s="22" t="inlineStr"/>
-    </row>
-    <row r="245" ht="16" customHeight="1">
-      <c r="A245" s="25" t="inlineStr">
-        <is>
-          <t>ram:BasisAmount</t>
-        </is>
-      </c>
-      <c r="B245" s="22" t="inlineStr">
-        <is>
-          <t>Discount base amount</t>
-        </is>
-      </c>
-      <c r="C245" s="22" t="inlineStr">
+      <c r="F247" s="22" t="inlineStr">
+        <is>
+          <t>EN 16931</t>
+        </is>
+      </c>
+      <c r="G247" s="22" t="inlineStr">
+        <is>
+          <t>0.00 if absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="16" customHeight="1">
+      <c r="A248" s="21" t="inlineStr">
+        <is>
+          <t>ram:TaxBasisTotalAmount</t>
+        </is>
+      </c>
+      <c r="B248" s="22" t="inlineStr">
+        <is>
+          <t>Invoice total amount excl. VAT</t>
+        </is>
+      </c>
+      <c r="C248" s="22" t="inlineStr">
         <is>
           <t>Decimal</t>
         </is>
       </c>
-      <c r="D245" s="24" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="E245" s="22" t="inlineStr">
-        <is>
-          <t>0..1</t>
-        </is>
-      </c>
-      <c r="F245" s="22" t="inlineStr">
-        <is>
-          <t>EXTENDED</t>
-        </is>
-      </c>
-      <c r="G245" s="22" t="inlineStr"/>
-    </row>
-    <row r="246" ht="16" customHeight="1">
-      <c r="A246" s="25" t="inlineStr">
-        <is>
-          <t>ram:CalculationPercent</t>
-        </is>
-      </c>
-      <c r="B246" s="22" t="inlineStr">
-        <is>
-          <t>Discount rate (%)</t>
-        </is>
-      </c>
-      <c r="C246" s="22" t="inlineStr">
-        <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="D246" s="24" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="E246" s="22" t="inlineStr">
-        <is>
-          <t>0..1</t>
-        </is>
-      </c>
-      <c r="F246" s="22" t="inlineStr">
-        <is>
-          <t>EXTENDED</t>
-        </is>
-      </c>
-      <c r="G246" s="22" t="inlineStr"/>
-    </row>
-    <row r="247" ht="16" customHeight="1">
-      <c r="A247" s="25" t="inlineStr">
-        <is>
-          <t>ram:ActualDiscountAmount</t>
-        </is>
-      </c>
-      <c r="B247" s="22" t="inlineStr">
-        <is>
-          <t>Discount amount</t>
-        </is>
-      </c>
-      <c r="C247" s="22" t="inlineStr">
-        <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="D247" s="24" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="E247" s="22" t="inlineStr">
-        <is>
-          <t>0..1</t>
-        </is>
-      </c>
-      <c r="F247" s="22" t="inlineStr">
-        <is>
-          <t>EXTENDED</t>
-        </is>
-      </c>
-      <c r="G247" s="22" t="inlineStr"/>
-    </row>
-    <row r="248" ht="16" customHeight="1">
-      <c r="A248" s="10" t="inlineStr">
-        <is>
-          <t>ram:SpecifiedTradeSettlementHeaderMonetarySummation</t>
-        </is>
-      </c>
-      <c r="B248" s="11" t="inlineStr">
-        <is>
-          <t>Header monetary summation (totals)</t>
-        </is>
-      </c>
-      <c r="C248" s="11" t="inlineStr">
-        <is>
-          <t>Complex</t>
-        </is>
-      </c>
-      <c r="D248" s="13" t="inlineStr">
+      <c r="D248" s="23" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="E248" s="11" t="inlineStr">
+      <c r="E248" s="22" t="inlineStr">
         <is>
           <t>1..1</t>
         </is>
       </c>
-      <c r="F248" s="11" t="inlineStr">
+      <c r="F248" s="22" t="inlineStr">
         <is>
           <t>MINIMUM</t>
         </is>
       </c>
-      <c r="G248" s="11" t="inlineStr"/>
+      <c r="G248" s="22" t="inlineStr"/>
     </row>
     <row r="249" ht="16" customHeight="1">
       <c r="A249" s="21" t="inlineStr">
         <is>
-          <t>ram:LineTotalAmount</t>
+          <t>ram:TaxTotalAmount @currencyID</t>
         </is>
       </c>
       <c r="B249" s="22" t="inlineStr">
         <is>
-          <t>Sum of invoice line net amounts</t>
+          <t>Total VAT amount</t>
         </is>
       </c>
       <c r="C249" s="22" t="inlineStr">
@@ -8899,17 +8867,21 @@
           <t>MINIMUM</t>
         </is>
       </c>
-      <c r="G249" s="22" t="inlineStr"/>
+      <c r="G249" s="22" t="inlineStr">
+        <is>
+          <t>currencyID = invoice currency</t>
+        </is>
+      </c>
     </row>
     <row r="250" ht="16" customHeight="1">
       <c r="A250" s="21" t="inlineStr">
         <is>
-          <t>ram:ChargeTotalAmount</t>
+          <t>ram:GrandTotalAmount</t>
         </is>
       </c>
       <c r="B250" s="22" t="inlineStr">
         <is>
-          <t>Sum of document-level surcharges</t>
+          <t>Invoice total amount incl. VAT</t>
         </is>
       </c>
       <c r="C250" s="22" t="inlineStr">
@@ -8917,36 +8889,32 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="D250" s="27" t="inlineStr">
-        <is>
-          <t>Conditional</t>
+      <c r="D250" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="E250" s="22" t="inlineStr">
         <is>
-          <t>0..1</t>
+          <t>1..1</t>
         </is>
       </c>
       <c r="F250" s="22" t="inlineStr">
         <is>
-          <t>EN 16931</t>
-        </is>
-      </c>
-      <c r="G250" s="22" t="inlineStr">
-        <is>
-          <t>0.00 if absent</t>
-        </is>
-      </c>
+          <t>MINIMUM</t>
+        </is>
+      </c>
+      <c r="G250" s="22" t="inlineStr"/>
     </row>
     <row r="251" ht="16" customHeight="1">
       <c r="A251" s="21" t="inlineStr">
         <is>
-          <t>ram:AllowanceTotalAmount</t>
+          <t>ram:TotalPrepaidAmount</t>
         </is>
       </c>
       <c r="B251" s="22" t="inlineStr">
         <is>
-          <t>Sum of document-level discounts</t>
+          <t>Amount already paid (prepayment)</t>
         </is>
       </c>
       <c r="C251" s="22" t="inlineStr">
@@ -8954,9 +8922,9 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="D251" s="27" t="inlineStr">
-        <is>
-          <t>Conditional</t>
+      <c r="D251" s="24" t="inlineStr">
+        <is>
+          <t>Optional</t>
         </is>
       </c>
       <c r="E251" s="22" t="inlineStr">
@@ -8966,24 +8934,20 @@
       </c>
       <c r="F251" s="22" t="inlineStr">
         <is>
-          <t>EN 16931</t>
-        </is>
-      </c>
-      <c r="G251" s="22" t="inlineStr">
-        <is>
-          <t>0.00 if absent</t>
-        </is>
-      </c>
+          <t>BASIC WL</t>
+        </is>
+      </c>
+      <c r="G251" s="22" t="inlineStr"/>
     </row>
     <row r="252" ht="16" customHeight="1">
       <c r="A252" s="21" t="inlineStr">
         <is>
-          <t>ram:TaxBasisTotalAmount</t>
+          <t>ram:RoundingAmount</t>
         </is>
       </c>
       <c r="B252" s="22" t="inlineStr">
         <is>
-          <t>Invoice total amount excl. VAT</t>
+          <t>Rounding amount</t>
         </is>
       </c>
       <c r="C252" s="22" t="inlineStr">
@@ -8991,19 +8955,19 @@
           <t>Decimal</t>
         </is>
       </c>
-      <c r="D252" s="23" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
+      <c r="D252" s="24" t="inlineStr">
+        <is>
+          <t>Optional</t>
         </is>
       </c>
       <c r="E252" s="22" t="inlineStr">
         <is>
-          <t>1..1</t>
+          <t>0..1</t>
         </is>
       </c>
       <c r="F252" s="22" t="inlineStr">
         <is>
-          <t>MINIMUM</t>
+          <t>EN 16931</t>
         </is>
       </c>
       <c r="G252" s="22" t="inlineStr"/>
@@ -9011,12 +8975,12 @@
     <row r="253" ht="16" customHeight="1">
       <c r="A253" s="21" t="inlineStr">
         <is>
-          <t>ram:TaxTotalAmount @currencyID</t>
+          <t>ram:DuePayableAmount</t>
         </is>
       </c>
       <c r="B253" s="22" t="inlineStr">
         <is>
-          <t>Total VAT amount</t>
+          <t>Amount due for payment</t>
         </is>
       </c>
       <c r="C253" s="22" t="inlineStr">
@@ -9039,74 +9003,73 @@
           <t>MINIMUM</t>
         </is>
       </c>
-      <c r="G253" s="22" t="inlineStr">
-        <is>
-          <t>currencyID = invoice currency</t>
-        </is>
+      <c r="G253" s="22">
+        <f> GrandTotal – Prepayments</f>
+        <v/>
       </c>
     </row>
     <row r="254" ht="16" customHeight="1">
-      <c r="A254" s="21" t="inlineStr">
-        <is>
-          <t>ram:GrandTotalAmount</t>
-        </is>
-      </c>
-      <c r="B254" s="22" t="inlineStr">
-        <is>
-          <t>Invoice total amount incl. VAT</t>
-        </is>
-      </c>
-      <c r="C254" s="22" t="inlineStr">
-        <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="D254" s="23" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="E254" s="22" t="inlineStr">
-        <is>
-          <t>1..1</t>
-        </is>
-      </c>
-      <c r="F254" s="22" t="inlineStr">
-        <is>
-          <t>MINIMUM</t>
-        </is>
-      </c>
-      <c r="G254" s="22" t="inlineStr"/>
+      <c r="A254" s="10" t="inlineStr">
+        <is>
+          <t>ram:InvoiceReferencedDocument</t>
+        </is>
+      </c>
+      <c r="B254" s="11" t="inlineStr">
+        <is>
+          <t>Preceding invoice reference (credit note)</t>
+        </is>
+      </c>
+      <c r="C254" s="11" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="D254" s="12" t="inlineStr">
+        <is>
+          <t>Conditional</t>
+        </is>
+      </c>
+      <c r="E254" s="11" t="inlineStr">
+        <is>
+          <t>0..n</t>
+        </is>
+      </c>
+      <c r="F254" s="11" t="inlineStr">
+        <is>
+          <t>EN 16931</t>
+        </is>
+      </c>
+      <c r="G254" s="11" t="inlineStr"/>
     </row>
     <row r="255" ht="16" customHeight="1">
       <c r="A255" s="21" t="inlineStr">
         <is>
-          <t>ram:TotalPrepaidAmount</t>
+          <t>ram:IssuerAssignedID</t>
         </is>
       </c>
       <c r="B255" s="22" t="inlineStr">
         <is>
-          <t>Amount already paid (prepayment)</t>
+          <t>Preceding invoice number</t>
         </is>
       </c>
       <c r="C255" s="22" t="inlineStr">
         <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="D255" s="24" t="inlineStr">
-        <is>
-          <t>Optional</t>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D255" s="23" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="E255" s="22" t="inlineStr">
         <is>
-          <t>0..1</t>
+          <t>1..1</t>
         </is>
       </c>
       <c r="F255" s="22" t="inlineStr">
         <is>
-          <t>BASIC WL</t>
+          <t>EN 16931</t>
         </is>
       </c>
       <c r="G255" s="22" t="inlineStr"/>
@@ -9114,17 +9077,17 @@
     <row r="256" ht="16" customHeight="1">
       <c r="A256" s="21" t="inlineStr">
         <is>
-          <t>ram:RoundingAmount</t>
+          <t>ram:FormattedIssueDateTime</t>
         </is>
       </c>
       <c r="B256" s="22" t="inlineStr">
         <is>
-          <t>Rounding amount</t>
+          <t>Preceding invoice date</t>
         </is>
       </c>
       <c r="C256" s="22" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>Complex</t>
         </is>
       </c>
       <c r="D256" s="24" t="inlineStr">
@@ -9145,19 +9108,19 @@
       <c r="G256" s="22" t="inlineStr"/>
     </row>
     <row r="257" ht="16" customHeight="1">
-      <c r="A257" s="21" t="inlineStr">
-        <is>
-          <t>ram:DuePayableAmount</t>
+      <c r="A257" s="25" t="inlineStr">
+        <is>
+          <t>qdt:DateTimeString @format="102"</t>
         </is>
       </c>
       <c r="B257" s="22" t="inlineStr">
         <is>
-          <t>Amount due for payment</t>
+          <t>Preceding invoice date</t>
         </is>
       </c>
       <c r="C257" s="22" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D257" s="23" t="inlineStr">
@@ -9172,23 +9135,20 @@
       </c>
       <c r="F257" s="22" t="inlineStr">
         <is>
-          <t>MINIMUM</t>
-        </is>
-      </c>
-      <c r="G257" s="22">
-        <f> GrandTotal – Prepayments</f>
-        <v/>
-      </c>
+          <t>EN 16931</t>
+        </is>
+      </c>
+      <c r="G257" s="22" t="inlineStr"/>
     </row>
     <row r="258" ht="16" customHeight="1">
       <c r="A258" s="10" t="inlineStr">
         <is>
-          <t>ram:InvoiceReferencedDocument</t>
+          <t>ram:ReceivableSpecifiedTradeAccountingAccount</t>
         </is>
       </c>
       <c r="B258" s="11" t="inlineStr">
         <is>
-          <t>Preceding invoice reference (credit note)</t>
+          <t>Buyer accounting reference</t>
         </is>
       </c>
       <c r="C258" s="11" t="inlineStr">
@@ -9196,19 +9156,19 @@
           <t>Complex</t>
         </is>
       </c>
-      <c r="D258" s="12" t="inlineStr">
-        <is>
-          <t>Conditional</t>
+      <c r="D258" s="19" t="inlineStr">
+        <is>
+          <t>Optional</t>
         </is>
       </c>
       <c r="E258" s="11" t="inlineStr">
         <is>
-          <t>0..n</t>
+          <t>0..1</t>
         </is>
       </c>
       <c r="F258" s="11" t="inlineStr">
         <is>
-          <t>EN 16931</t>
+          <t>EXTENDED</t>
         </is>
       </c>
       <c r="G258" s="11" t="inlineStr"/>
@@ -9216,12 +9176,12 @@
     <row r="259" ht="16" customHeight="1">
       <c r="A259" s="21" t="inlineStr">
         <is>
-          <t>ram:IssuerAssignedID</t>
+          <t>ram:ID</t>
         </is>
       </c>
       <c r="B259" s="22" t="inlineStr">
         <is>
-          <t>Preceding invoice number</t>
+          <t>Buyer accounting reference number</t>
         </is>
       </c>
       <c r="C259" s="22" t="inlineStr">
@@ -9241,7 +9201,7 @@
       </c>
       <c r="F259" s="22" t="inlineStr">
         <is>
-          <t>EN 16931</t>
+          <t>EXTENDED</t>
         </is>
       </c>
       <c r="G259" s="22" t="inlineStr"/>
@@ -9249,17 +9209,17 @@
     <row r="260" ht="16" customHeight="1">
       <c r="A260" s="21" t="inlineStr">
         <is>
-          <t>ram:FormattedIssueDateTime</t>
+          <t>ram:TypeCode</t>
         </is>
       </c>
       <c r="B260" s="22" t="inlineStr">
         <is>
-          <t>Preceding invoice date</t>
+          <t>Account type code (e.g. 1=general)</t>
         </is>
       </c>
       <c r="C260" s="22" t="inlineStr">
         <is>
-          <t>Complex</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="D260" s="24" t="inlineStr">
@@ -9274,151 +9234,23 @@
       </c>
       <c r="F260" s="22" t="inlineStr">
         <is>
-          <t>EN 16931</t>
+          <t>EXTENDED</t>
         </is>
       </c>
       <c r="G260" s="22" t="inlineStr"/>
     </row>
-    <row r="261" ht="16" customHeight="1">
-      <c r="A261" s="25" t="inlineStr">
-        <is>
-          <t>qdt:DateTimeString @format="102"</t>
-        </is>
-      </c>
-      <c r="B261" s="22" t="inlineStr">
-        <is>
-          <t>Preceding invoice date</t>
-        </is>
-      </c>
-      <c r="C261" s="22" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D261" s="23" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="E261" s="22" t="inlineStr">
-        <is>
-          <t>1..1</t>
-        </is>
-      </c>
-      <c r="F261" s="22" t="inlineStr">
-        <is>
-          <t>EN 16931</t>
-        </is>
-      </c>
-      <c r="G261" s="22" t="inlineStr"/>
-    </row>
-    <row r="262" ht="16" customHeight="1">
-      <c r="A262" s="10" t="inlineStr">
-        <is>
-          <t>ram:ReceivableSpecifiedTradeAccountingAccount</t>
-        </is>
-      </c>
-      <c r="B262" s="11" t="inlineStr">
-        <is>
-          <t>Buyer accounting reference</t>
-        </is>
-      </c>
-      <c r="C262" s="11" t="inlineStr">
-        <is>
-          <t>Complex</t>
-        </is>
-      </c>
-      <c r="D262" s="19" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="E262" s="11" t="inlineStr">
-        <is>
-          <t>0..1</t>
-        </is>
-      </c>
-      <c r="F262" s="11" t="inlineStr">
-        <is>
-          <t>EXTENDED</t>
-        </is>
-      </c>
-      <c r="G262" s="11" t="inlineStr"/>
-    </row>
-    <row r="263" ht="16" customHeight="1">
-      <c r="A263" s="21" t="inlineStr">
-        <is>
-          <t>ram:ID</t>
-        </is>
-      </c>
-      <c r="B263" s="22" t="inlineStr">
-        <is>
-          <t>Buyer accounting reference number</t>
-        </is>
-      </c>
-      <c r="C263" s="22" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="D263" s="23" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
-        </is>
-      </c>
-      <c r="E263" s="22" t="inlineStr">
-        <is>
-          <t>1..1</t>
-        </is>
-      </c>
-      <c r="F263" s="22" t="inlineStr">
-        <is>
-          <t>EXTENDED</t>
-        </is>
-      </c>
-      <c r="G263" s="22" t="inlineStr"/>
-    </row>
-    <row r="264" ht="16" customHeight="1">
-      <c r="A264" s="21" t="inlineStr">
-        <is>
-          <t>ram:TypeCode</t>
-        </is>
-      </c>
-      <c r="B264" s="22" t="inlineStr">
-        <is>
-          <t>Account type code (e.g. 1=general)</t>
-        </is>
-      </c>
-      <c r="C264" s="22" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="D264" s="24" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="E264" s="22" t="inlineStr">
-        <is>
-          <t>0..1</t>
-        </is>
-      </c>
-      <c r="F264" s="22" t="inlineStr">
-        <is>
-          <t>EXTENDED</t>
-        </is>
-      </c>
-      <c r="G264" s="22" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:G264"/>
-  <mergeCells count="6">
+  <autoFilter ref="A2:G260"/>
+  <mergeCells count="10">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A17:G17"/>
     <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A31:G31"/>
     <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A176:G176"/>
+    <mergeCell ref="A156:G156"/>
     <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A81:G81"/>
     <mergeCell ref="A11:G11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9802,7 +9634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -9934,11 +9766,7 @@
           <t>Self-billed invoice</t>
         </is>
       </c>
-      <c r="D8" s="35" t="inlineStr">
-        <is>
-          <t>Autofacturation</t>
-        </is>
-      </c>
+      <c r="D8" s="35" t="inlineStr"/>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="36" t="inlineStr"/>
@@ -9989,7 +9817,7 @@
       </c>
       <c r="C11" s="36" t="inlineStr">
         <is>
-          <t>Zero rated goods/services</t>
+          <t>Zero rated</t>
         </is>
       </c>
       <c r="D11" s="36" t="inlineStr">
@@ -10021,7 +9849,7 @@
       </c>
       <c r="C13" s="36" t="inlineStr">
         <is>
-          <t>Reverse charge (VAT)</t>
+          <t>Reverse charge</t>
         </is>
       </c>
       <c r="D13" s="36" t="inlineStr">
@@ -10472,31 +10300,35 @@
       <c r="A43" s="36" t="inlineStr"/>
       <c r="B43" s="36" t="inlineStr">
         <is>
-          <t>0192</t>
+          <t>9930</t>
         </is>
       </c>
       <c r="C43" s="36" t="inlineStr">
         <is>
-          <t>PEPPOL ID NL</t>
-        </is>
-      </c>
-      <c r="D43" s="36" t="inlineStr"/>
+          <t>VAT number (EU)</t>
+        </is>
+      </c>
+      <c r="D43" s="36" t="inlineStr">
+        <is>
+          <t>Country prefix + number</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" s="35" t="inlineStr"/>
       <c r="B44" s="35" t="inlineStr">
         <is>
-          <t>9930</t>
+          <t>9957</t>
         </is>
       </c>
       <c r="C44" s="35" t="inlineStr">
         <is>
-          <t>VAT number (EU)</t>
+          <t>French VAT number</t>
         </is>
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>Country prefix + number</t>
+          <t>FRxxxxxxxxxxxxxxx</t>
         </is>
       </c>
     </row>
@@ -10504,66 +10336,62 @@
       <c r="A45" s="36" t="inlineStr"/>
       <c r="B45" s="36" t="inlineStr">
         <is>
-          <t>9957</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="C45" s="36" t="inlineStr">
         <is>
-          <t>French VAT number</t>
+          <t>Email address</t>
         </is>
       </c>
       <c r="D45" s="36" t="inlineStr">
         <is>
-          <t>FRxxxxxxxxxxxxxxx</t>
+          <t>For URIUniversalCommunication</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="35" t="inlineStr"/>
-      <c r="B46" s="35" t="inlineStr">
-        <is>
-          <t>EM</t>
-        </is>
-      </c>
-      <c r="C46" s="35" t="inlineStr">
-        <is>
-          <t>Email address</t>
-        </is>
-      </c>
-      <c r="D46" s="35" t="inlineStr">
-        <is>
-          <t>For URIUniversalCommunication</t>
-        </is>
-      </c>
+      <c r="A46" s="34" t="inlineStr">
+        <is>
+          <t>unitCode (UN/ECE Rec 20 – examples)</t>
+        </is>
+      </c>
+      <c r="B46" s="34" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+      <c r="C46" s="34" t="inlineStr">
+        <is>
+          <t>Unit / piece</t>
+        </is>
+      </c>
+      <c r="D46" s="34" t="inlineStr"/>
     </row>
     <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="34" t="inlineStr">
-        <is>
-          <t>unitCode (UN/ECE Rec 20 – examples)</t>
-        </is>
-      </c>
-      <c r="B47" s="34" t="inlineStr">
-        <is>
-          <t>C62</t>
-        </is>
-      </c>
-      <c r="C47" s="34" t="inlineStr">
-        <is>
-          <t>Unit / piece</t>
-        </is>
-      </c>
-      <c r="D47" s="34" t="inlineStr"/>
+      <c r="A47" s="36" t="inlineStr"/>
+      <c r="B47" s="36" t="inlineStr">
+        <is>
+          <t>HUR</t>
+        </is>
+      </c>
+      <c r="C47" s="36" t="inlineStr">
+        <is>
+          <t>Hour</t>
+        </is>
+      </c>
+      <c r="D47" s="36" t="inlineStr"/>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" s="35" t="inlineStr"/>
       <c r="B48" s="35" t="inlineStr">
         <is>
-          <t>HUR</t>
+          <t>DAY</t>
         </is>
       </c>
       <c r="C48" s="35" t="inlineStr">
         <is>
-          <t>Hour</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="D48" s="35" t="inlineStr"/>
@@ -10572,12 +10400,12 @@
       <c r="A49" s="36" t="inlineStr"/>
       <c r="B49" s="36" t="inlineStr">
         <is>
-          <t>DAY</t>
+          <t>WEE</t>
         </is>
       </c>
       <c r="C49" s="36" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Week</t>
         </is>
       </c>
       <c r="D49" s="36" t="inlineStr"/>
@@ -10586,12 +10414,12 @@
       <c r="A50" s="35" t="inlineStr"/>
       <c r="B50" s="35" t="inlineStr">
         <is>
-          <t>WEE</t>
+          <t>MON</t>
         </is>
       </c>
       <c r="C50" s="35" t="inlineStr">
         <is>
-          <t>Week</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="D50" s="35" t="inlineStr"/>
@@ -10600,12 +10428,12 @@
       <c r="A51" s="36" t="inlineStr"/>
       <c r="B51" s="36" t="inlineStr">
         <is>
-          <t>MON</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="C51" s="36" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="D51" s="36" t="inlineStr"/>
@@ -10614,12 +10442,12 @@
       <c r="A52" s="35" t="inlineStr"/>
       <c r="B52" s="35" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>KGM</t>
         </is>
       </c>
       <c r="C52" s="35" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>Kilogram</t>
         </is>
       </c>
       <c r="D52" s="35" t="inlineStr"/>
@@ -10628,12 +10456,12 @@
       <c r="A53" s="36" t="inlineStr"/>
       <c r="B53" s="36" t="inlineStr">
         <is>
-          <t>KGM</t>
+          <t>GRM</t>
         </is>
       </c>
       <c r="C53" s="36" t="inlineStr">
         <is>
-          <t>Kilogram</t>
+          <t>Gram</t>
         </is>
       </c>
       <c r="D53" s="36" t="inlineStr"/>
@@ -10642,12 +10470,12 @@
       <c r="A54" s="35" t="inlineStr"/>
       <c r="B54" s="35" t="inlineStr">
         <is>
-          <t>GRM</t>
+          <t>LTR</t>
         </is>
       </c>
       <c r="C54" s="35" t="inlineStr">
         <is>
-          <t>Gram</t>
+          <t>Litre</t>
         </is>
       </c>
       <c r="D54" s="35" t="inlineStr"/>
@@ -10656,12 +10484,12 @@
       <c r="A55" s="36" t="inlineStr"/>
       <c r="B55" s="36" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>MTR</t>
         </is>
       </c>
       <c r="C55" s="36" t="inlineStr">
         <is>
-          <t>Litre</t>
+          <t>Metre</t>
         </is>
       </c>
       <c r="D55" s="36" t="inlineStr"/>
@@ -10670,12 +10498,12 @@
       <c r="A56" s="35" t="inlineStr"/>
       <c r="B56" s="35" t="inlineStr">
         <is>
-          <t>MTR</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="C56" s="35" t="inlineStr">
         <is>
-          <t>Metre</t>
+          <t>Square metre</t>
         </is>
       </c>
       <c r="D56" s="35" t="inlineStr"/>
@@ -10684,12 +10512,12 @@
       <c r="A57" s="36" t="inlineStr"/>
       <c r="B57" s="36" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>MTQ</t>
         </is>
       </c>
       <c r="C57" s="36" t="inlineStr">
         <is>
-          <t>Square metre</t>
+          <t>Cubic metre</t>
         </is>
       </c>
       <c r="D57" s="36" t="inlineStr"/>
@@ -10698,12 +10526,12 @@
       <c r="A58" s="35" t="inlineStr"/>
       <c r="B58" s="35" t="inlineStr">
         <is>
-          <t>MTQ</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="C58" s="35" t="inlineStr">
         <is>
-          <t>Cubic metre</t>
+          <t>Set / kit</t>
         </is>
       </c>
       <c r="D58" s="35" t="inlineStr"/>
@@ -10712,32 +10540,18 @@
       <c r="A59" s="36" t="inlineStr"/>
       <c r="B59" s="36" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>TNE</t>
         </is>
       </c>
       <c r="C59" s="36" t="inlineStr">
         <is>
-          <t>Set / kit</t>
+          <t>Tonne</t>
         </is>
       </c>
       <c r="D59" s="36" t="inlineStr"/>
     </row>
-    <row r="60" ht="15" customHeight="1">
-      <c r="A60" s="35" t="inlineStr"/>
-      <c r="B60" s="35" t="inlineStr">
-        <is>
-          <t>TNE</t>
-        </is>
-      </c>
-      <c r="C60" s="35" t="inlineStr">
-        <is>
-          <t>Tonne</t>
-        </is>
-      </c>
-      <c r="D60" s="35" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:D60"/>
+  <autoFilter ref="A2:D59"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -10751,16 +10565,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A84"/>
+  <dimension ref="A1:A476"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
+    <col width="130" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="37" t="inlineStr">
         <is>
-          <t>XML skeleton example – MINIMUM profile (mandatory tags annotated)</t>
+          <t>XML skeleton example – EXTENDED profile (all tags annotated)</t>
         </is>
       </c>
     </row>
@@ -10774,35 +10588,35 @@
     <row r="3" ht="14" customHeight="1">
       <c r="A3" s="39" t="inlineStr">
         <is>
-          <t>&lt;!-- ╔══════════════════════════════════════════════════════════════╗ --&gt;</t>
+          <t>&lt;!-- ╔════════════════════════════════════════════════════════════════════════╗ --&gt;</t>
         </is>
       </c>
     </row>
     <row r="4" ht="14" customHeight="1">
       <c r="A4" s="39" t="inlineStr">
         <is>
-          <t>&lt;!-- ║  FACTUR-X / ZugFERD – MINIMUM Profile                       ║ --&gt;</t>
+          <t>&lt;!-- ║  FACTUR-X / ZugFERD – EXTENDED Profile – Fully annotated example     ║ --&gt;</t>
         </is>
       </c>
     </row>
     <row r="5" ht="14" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>&lt;!-- ║  Tags marked (M)=Mandatory  (O)=Optional                    ║ --&gt;</t>
+          <t>&lt;!-- ║  (M)=Mandatory  (O)=Optional  (C)=Conditional                        ║ --&gt;</t>
         </is>
       </c>
     </row>
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="39" t="inlineStr">
         <is>
-          <t>&lt;!-- ╚══════════════════════════════════════════════════════════════╝ --&gt;</t>
+          <t>&lt;!-- ╚════════════════════════════════════════════════════════════════════════╝ --&gt;</t>
         </is>
       </c>
     </row>
     <row r="7" ht="14" customHeight="1">
-      <c r="A7" s="39" t="inlineStr">
-        <is>
-          <t>&lt;rsm:CrossIndustryInvoice                                &lt;!-- ROOT (M) --&gt;</t>
+      <c r="A7" s="38" t="inlineStr">
+        <is>
+          <t>&lt;rsm:CrossIndustryInvoice</t>
         </is>
       </c>
     </row>
@@ -10847,455 +10661,3127 @@
     <row r="14" ht="14" customHeight="1">
       <c r="A14" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">  &lt;!-- ── Profile context ────────────────────────────────────────── --&gt;</t>
+          <t xml:space="preserve">  &lt;!-- ╔══════════════════════════════════════════════╗ --&gt;</t>
         </is>
       </c>
     </row>
     <row r="15" ht="14" customHeight="1">
       <c r="A15" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">  &lt;rsm:ExchangedDocumentContext&gt;                         &lt;!-- (M) --&gt;</t>
+          <t xml:space="preserve">  &lt;!-- ║  1. PROFILE CONTEXT                          ║ --&gt;</t>
         </is>
       </c>
     </row>
     <row r="16" ht="14" customHeight="1">
       <c r="A16" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    &lt;ram:GuidelineSpecifiedDocumentContextParameter&gt;     &lt;!-- (M) --&gt;</t>
+          <t xml:space="preserve">  &lt;!-- ╚══════════════════════════════════════════════╝ --&gt;</t>
         </is>
       </c>
     </row>
     <row r="17" ht="14" customHeight="1">
       <c r="A17" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">      &lt;ram:ID&gt;urn:factur-x.eu:1p0:minimum&lt;/ram:ID&gt;       &lt;!-- (M) --&gt;</t>
+          <t xml:space="preserve">  &lt;rsm:ExchangedDocumentContext&gt;                         &lt;!-- (M) --&gt;</t>
         </is>
       </c>
     </row>
     <row r="18" ht="14" customHeight="1">
-      <c r="A18" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    &lt;/ram:GuidelineSpecifiedDocumentContextParameter&gt;</t>
+      <c r="A18" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    &lt;ram:BusinessProcessSpecifiedDocumentContextParameter&gt;  &lt;!-- (O) --&gt;</t>
         </is>
       </c>
     </row>
     <row r="19" ht="14" customHeight="1">
       <c r="A19" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">  &lt;/rsm:ExchangedDocumentContext&gt;</t>
+          <t xml:space="preserve">      &lt;ram:ID&gt;urn:fdc:peppol.eu:2017:poacc:billing:01:1.0&lt;/ram:ID&gt;</t>
         </is>
       </c>
     </row>
     <row r="20" ht="14" customHeight="1">
-      <c r="A20" s="38" t="inlineStr"/>
+      <c r="A20" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    &lt;/ram:BusinessProcessSpecifiedDocumentContextParameter&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="14" customHeight="1">
       <c r="A21" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">  &lt;!-- ── Document header ───────────────────────────────────────── --&gt;</t>
+          <t xml:space="preserve">    &lt;ram:GuidelineSpecifiedDocumentContextParameter&gt;     &lt;!-- (M) --&gt;</t>
         </is>
       </c>
     </row>
     <row r="22" ht="14" customHeight="1">
       <c r="A22" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">  &lt;rsm:ExchangedDocument&gt;                                &lt;!-- (M) --&gt;</t>
+          <t xml:space="preserve">      &lt;ram:ID&gt;urn:factur-x.eu:1p0:extended&lt;/ram:ID&gt;      &lt;!-- (M) EXTENDED profile --&gt;</t>
         </is>
       </c>
     </row>
     <row r="23" ht="14" customHeight="1">
-      <c r="A23" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    &lt;ram:ID&gt;INV-2024-00123&lt;/ram:ID&gt;                       &lt;!-- (M) Invoice number --&gt;</t>
+      <c r="A23" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    &lt;/ram:GuidelineSpecifiedDocumentContextParameter&gt;</t>
         </is>
       </c>
     </row>
     <row r="24" ht="14" customHeight="1">
-      <c r="A24" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    &lt;ram:TypeCode&gt;380&lt;/ram:TypeCode&gt;                      &lt;!-- (M) 380=Invoice --&gt;</t>
+      <c r="A24" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  &lt;/rsm:ExchangedDocumentContext&gt;</t>
         </is>
       </c>
     </row>
     <row r="25" ht="14" customHeight="1">
-      <c r="A25" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    &lt;ram:IssueDateTime&gt;                                  &lt;!-- (M) --&gt;</t>
-        </is>
-      </c>
+      <c r="A25" s="38" t="inlineStr"/>
     </row>
     <row r="26" ht="14" customHeight="1">
       <c r="A26" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">      &lt;udt:DateTimeString format="102"&gt;20240315&lt;/udt:DateTimeString&gt;  &lt;!-- (M) YYYYMMDD --&gt;</t>
+          <t xml:space="preserve">  &lt;!-- ╔══════════════════════════════════════════════╗ --&gt;</t>
         </is>
       </c>
     </row>
     <row r="27" ht="14" customHeight="1">
-      <c r="A27" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    &lt;/ram:IssueDateTime&gt;</t>
+      <c r="A27" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  &lt;!-- ║  2. DOCUMENT HEADER                          ║ --&gt;</t>
         </is>
       </c>
     </row>
     <row r="28" ht="14" customHeight="1">
-      <c r="A28" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  &lt;/rsm:ExchangedDocument&gt;</t>
+      <c r="A28" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  &lt;!-- ╚══════════════════════════════════════════════╝ --&gt;</t>
         </is>
       </c>
     </row>
     <row r="29" ht="14" customHeight="1">
-      <c r="A29" s="38" t="inlineStr"/>
+      <c r="A29" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  &lt;rsm:ExchangedDocument&gt;                                &lt;!-- (M) --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="14" customHeight="1">
       <c r="A30" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">  &lt;!-- ── Trade transaction ─────────────────────────────────────── --&gt;</t>
+          <t xml:space="preserve">    &lt;ram:ID&gt;INV-2024-00789&lt;/ram:ID&gt;                       &lt;!-- (M) Invoice number --&gt;</t>
         </is>
       </c>
     </row>
     <row r="31" ht="14" customHeight="1">
       <c r="A31" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">  &lt;rsm:SupplyChainTradeTransaction&gt;                      &lt;!-- (M) --&gt;</t>
+          <t xml:space="preserve">    &lt;ram:Name&gt;INVOICE&lt;/ram:Name&gt;                          &lt;!-- (O) EXTENDED only --&gt;</t>
         </is>
       </c>
     </row>
     <row r="32" ht="14" customHeight="1">
-      <c r="A32" s="38" t="inlineStr"/>
+      <c r="A32" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    &lt;ram:TypeCode&gt;380&lt;/ram:TypeCode&gt;                      &lt;!-- (M) 380=Invoice --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="14" customHeight="1">
       <c r="A33" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    &lt;!-- Trade agreement --&gt;</t>
+          <t xml:space="preserve">    &lt;ram:IssueDateTime&gt;                                  &lt;!-- (M) --&gt;</t>
         </is>
       </c>
     </row>
     <row r="34" ht="14" customHeight="1">
-      <c r="A34" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    &lt;ram:ApplicableHeaderTradeAgreement&gt;                 &lt;!-- (M) --&gt;</t>
+      <c r="A34" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;udt:DateTimeString format="102"&gt;20240315&lt;/udt:DateTimeString&gt;</t>
         </is>
       </c>
     </row>
     <row r="35" ht="14" customHeight="1">
-      <c r="A35" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      &lt;ram:BuyerReference&gt;DEPT-PURCHASING-42&lt;/ram:BuyerReference&gt;  &lt;!-- (M) MINIMUM --&gt;</t>
+      <c r="A35" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    &lt;/ram:IssueDateTime&gt;</t>
         </is>
       </c>
     </row>
     <row r="36" ht="14" customHeight="1">
-      <c r="A36" s="38" t="inlineStr"/>
+      <c r="A36" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    &lt;ram:CopyIndicator&gt;false&lt;/ram:CopyIndicator&gt;          &lt;!-- (O) EXTENDED --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="14" customHeight="1">
       <c r="A37" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">      &lt;!-- Seller --&gt;</t>
+          <t xml:space="preserve">    &lt;ram:LanguageID&gt;en&lt;/ram:LanguageID&gt;                   &lt;!-- (O) EXTENDED --&gt;</t>
         </is>
       </c>
     </row>
     <row r="38" ht="14" customHeight="1">
       <c r="A38" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">      &lt;ram:SellerTradeParty&gt;                             &lt;!-- (M) --&gt;</t>
+          <t xml:space="preserve">    &lt;!-- General note --&gt;</t>
         </is>
       </c>
     </row>
     <row r="39" ht="14" customHeight="1">
       <c r="A39" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">        &lt;ram:Name&gt;ACME Ltd&lt;/ram:Name&gt;                   &lt;!-- (M) --&gt;</t>
+          <t xml:space="preserve">    &lt;ram:IncludedNote&gt;                                   &lt;!-- (O) from BASIC onwards --&gt;</t>
         </is>
       </c>
     </row>
     <row r="40" ht="14" customHeight="1">
-      <c r="A40" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        &lt;ram:PostalTradeAddress&gt;                         &lt;!-- (M) --&gt;</t>
+      <c r="A40" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:Content&gt;Payment by SEPA credit transfer within 30 days.&lt;/ram:Content&gt;</t>
         </is>
       </c>
     </row>
     <row r="41" ht="14" customHeight="1">
-      <c r="A41" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          &lt;ram:CountryID&gt;GB&lt;/ram:CountryID&gt;              &lt;!-- (M) --&gt;</t>
+      <c r="A41" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:SubjectCode&gt;AAI&lt;/ram:SubjectCode&gt;</t>
         </is>
       </c>
     </row>
     <row r="42" ht="14" customHeight="1">
       <c r="A42" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">        &lt;/ram:PostalTradeAddress&gt;</t>
+          <t xml:space="preserve">    &lt;/ram:IncludedNote&gt;</t>
         </is>
       </c>
     </row>
     <row r="43" ht="14" customHeight="1">
       <c r="A43" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">        &lt;ram:SpecifiedTaxRegistration&gt;                   &lt;!-- (M) --&gt;</t>
+          <t xml:space="preserve">    &lt;!-- Regulatory note --&gt;</t>
         </is>
       </c>
     </row>
     <row r="44" ht="14" customHeight="1">
-      <c r="A44" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          &lt;ram:ID schemeID="VA"&gt;GB123456789&lt;/ram:ID&gt;     &lt;!-- (M) VAT number --&gt;</t>
+      <c r="A44" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    &lt;ram:IncludedNote&gt;</t>
         </is>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1">
       <c r="A45" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">        &lt;/ram:SpecifiedTaxRegistration&gt;</t>
+          <t xml:space="preserve">      &lt;ram:Content&gt;VAT reverse charge applies – customer to account for VAT.&lt;/ram:Content&gt;</t>
         </is>
       </c>
     </row>
     <row r="46" ht="14" customHeight="1">
       <c r="A46" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">      &lt;/ram:SellerTradeParty&gt;</t>
+          <t xml:space="preserve">      &lt;ram:SubjectCode&gt;REG&lt;/ram:SubjectCode&gt;</t>
         </is>
       </c>
     </row>
     <row r="47" ht="14" customHeight="1">
-      <c r="A47" s="38" t="inlineStr"/>
+      <c r="A47" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    &lt;/ram:IncludedNote&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="14" customHeight="1">
-      <c r="A48" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      &lt;!-- Buyer --&gt;</t>
+      <c r="A48" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  &lt;/rsm:ExchangedDocument&gt;</t>
         </is>
       </c>
     </row>
     <row r="49" ht="14" customHeight="1">
-      <c r="A49" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      &lt;ram:BuyerTradeParty&gt;                              &lt;!-- (M) --&gt;</t>
-        </is>
-      </c>
+      <c r="A49" s="38" t="inlineStr"/>
     </row>
     <row r="50" ht="14" customHeight="1">
       <c r="A50" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">        &lt;ram:Name&gt;CLIENT Corp&lt;/ram:Name&gt;                &lt;!-- (M) --&gt;</t>
+          <t xml:space="preserve">  &lt;!-- ╔══════════════════════════════════════════════╗ --&gt;</t>
         </is>
       </c>
     </row>
     <row r="51" ht="14" customHeight="1">
       <c r="A51" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">        &lt;ram:PostalTradeAddress&gt;                         &lt;!-- (M) --&gt;</t>
+          <t xml:space="preserve">  &lt;!-- ║  3. TRADE TRANSACTION                        ║ --&gt;</t>
         </is>
       </c>
     </row>
     <row r="52" ht="14" customHeight="1">
       <c r="A52" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">          &lt;ram:CountryID&gt;GB&lt;/ram:CountryID&gt;              &lt;!-- (M) --&gt;</t>
+          <t xml:space="preserve">  &lt;!-- ╚══════════════════════════════════════════════╝ --&gt;</t>
         </is>
       </c>
     </row>
     <row r="53" ht="14" customHeight="1">
       <c r="A53" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">        &lt;/ram:PostalTradeAddress&gt;</t>
+          <t xml:space="preserve">  &lt;rsm:SupplyChainTradeTransaction&gt;</t>
         </is>
       </c>
     </row>
     <row r="54" ht="14" customHeight="1">
-      <c r="A54" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      &lt;/ram:BuyerTradeParty&gt;</t>
-        </is>
-      </c>
+      <c r="A54" s="38" t="inlineStr"/>
     </row>
     <row r="55" ht="14" customHeight="1">
-      <c r="A55" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    &lt;/ram:ApplicableHeaderTradeAgreement&gt;</t>
+      <c r="A55" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    &lt;!-- ══════════════════════════════════════════════</t>
         </is>
       </c>
     </row>
     <row r="56" ht="14" customHeight="1">
-      <c r="A56" s="38" t="inlineStr"/>
+      <c r="A56" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         3a. INVOICE LINE ITEMS</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="14" customHeight="1">
-      <c r="A57" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    &lt;!-- Delivery (empty but mandatory in MINIMUM) --&gt;</t>
+      <c r="A57" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         ══════════════════════════════════════════ --&gt;</t>
         </is>
       </c>
     </row>
     <row r="58" ht="14" customHeight="1">
-      <c r="A58" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    &lt;ram:ApplicableHeaderTradeDelivery/&gt;                 &lt;!-- (M) --&gt;</t>
-        </is>
-      </c>
+      <c r="A58" s="38" t="inlineStr"/>
     </row>
     <row r="59" ht="14" customHeight="1">
-      <c r="A59" s="38" t="inlineStr"/>
+      <c r="A59" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    &lt;!-- ── Line 1: Consulting services ──────────── --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="14" customHeight="1">
-      <c r="A60" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    &lt;!-- Settlement --&gt;</t>
+      <c r="A60" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    &lt;ram:IncludedSupplyChainTradeLineItem&gt;</t>
         </is>
       </c>
     </row>
     <row r="61" ht="14" customHeight="1">
-      <c r="A61" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    &lt;ram:ApplicableHeaderTradeSettlement&gt;                &lt;!-- (M) --&gt;</t>
+      <c r="A61" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:AssociatedDocumentLineDocument&gt;</t>
         </is>
       </c>
     </row>
     <row r="62" ht="14" customHeight="1">
       <c r="A62" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">      &lt;ram:InvoiceCurrencyCode&gt;GBP&lt;/ram:InvoiceCurrencyCode&gt;  &lt;!-- (M) --&gt;</t>
+          <t xml:space="preserve">        &lt;ram:LineID&gt;1&lt;/ram:LineID&gt;                        &lt;!-- (M) Line number --&gt;</t>
         </is>
       </c>
     </row>
     <row r="63" ht="14" customHeight="1">
-      <c r="A63" s="38" t="inlineStr"/>
+      <c r="A63" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:IncludedNote&gt;                               &lt;!-- (O) EN 16931 --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="14" customHeight="1">
-      <c r="A64" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      &lt;!-- VAT breakdown per rate --&gt;</t>
+      <c r="A64" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:Content&gt;Services delivered 01/02 to 28/02/2024.&lt;/ram:Content&gt;</t>
         </is>
       </c>
     </row>
     <row r="65" ht="14" customHeight="1">
-      <c r="A65" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      &lt;ram:ApplicableTradeTax&gt;                           &lt;!-- (M) 1..n --&gt;</t>
+      <c r="A65" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:IncludedNote&gt;</t>
         </is>
       </c>
     </row>
     <row r="66" ht="14" customHeight="1">
-      <c r="A66" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        &lt;ram:CalculatedAmount&gt;200.00&lt;/ram:CalculatedAmount&gt;   &lt;!-- (M) --&gt;</t>
+      <c r="A66" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:AssociatedDocumentLineDocument&gt;</t>
         </is>
       </c>
     </row>
     <row r="67" ht="14" customHeight="1">
-      <c r="A67" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        &lt;ram:TypeCode&gt;VAT&lt;/ram:TypeCode&gt;                 &lt;!-- (M) --&gt;</t>
-        </is>
-      </c>
+      <c r="A67" s="38" t="inlineStr"/>
     </row>
     <row r="68" ht="14" customHeight="1">
-      <c r="A68" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        &lt;ram:BasisAmount&gt;1000.00&lt;/ram:BasisAmount&gt;       &lt;!-- (M) --&gt;</t>
+      <c r="A68" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:SpecifiedTradeProduct&gt;</t>
         </is>
       </c>
     </row>
     <row r="69" ht="14" customHeight="1">
       <c r="A69" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">        &lt;ram:CategoryCode&gt;S&lt;/ram:CategoryCode&gt;           &lt;!-- (M) --&gt;</t>
+          <t xml:space="preserve">        &lt;ram:GlobalID schemeID="0160"&gt;3701234567890&lt;/ram:GlobalID&gt;  &lt;!-- (O) GTIN --&gt;</t>
         </is>
       </c>
     </row>
     <row r="70" ht="14" customHeight="1">
       <c r="A70" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">        &lt;ram:RateApplicablePercent&gt;20.00&lt;/ram:RateApplicablePercent&gt;  &lt;!-- (M) --&gt;</t>
+          <t xml:space="preserve">        &lt;ram:SellerAssignedID&gt;REF-CONSULT-001&lt;/ram:SellerAssignedID&gt;  &lt;!-- (O) --&gt;</t>
         </is>
       </c>
     </row>
     <row r="71" ht="14" customHeight="1">
-      <c r="A71" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      &lt;/ram:ApplicableTradeTax&gt;</t>
+      <c r="A71" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:BuyerAssignedID&gt;BUY-SRV-42&lt;/ram:BuyerAssignedID&gt;         &lt;!-- (O) EXTENDED --&gt;</t>
         </is>
       </c>
     </row>
     <row r="72" ht="14" customHeight="1">
-      <c r="A72" s="38" t="inlineStr"/>
+      <c r="A72" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:Name&gt;Digital transformation consulting services&lt;/ram:Name&gt;  &lt;!-- (M) --&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="14" customHeight="1">
       <c r="A73" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">      &lt;!-- Monetary totals --&gt;</t>
+          <t xml:space="preserve">        &lt;ram:Description&gt;Strategic advisory – phase 1 current-state analysis.&lt;/ram:Description&gt;  &lt;!-- (O) EN 16931 --&gt;</t>
         </is>
       </c>
     </row>
     <row r="74" ht="14" customHeight="1">
       <c r="A74" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">      &lt;ram:SpecifiedTradeSettlementHeaderMonetarySummation&gt;   &lt;!-- (M) --&gt;</t>
+          <t xml:space="preserve">        &lt;ram:OriginTradeCountry&gt;                         &lt;!-- (O) EXTENDED --&gt;</t>
         </is>
       </c>
     </row>
     <row r="75" ht="14" customHeight="1">
-      <c r="A75" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        &lt;ram:LineTotalAmount&gt;1000.00&lt;/ram:LineTotalAmount&gt;    &lt;!-- (M) --&gt;</t>
+      <c r="A75" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:ID&gt;GB&lt;/ram:ID&gt;</t>
         </is>
       </c>
     </row>
     <row r="76" ht="14" customHeight="1">
-      <c r="A76" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        &lt;ram:TaxBasisTotalAmount&gt;1000.00&lt;/ram:TaxBasisTotalAmount&gt;   &lt;!-- (M) --&gt;</t>
+      <c r="A76" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:OriginTradeCountry&gt;</t>
         </is>
       </c>
     </row>
     <row r="77" ht="14" customHeight="1">
-      <c r="A77" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        &lt;ram:TaxTotalAmount currencyID="GBP"&gt;200.00&lt;/ram:TaxTotalAmount&gt;  &lt;!-- (M) --&gt;</t>
+      <c r="A77" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:SpecifiedTradeProduct&gt;</t>
         </is>
       </c>
     </row>
     <row r="78" ht="14" customHeight="1">
-      <c r="A78" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        &lt;ram:GrandTotalAmount&gt;1200.00&lt;/ram:GrandTotalAmount&gt;  &lt;!-- (M) --&gt;</t>
-        </is>
-      </c>
+      <c r="A78" s="38" t="inlineStr"/>
     </row>
     <row r="79" ht="14" customHeight="1">
-      <c r="A79" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        &lt;ram:DuePayableAmount&gt;1200.00&lt;/ram:DuePayableAmount&gt;  &lt;!-- (M) --&gt;</t>
+      <c r="A79" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:SpecifiedLineTradeAgreement&gt;</t>
         </is>
       </c>
     </row>
     <row r="80" ht="14" customHeight="1">
-      <c r="A80" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      &lt;/ram:SpecifiedTradeSettlementHeaderMonetarySummation&gt;</t>
+      <c r="A80" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:BuyerOrderReferencedDocument&gt;               &lt;!-- (O) EN 16931 --&gt;</t>
         </is>
       </c>
     </row>
     <row r="81" ht="14" customHeight="1">
       <c r="A81" s="38" t="inlineStr">
         <is>
+          <t xml:space="preserve">          &lt;ram:LineID&gt;5&lt;/ram:LineID&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="14" customHeight="1">
+      <c r="A82" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:BuyerOrderReferencedDocument&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="14" customHeight="1">
+      <c r="A83" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;!-- Gross price with commercial discount --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="14" customHeight="1">
+      <c r="A84" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:GrossPriceProductTradePrice&gt;                &lt;!-- (O) EN 16931 --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="14" customHeight="1">
+      <c r="A85" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:ChargeAmount&gt;1250.00&lt;/ram:ChargeAmount&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="14" customHeight="1">
+      <c r="A86" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:BasisQuantity unitCode="HUR"&gt;1&lt;/ram:BasisQuantity&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="14" customHeight="1">
+      <c r="A87" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:AppliedTradeAllowanceCharge&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="14" customHeight="1">
+      <c r="A88" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            &lt;ram:ChargeIndicator&gt;false&lt;/ram:ChargeIndicator&gt;  &lt;!-- false=discount --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="14" customHeight="1">
+      <c r="A89" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            &lt;ram:ActualAmount&gt;250.00&lt;/ram:ActualAmount&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="14" customHeight="1">
+      <c r="A90" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;/ram:AppliedTradeAllowanceCharge&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="14" customHeight="1">
+      <c r="A91" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:GrossPriceProductTradePrice&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="14" customHeight="1">
+      <c r="A92" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;!-- Net unit price excl. VAT --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="14" customHeight="1">
+      <c r="A93" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:NetPriceProductTradePrice&gt;                  &lt;!-- (M) from BASIC onwards --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="14" customHeight="1">
+      <c r="A94" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:ChargeAmount&gt;1000.00&lt;/ram:ChargeAmount&gt;   &lt;!-- Net = 1250 – 250 --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="14" customHeight="1">
+      <c r="A95" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:BasisQuantity unitCode="HUR"&gt;1&lt;/ram:BasisQuantity&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="14" customHeight="1">
+      <c r="A96" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:NetPriceProductTradePrice&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="14" customHeight="1">
+      <c r="A97" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:SpecifiedLineTradeAgreement&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="14" customHeight="1">
+      <c r="A98" s="38" t="inlineStr"/>
+    </row>
+    <row r="99" ht="14" customHeight="1">
+      <c r="A99" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:SpecifiedLineTradeDelivery&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="14" customHeight="1">
+      <c r="A100" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:BilledQuantity unitCode="HUR"&gt;8&lt;/ram:BilledQuantity&gt;  &lt;!-- (M) 8 hours --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="14" customHeight="1">
+      <c r="A101" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:SpecifiedLineTradeDelivery&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="14" customHeight="1">
+      <c r="A102" s="38" t="inlineStr"/>
+    </row>
+    <row r="103" ht="14" customHeight="1">
+      <c r="A103" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:SpecifiedLineTradeSettlement&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="14" customHeight="1">
+      <c r="A104" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:ApplicableTradeTax&gt;                         &lt;!-- (M) --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="14" customHeight="1">
+      <c r="A105" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:TypeCode&gt;VAT&lt;/ram:TypeCode&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="14" customHeight="1">
+      <c r="A106" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:CategoryCode&gt;S&lt;/ram:CategoryCode&gt;         &lt;!-- S = standard rate --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="14" customHeight="1">
+      <c r="A107" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:RateApplicablePercent&gt;20.00&lt;/ram:RateApplicablePercent&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="14" customHeight="1">
+      <c r="A108" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:ApplicableTradeTax&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="14" customHeight="1">
+      <c r="A109" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;!-- Additional line-level discount --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="14" customHeight="1">
+      <c r="A110" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:SpecifiedTradeAllowanceCharge&gt;              &lt;!-- (O) EN 16931 --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="14" customHeight="1">
+      <c r="A111" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:ChargeIndicator&gt;false&lt;/ram:ChargeIndicator&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="14" customHeight="1">
+      <c r="A112" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:CalculationPercent&gt;5&lt;/ram:CalculationPercent&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="14" customHeight="1">
+      <c r="A113" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:BasisAmount&gt;8000.00&lt;/ram:BasisAmount&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="14" customHeight="1">
+      <c r="A114" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:ActualAmount&gt;400.00&lt;/ram:ActualAmount&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="14" customHeight="1">
+      <c r="A115" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:Reason&gt;Loyalty discount&lt;/ram:Reason&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="14" customHeight="1">
+      <c r="A116" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:CategoryTradeTax&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="14" customHeight="1">
+      <c r="A117" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            &lt;ram:TypeCode&gt;VAT&lt;/ram:TypeCode&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="14" customHeight="1">
+      <c r="A118" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            &lt;ram:CategoryCode&gt;S&lt;/ram:CategoryCode&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="14" customHeight="1">
+      <c r="A119" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            &lt;ram:RateApplicablePercent&gt;20.00&lt;/ram:RateApplicablePercent&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="14" customHeight="1">
+      <c r="A120" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;/ram:CategoryTradeTax&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="14" customHeight="1">
+      <c r="A121" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:SpecifiedTradeAllowanceCharge&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="14" customHeight="1">
+      <c r="A122" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;!-- Referenced document (technical report) --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="14" customHeight="1">
+      <c r="A123" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:AdditionalReferencedDocument&gt;               &lt;!-- (O) EN 16931 --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="14" customHeight="1">
+      <c r="A124" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:IssuerAssignedID&gt;RPT-2024-001&lt;/ram:IssuerAssignedID&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="14" customHeight="1">
+      <c r="A125" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:TypeCode&gt;130&lt;/ram:TypeCode&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="14" customHeight="1">
+      <c r="A126" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:ReferenceTypeCode&gt;ACD&lt;/ram:ReferenceTypeCode&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="14" customHeight="1">
+      <c r="A127" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:AdditionalReferencedDocument&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="14" customHeight="1">
+      <c r="A128" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:SpecifiedTradeSettlementLineMonetarySummation&gt;  &lt;!-- (M) --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="14" customHeight="1">
+      <c r="A129" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;!-- 8h × 1000 – 400 line discount = 7600 --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="14" customHeight="1">
+      <c r="A130" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:LineTotalAmount&gt;7600.00&lt;/ram:LineTotalAmount&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="14" customHeight="1">
+      <c r="A131" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:SpecifiedTradeSettlementLineMonetarySummation&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="14" customHeight="1">
+      <c r="A132" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:SpecifiedLineTradeSettlement&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="14" customHeight="1">
+      <c r="A133" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    &lt;/ram:IncludedSupplyChainTradeLineItem&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="14" customHeight="1">
+      <c r="A134" s="38" t="inlineStr"/>
+    </row>
+    <row r="135" ht="14" customHeight="1">
+      <c r="A135" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    &lt;!-- ── Line 2: Software licence ──────────────── --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="14" customHeight="1">
+      <c r="A136" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    &lt;ram:IncludedSupplyChainTradeLineItem&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="14" customHeight="1">
+      <c r="A137" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:AssociatedDocumentLineDocument&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="14" customHeight="1">
+      <c r="A138" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:LineID&gt;2&lt;/ram:LineID&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="14" customHeight="1">
+      <c r="A139" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:AssociatedDocumentLineDocument&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="14" customHeight="1">
+      <c r="A140" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:SpecifiedTradeProduct&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="14" customHeight="1">
+      <c r="A141" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:SellerAssignedID&gt;LIC-SOFT-2024&lt;/ram:SellerAssignedID&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="14" customHeight="1">
+      <c r="A142" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:Name&gt;Annual software licence – Analytics Module&lt;/ram:Name&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="14" customHeight="1">
+      <c r="A143" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:Description&gt;Unlimited access 12 months, 10 concurrent users.&lt;/ram:Description&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="14" customHeight="1">
+      <c r="A144" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:SpecifiedTradeProduct&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="14" customHeight="1">
+      <c r="A145" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:SpecifiedLineTradeAgreement&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="14" customHeight="1">
+      <c r="A146" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:NetPriceProductTradePrice&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="14" customHeight="1">
+      <c r="A147" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:ChargeAmount&gt;2500.00&lt;/ram:ChargeAmount&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="14" customHeight="1">
+      <c r="A148" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:BasisQuantity unitCode="ANN"&gt;1&lt;/ram:BasisQuantity&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="14" customHeight="1">
+      <c r="A149" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:NetPriceProductTradePrice&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="14" customHeight="1">
+      <c r="A150" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:SpecifiedLineTradeAgreement&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="14" customHeight="1">
+      <c r="A151" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:SpecifiedLineTradeDelivery&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="14" customHeight="1">
+      <c r="A152" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:BilledQuantity unitCode="ANN"&gt;1&lt;/ram:BilledQuantity&gt;  &lt;!-- 1 year --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="14" customHeight="1">
+      <c r="A153" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:SpecifiedLineTradeDelivery&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="14" customHeight="1">
+      <c r="A154" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:SpecifiedLineTradeSettlement&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="14" customHeight="1">
+      <c r="A155" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:ApplicableTradeTax&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="14" customHeight="1">
+      <c r="A156" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:TypeCode&gt;VAT&lt;/ram:TypeCode&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="14" customHeight="1">
+      <c r="A157" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:CategoryCode&gt;S&lt;/ram:CategoryCode&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="14" customHeight="1">
+      <c r="A158" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:RateApplicablePercent&gt;20.00&lt;/ram:RateApplicablePercent&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="14" customHeight="1">
+      <c r="A159" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:ApplicableTradeTax&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="14" customHeight="1">
+      <c r="A160" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:SpecifiedTradeSettlementLineMonetarySummation&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="14" customHeight="1">
+      <c r="A161" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:LineTotalAmount&gt;2500.00&lt;/ram:LineTotalAmount&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="14" customHeight="1">
+      <c r="A162" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:SpecifiedTradeSettlementLineMonetarySummation&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="14" customHeight="1">
+      <c r="A163" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:SpecifiedLineTradeSettlement&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="14" customHeight="1">
+      <c r="A164" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    &lt;/ram:IncludedSupplyChainTradeLineItem&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="14" customHeight="1">
+      <c r="A165" s="38" t="inlineStr"/>
+    </row>
+    <row r="166" ht="14" customHeight="1">
+      <c r="A166" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    &lt;!-- ── Line 3: Training (VAT-exempt) ─────────── --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="14" customHeight="1">
+      <c r="A167" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    &lt;ram:IncludedSupplyChainTradeLineItem&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="14" customHeight="1">
+      <c r="A168" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:AssociatedDocumentLineDocument&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="14" customHeight="1">
+      <c r="A169" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:LineID&gt;3&lt;/ram:LineID&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="14" customHeight="1">
+      <c r="A170" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:AssociatedDocumentLineDocument&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="14" customHeight="1">
+      <c r="A171" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:SpecifiedTradeProduct&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="14" customHeight="1">
+      <c r="A172" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:Name&gt;Certified Agile Project Management Training&lt;/ram:Name&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="14" customHeight="1">
+      <c r="A173" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:Description&gt;2-day on-site workshop, 6 participants, materials included.&lt;/ram:Description&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="14" customHeight="1">
+      <c r="A174" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:SpecifiedTradeProduct&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="14" customHeight="1">
+      <c r="A175" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:SpecifiedLineTradeAgreement&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="14" customHeight="1">
+      <c r="A176" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:NetPriceProductTradePrice&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="14" customHeight="1">
+      <c r="A177" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:ChargeAmount&gt;900.00&lt;/ram:ChargeAmount&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="14" customHeight="1">
+      <c r="A178" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:BasisQuantity unitCode="DAY"&gt;1&lt;/ram:BasisQuantity&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="14" customHeight="1">
+      <c r="A179" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:NetPriceProductTradePrice&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="14" customHeight="1">
+      <c r="A180" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:SpecifiedLineTradeAgreement&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="14" customHeight="1">
+      <c r="A181" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:SpecifiedLineTradeDelivery&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="14" customHeight="1">
+      <c r="A182" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:BilledQuantity unitCode="DAY"&gt;2&lt;/ram:BilledQuantity&gt;  &lt;!-- 2 days --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="14" customHeight="1">
+      <c r="A183" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:SpecifiedLineTradeDelivery&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="14" customHeight="1">
+      <c r="A184" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:SpecifiedLineTradeSettlement&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="14" customHeight="1">
+      <c r="A185" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:ApplicableTradeTax&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="14" customHeight="1">
+      <c r="A186" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:TypeCode&gt;VAT&lt;/ram:TypeCode&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="14" customHeight="1">
+      <c r="A187" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:CategoryCode&gt;E&lt;/ram:CategoryCode&gt;         &lt;!-- E = exempt --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="14" customHeight="1">
+      <c r="A188" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:ExemptionReasonCode&gt;VATEX-EU-O&lt;/ram:ExemptionReasonCode&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="14" customHeight="1">
+      <c r="A189" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:RateApplicablePercent&gt;0&lt;/ram:RateApplicablePercent&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="14" customHeight="1">
+      <c r="A190" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:ApplicableTradeTax&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="14" customHeight="1">
+      <c r="A191" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:SpecifiedTradeSettlementLineMonetarySummation&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="14" customHeight="1">
+      <c r="A192" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:LineTotalAmount&gt;1800.00&lt;/ram:LineTotalAmount&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="14" customHeight="1">
+      <c r="A193" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:SpecifiedTradeSettlementLineMonetarySummation&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="14" customHeight="1">
+      <c r="A194" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:SpecifiedLineTradeSettlement&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="14" customHeight="1">
+      <c r="A195" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    &lt;/ram:IncludedSupplyChainTradeLineItem&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="14" customHeight="1">
+      <c r="A196" s="38" t="inlineStr"/>
+    </row>
+    <row r="197" ht="14" customHeight="1">
+      <c r="A197" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    &lt;!-- ══════════════════════════════════════════════</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="14" customHeight="1">
+      <c r="A198" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         3b. HEADER TRADE AGREEMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="14" customHeight="1">
+      <c r="A199" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         ══════════════════════════════════════════ --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="14" customHeight="1">
+      <c r="A200" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    &lt;ram:ApplicableHeaderTradeAgreement&gt;                 &lt;!-- (M) --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="14" customHeight="1">
+      <c r="A201" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:BuyerReference&gt;PURCH-DEPT-2024&lt;/ram:BuyerReference&gt;  &lt;!-- (M) MINIMUM --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="14" customHeight="1">
+      <c r="A202" s="38" t="inlineStr"/>
+    </row>
+    <row r="203" ht="14" customHeight="1">
+      <c r="A203" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;!-- ── SELLER ─────────────────────────────────── --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="14" customHeight="1">
+      <c r="A204" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:SellerTradeParty&gt;                             &lt;!-- (M) --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="14" customHeight="1">
+      <c r="A205" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:GlobalID schemeID="0060"&gt;123456789&lt;/ram:GlobalID&gt;  &lt;!-- DUNS --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="14" customHeight="1">
+      <c r="A206" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:ID&gt;SELL-001&lt;/ram:ID&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="14" customHeight="1">
+      <c r="A207" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:Name&gt;ACME Consulting Ltd&lt;/ram:Name&gt;          &lt;!-- (M) --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="14" customHeight="1">
+      <c r="A208" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:Description&gt;Private limited company, registered in England &amp;amp; Wales&lt;/ram:Description&gt;  &lt;!-- EXTENDED --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="14" customHeight="1">
+      <c r="A209" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:SpecifiedLegalOrganization&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="14" customHeight="1">
+      <c r="A210" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:ID schemeID="0060"&gt;123456789&lt;/ram:ID&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="14" customHeight="1">
+      <c r="A211" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:TradingBusinessName&gt;ACME Consulting&lt;/ram:TradingBusinessName&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="14" customHeight="1">
+      <c r="A212" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:SpecifiedLegalOrganization&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="14" customHeight="1">
+      <c r="A213" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:DefinedTradeContact&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="14" customHeight="1">
+      <c r="A214" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:PersonName&gt;Alice Johnson&lt;/ram:PersonName&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="14" customHeight="1">
+      <c r="A215" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:DepartmentName&gt;Accounts Receivable&lt;/ram:DepartmentName&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="14" customHeight="1">
+      <c r="A216" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:TelephoneUniversalCommunication&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="14" customHeight="1">
+      <c r="A217" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            &lt;ram:CompleteNumber&gt;+44 20 7123 4567&lt;/ram:CompleteNumber&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="14" customHeight="1">
+      <c r="A218" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;/ram:TelephoneUniversalCommunication&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="14" customHeight="1">
+      <c r="A219" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:EmailURIUniversalCommunication&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="14" customHeight="1">
+      <c r="A220" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            &lt;ram:URIID&gt;billing@acme-consulting.co.uk&lt;/ram:URIID&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="14" customHeight="1">
+      <c r="A221" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;/ram:EmailURIUniversalCommunication&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="14" customHeight="1">
+      <c r="A222" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:DefinedTradeContact&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="14" customHeight="1">
+      <c r="A223" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:PostalTradeAddress&gt;                         &lt;!-- (M) --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="14" customHeight="1">
+      <c r="A224" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:PostcodeCode&gt;EC2V 8RF&lt;/ram:PostcodeCode&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="14" customHeight="1">
+      <c r="A225" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:LineOne&gt;10 Cheapside&lt;/ram:LineOne&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="14" customHeight="1">
+      <c r="A226" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:LineTwo&gt;Floor 5&lt;/ram:LineTwo&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="14" customHeight="1">
+      <c r="A227" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:LineThree&gt;City of London&lt;/ram:LineThree&gt;  &lt;!-- EXTENDED --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="14" customHeight="1">
+      <c r="A228" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:CityName&gt;London&lt;/ram:CityName&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="14" customHeight="1">
+      <c r="A229" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:CountryID&gt;GB&lt;/ram:CountryID&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="14" customHeight="1">
+      <c r="A230" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:CountrySubDivisionName&gt;England&lt;/ram:CountrySubDivisionName&gt;  &lt;!-- EXTENDED --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="14" customHeight="1">
+      <c r="A231" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:PostalTradeAddress&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="14" customHeight="1">
+      <c r="A232" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:URIUniversalCommunication&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="14" customHeight="1">
+      <c r="A233" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:URIID schemeID="EM"&gt;billing@acme-consulting.co.uk&lt;/ram:URIID&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="14" customHeight="1">
+      <c r="A234" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:URIUniversalCommunication&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="14" customHeight="1">
+      <c r="A235" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:SpecifiedTaxRegistration&gt;                   &lt;!-- (M) --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="14" customHeight="1">
+      <c r="A236" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:ID schemeID="VA"&gt;GB123456789&lt;/ram:ID&gt;     &lt;!-- VAT number --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="14" customHeight="1">
+      <c r="A237" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:SpecifiedTaxRegistration&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="14" customHeight="1">
+      <c r="A238" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:SellerTradeParty&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="14" customHeight="1">
+      <c r="A239" s="38" t="inlineStr"/>
+    </row>
+    <row r="240" ht="14" customHeight="1">
+      <c r="A240" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;!-- ── BUYER ──────────────────────────────────── --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="14" customHeight="1">
+      <c r="A241" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:BuyerTradeParty&gt;                              &lt;!-- (M) --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="14" customHeight="1">
+      <c r="A242" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:GlobalID schemeID="0060"&gt;987654321&lt;/ram:GlobalID&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="14" customHeight="1">
+      <c r="A243" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:ID&gt;CLI-789&lt;/ram:ID&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="14" customHeight="1">
+      <c r="A244" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:Name&gt;Client Industries Plc&lt;/ram:Name&gt;       &lt;!-- (M) --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="14" customHeight="1">
+      <c r="A245" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:SpecifiedLegalOrganization&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="14" customHeight="1">
+      <c r="A246" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:ID schemeID="0060"&gt;987654321&lt;/ram:ID&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="14" customHeight="1">
+      <c r="A247" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:TradingBusinessName&gt;Client Group&lt;/ram:TradingBusinessName&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="14" customHeight="1">
+      <c r="A248" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:SpecifiedLegalOrganization&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="14" customHeight="1">
+      <c r="A249" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:DefinedTradeContact&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="14" customHeight="1">
+      <c r="A250" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:PersonName&gt;Bob Smith&lt;/ram:PersonName&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="14" customHeight="1">
+      <c r="A251" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:TelephoneUniversalCommunication&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="14" customHeight="1">
+      <c r="A252" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            &lt;ram:CompleteNumber&gt;+44 161 234 5678&lt;/ram:CompleteNumber&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="14" customHeight="1">
+      <c r="A253" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;/ram:TelephoneUniversalCommunication&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="14" customHeight="1">
+      <c r="A254" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:EmailURIUniversalCommunication&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="14" customHeight="1">
+      <c r="A255" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            &lt;ram:URIID&gt;b.smith@client-industries.co.uk&lt;/ram:URIID&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="14" customHeight="1">
+      <c r="A256" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;/ram:EmailURIUniversalCommunication&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="14" customHeight="1">
+      <c r="A257" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:DefinedTradeContact&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="14" customHeight="1">
+      <c r="A258" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:PostalTradeAddress&gt;                         &lt;!-- (M) --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="14" customHeight="1">
+      <c r="A259" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:PostcodeCode&gt;M2 4WU&lt;/ram:PostcodeCode&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="14" customHeight="1">
+      <c r="A260" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:LineOne&gt;1 Spinningfields&lt;/ram:LineOne&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="14" customHeight="1">
+      <c r="A261" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:LineTwo&gt;Tower 2&lt;/ram:LineTwo&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="14" customHeight="1">
+      <c r="A262" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:CityName&gt;Manchester&lt;/ram:CityName&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="14" customHeight="1">
+      <c r="A263" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:CountryID&gt;GB&lt;/ram:CountryID&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="14" customHeight="1">
+      <c r="A264" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:CountrySubDivisionName&gt;England&lt;/ram:CountrySubDivisionName&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="14" customHeight="1">
+      <c r="A265" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:PostalTradeAddress&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="14" customHeight="1">
+      <c r="A266" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:URIUniversalCommunication&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="14" customHeight="1">
+      <c r="A267" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:URIID schemeID="EM"&gt;purchase@client-industries.co.uk&lt;/ram:URIID&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="14" customHeight="1">
+      <c r="A268" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:URIUniversalCommunication&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="14" customHeight="1">
+      <c r="A269" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:SpecifiedTaxRegistration&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="14" customHeight="1">
+      <c r="A270" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:ID schemeID="VA"&gt;GB987654321&lt;/ram:ID&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="14" customHeight="1">
+      <c r="A271" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:SpecifiedTaxRegistration&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="14" customHeight="1">
+      <c r="A272" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:BuyerTradeParty&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="14" customHeight="1">
+      <c r="A273" s="38" t="inlineStr"/>
+    </row>
+    <row r="274" ht="14" customHeight="1">
+      <c r="A274" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;!-- ── REFERENCES ─────────────────────────────── --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="14" customHeight="1">
+      <c r="A275" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:BuyerOrderReferencedDocument&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="14" customHeight="1">
+      <c r="A276" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:IssuerAssignedID&gt;PO-2024-1056&lt;/ram:IssuerAssignedID&gt;   &lt;!-- Purchase order --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="14" customHeight="1">
+      <c r="A277" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:BuyerOrderReferencedDocument&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="14" customHeight="1">
+      <c r="A278" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:ContractReferencedDocument&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="279" ht="14" customHeight="1">
+      <c r="A279" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:IssuerAssignedID&gt;CTR-2023-089&lt;/ram:IssuerAssignedID&gt;   &lt;!-- Contract --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="14" customHeight="1">
+      <c r="A280" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:ContractReferencedDocument&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="14" customHeight="1">
+      <c r="A281" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:QuotationReferencedDocument&gt;                 &lt;!-- EXTENDED --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="14" customHeight="1">
+      <c r="A282" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:IssuerAssignedID&gt;QUO-2024-0123&lt;/ram:IssuerAssignedID&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="14" customHeight="1">
+      <c r="A283" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:QuotationReferencedDocument&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="14" customHeight="1">
+      <c r="A284" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;!-- Attachment – signed purchase order PDF --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="14" customHeight="1">
+      <c r="A285" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:AdditionalReferencedDocument&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="14" customHeight="1">
+      <c r="A286" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:IssuerAssignedID&gt;PO-2024-1056-ATT&lt;/ram:IssuerAssignedID&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="14" customHeight="1">
+      <c r="A287" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:TypeCode&gt;130&lt;/ram:TypeCode&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="14" customHeight="1">
+      <c r="A288" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:Name&gt;Signed purchase order&lt;/ram:Name&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="14" customHeight="1">
+      <c r="A289" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:AttachmentBinaryObject mimeCode="application/pdf" filename="purchase_order.pdf"&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="14" customHeight="1">
+      <c r="A290" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          JVBERi0xLjQKJeLjz9MKMyAwIG9iago8PC9UeXBlIC9QYWdlCi9NZWRpYUJveCBbMCAwIDU5NSA4NDJdCj4+CmVuZG9iago=</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="14" customHeight="1">
+      <c r="A291" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:AttachmentBinaryObject&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="14" customHeight="1">
+      <c r="A292" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:AdditionalReferencedDocument&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="14" customHeight="1">
+      <c r="A293" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;!-- Project / procurement reference --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="14" customHeight="1">
+      <c r="A294" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:SpecifiedProcuringProject&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="14" customHeight="1">
+      <c r="A295" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:ID&gt;PROJ-2024-DIGITAL&lt;/ram:ID&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="14" customHeight="1">
+      <c r="A296" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:Name&gt;Digital Transformation 2024&lt;/ram:Name&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="14" customHeight="1">
+      <c r="A297" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:SpecifiedProcuringProject&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="14" customHeight="1">
+      <c r="A298" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    &lt;/ram:ApplicableHeaderTradeAgreement&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="14" customHeight="1">
+      <c r="A299" s="38" t="inlineStr"/>
+    </row>
+    <row r="300" ht="14" customHeight="1">
+      <c r="A300" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    &lt;!-- ══════════════════════════════════════════════</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="14" customHeight="1">
+      <c r="A301" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         3c. HEADER TRADE DELIVERY</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="14" customHeight="1">
+      <c r="A302" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         ══════════════════════════════════════════ --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="14" customHeight="1">
+      <c r="A303" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    &lt;ram:ApplicableHeaderTradeDelivery&gt;                  &lt;!-- (M) --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="14" customHeight="1">
+      <c r="A304" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:ShipToTradeParty&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="14" customHeight="1">
+      <c r="A305" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:ID&gt;SITE-MCR-01&lt;/ram:ID&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="14" customHeight="1">
+      <c r="A306" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:Name&gt;Client Industries – Manchester Site&lt;/ram:Name&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="14" customHeight="1">
+      <c r="A307" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:PostalTradeAddress&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="14" customHeight="1">
+      <c r="A308" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:PostcodeCode&gt;M1 2AN&lt;/ram:PostcodeCode&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="14" customHeight="1">
+      <c r="A309" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:LineOne&gt;25 Piccadilly&lt;/ram:LineOne&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="14" customHeight="1">
+      <c r="A310" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:LineTwo&gt;Building C&lt;/ram:LineTwo&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="14" customHeight="1">
+      <c r="A311" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:CityName&gt;Manchester&lt;/ram:CityName&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="14" customHeight="1">
+      <c r="A312" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:CountryID&gt;GB&lt;/ram:CountryID&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="14" customHeight="1">
+      <c r="A313" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:PostalTradeAddress&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="14" customHeight="1">
+      <c r="A314" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:ShipToTradeParty&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="14" customHeight="1">
+      <c r="A315" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:ActualDeliverySupplyChainEvent&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="14" customHeight="1">
+      <c r="A316" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:OccurrenceDateTime&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="14" customHeight="1">
+      <c r="A317" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;udt:DateTimeString format="102"&gt;20240228&lt;/udt:DateTimeString&gt;  &lt;!-- Delivery date --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="14" customHeight="1">
+      <c r="A318" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:OccurrenceDateTime&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="14" customHeight="1">
+      <c r="A319" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:ActualDeliverySupplyChainEvent&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="14" customHeight="1">
+      <c r="A320" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:DeliveryNoteReferencedDocument&gt;               &lt;!-- EXTENDED --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="14" customHeight="1">
+      <c r="A321" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:IssuerAssignedID&gt;DN-2024-00456&lt;/ram:IssuerAssignedID&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="14" customHeight="1">
+      <c r="A322" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:FormattedIssueDateTime&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="14" customHeight="1">
+      <c r="A323" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;qdt:DateTimeString format="102"&gt;20240228&lt;/qdt:DateTimeString&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="14" customHeight="1">
+      <c r="A324" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:FormattedIssueDateTime&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="14" customHeight="1">
+      <c r="A325" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:DeliveryNoteReferencedDocument&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="14" customHeight="1">
+      <c r="A326" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:DespatchAdviceReferencedDocument&gt;             &lt;!-- EXTENDED --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="14" customHeight="1">
+      <c r="A327" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:IssuerAssignedID&gt;DA-2024-0099&lt;/ram:IssuerAssignedID&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="328" ht="14" customHeight="1">
+      <c r="A328" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:DespatchAdviceReferencedDocument&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="329" ht="14" customHeight="1">
+      <c r="A329" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    &lt;/ram:ApplicableHeaderTradeDelivery&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" ht="14" customHeight="1">
+      <c r="A330" s="38" t="inlineStr"/>
+    </row>
+    <row r="331" ht="14" customHeight="1">
+      <c r="A331" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    &lt;!-- ══════════════════════════════════════════════</t>
+        </is>
+      </c>
+    </row>
+    <row r="332" ht="14" customHeight="1">
+      <c r="A332" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         3d. HEADER TRADE SETTLEMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="333" ht="14" customHeight="1">
+      <c r="A333" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         ══════════════════════════════════════════ --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="334" ht="14" customHeight="1">
+      <c r="A334" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    &lt;ram:ApplicableHeaderTradeSettlement&gt;                &lt;!-- (M) --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="14" customHeight="1">
+      <c r="A335" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:CreditorReferenceID&gt;ACME-SEPA-2024&lt;/ram:CreditorReferenceID&gt;  &lt;!-- (O) SEPA --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="14" customHeight="1">
+      <c r="A336" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:PaymentReference&gt;INV-2024-00789&lt;/ram:PaymentReference&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="337" ht="14" customHeight="1">
+      <c r="A337" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:InvoiceCurrencyCode&gt;GBP&lt;/ram:InvoiceCurrencyCode&gt;  &lt;!-- (M) --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="14" customHeight="1">
+      <c r="A338" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:InvoiceIssuerReference&gt;INT-REF-0099&lt;/ram:InvoiceIssuerReference&gt;  &lt;!-- EXTENDED --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="339" ht="14" customHeight="1">
+      <c r="A339" s="38" t="inlineStr"/>
+    </row>
+    <row r="340" ht="14" customHeight="1">
+      <c r="A340" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;!-- Payee (if different from seller) --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="341" ht="14" customHeight="1">
+      <c r="A341" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:PayeeTradeParty&gt;                              &lt;!-- (O) EN 16931 --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="342" ht="14" customHeight="1">
+      <c r="A342" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:ID&gt;PAY-001&lt;/ram:ID&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="343" ht="14" customHeight="1">
+      <c r="A343" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:Name&gt;ACME Holding Ltd&lt;/ram:Name&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="344" ht="14" customHeight="1">
+      <c r="A344" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:SpecifiedLegalOrganization&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="345" ht="14" customHeight="1">
+      <c r="A345" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:ID schemeID="0060"&gt;111222333&lt;/ram:ID&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="14" customHeight="1">
+      <c r="A346" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:SpecifiedLegalOrganization&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="347" ht="14" customHeight="1">
+      <c r="A347" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:PayeeTradeParty&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="348" ht="14" customHeight="1">
+      <c r="A348" s="38" t="inlineStr"/>
+    </row>
+    <row r="349" ht="14" customHeight="1">
+      <c r="A349" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;!-- Payment means: SEPA Credit Transfer --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="350" ht="14" customHeight="1">
+      <c r="A350" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:SpecifiedTradeSettlementPaymentMeans&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="351" ht="14" customHeight="1">
+      <c r="A351" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:TypeCode&gt;58&lt;/ram:TypeCode&gt;                  &lt;!-- 58 = SEPA Credit Transfer --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="352" ht="14" customHeight="1">
+      <c r="A352" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:Information&gt;SEPA credit transfer – IBAN below&lt;/ram:Information&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="353" ht="14" customHeight="1">
+      <c r="A353" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:PayeePartyCreditorFinancialAccount&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="354" ht="14" customHeight="1">
+      <c r="A354" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:IBANID&gt;GB29NWBK60161331926819&lt;/ram:IBANID&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="355" ht="14" customHeight="1">
+      <c r="A355" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:ProprietaryID&gt;Main GBP account&lt;/ram:ProprietaryID&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="356" ht="14" customHeight="1">
+      <c r="A356" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:PayeePartyCreditorFinancialAccount&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="357" ht="14" customHeight="1">
+      <c r="A357" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:PayeeSpecifiedCreditorFinancialInstitution&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="358" ht="14" customHeight="1">
+      <c r="A358" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:BICID&gt;NWBKGB2L&lt;/ram:BICID&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="359" ht="14" customHeight="1">
+      <c r="A359" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:PayeeSpecifiedCreditorFinancialInstitution&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="360" ht="14" customHeight="1">
+      <c r="A360" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:SpecifiedTradeSettlementPaymentMeans&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="361" ht="14" customHeight="1">
+      <c r="A361" s="38" t="inlineStr"/>
+    </row>
+    <row r="362" ht="14" customHeight="1">
+      <c r="A362" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;!-- ── VAT: 20% standard rate (lines 1 + 2) ─ --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="363" ht="14" customHeight="1">
+      <c r="A363" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:ApplicableTradeTax&gt;                           &lt;!-- (M) 1..n --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="364" ht="14" customHeight="1">
+      <c r="A364" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:CalculatedAmount&gt;2020.00&lt;/ram:CalculatedAmount&gt;  &lt;!-- VAT = (7600+2500) × 20% --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="365" ht="14" customHeight="1">
+      <c r="A365" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:TypeCode&gt;VAT&lt;/ram:TypeCode&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="366" ht="14" customHeight="1">
+      <c r="A366" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:BasisAmount&gt;10100.00&lt;/ram:BasisAmount&gt;       &lt;!-- 7600 + 2500 --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="367" ht="14" customHeight="1">
+      <c r="A367" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:CategoryCode&gt;S&lt;/ram:CategoryCode&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="368" ht="14" customHeight="1">
+      <c r="A368" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:RateApplicablePercent&gt;20.00&lt;/ram:RateApplicablePercent&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="369" ht="14" customHeight="1">
+      <c r="A369" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:DueDateTypeCode&gt;72&lt;/ram:DueDateTypeCode&gt;     &lt;!-- 72 = invoice date --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="370" ht="14" customHeight="1">
+      <c r="A370" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:ApplicableTradeTax&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="371" ht="14" customHeight="1">
+      <c r="A371" s="38" t="inlineStr"/>
+    </row>
+    <row r="372" ht="14" customHeight="1">
+      <c r="A372" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;!-- ── VAT: exempt – training (line 3) ──────── --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="373" ht="14" customHeight="1">
+      <c r="A373" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:ApplicableTradeTax&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="374" ht="14" customHeight="1">
+      <c r="A374" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:CalculatedAmount&gt;0.00&lt;/ram:CalculatedAmount&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="375" ht="14" customHeight="1">
+      <c r="A375" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:TypeCode&gt;VAT&lt;/ram:TypeCode&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="376" ht="14" customHeight="1">
+      <c r="A376" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:BasisAmount&gt;1800.00&lt;/ram:BasisAmount&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="377" ht="14" customHeight="1">
+      <c r="A377" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:CategoryCode&gt;E&lt;/ram:CategoryCode&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="378" ht="14" customHeight="1">
+      <c r="A378" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:ExemptionReasonCode&gt;VATEX-EU-O&lt;/ram:ExemptionReasonCode&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="379" ht="14" customHeight="1">
+      <c r="A379" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:ExemptionReason&gt;Training services exempt from VAT&lt;/ram:ExemptionReason&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="380" ht="14" customHeight="1">
+      <c r="A380" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:RateApplicablePercent&gt;0&lt;/ram:RateApplicablePercent&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="381" ht="14" customHeight="1">
+      <c r="A381" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:ApplicableTradeTax&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="382" ht="14" customHeight="1">
+      <c r="A382" s="38" t="inlineStr"/>
+    </row>
+    <row r="383" ht="14" customHeight="1">
+      <c r="A383" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;!-- Invoicing period --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="384" ht="14" customHeight="1">
+      <c r="A384" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:BillingSpecifiedPeriod&gt;                       &lt;!-- (O) BASIC WL --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="385" ht="14" customHeight="1">
+      <c r="A385" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:StartDateTime&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="386" ht="14" customHeight="1">
+      <c r="A386" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;udt:DateTimeString format="102"&gt;20240201&lt;/udt:DateTimeString&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="387" ht="14" customHeight="1">
+      <c r="A387" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:StartDateTime&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="388" ht="14" customHeight="1">
+      <c r="A388" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:EndDateTime&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="389" ht="14" customHeight="1">
+      <c r="A389" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;udt:DateTimeString format="102"&gt;20240229&lt;/udt:DateTimeString&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="390" ht="14" customHeight="1">
+      <c r="A390" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:EndDateTime&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="391" ht="14" customHeight="1">
+      <c r="A391" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:BillingSpecifiedPeriod&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="392" ht="14" customHeight="1">
+      <c r="A392" s="38" t="inlineStr"/>
+    </row>
+    <row r="393" ht="14" customHeight="1">
+      <c r="A393" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;!-- Document-level discount --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="394" ht="14" customHeight="1">
+      <c r="A394" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:SpecifiedTradeAllowanceCharge&gt;                &lt;!-- (O) EN 16931 --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="395" ht="14" customHeight="1">
+      <c r="A395" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:ChargeIndicator&gt;false&lt;/ram:ChargeIndicator&gt;  &lt;!-- false = discount --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="396" ht="14" customHeight="1">
+      <c r="A396" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:SequenceNumeric&gt;1&lt;/ram:SequenceNumeric&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="397" ht="14" customHeight="1">
+      <c r="A397" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:CalculationPercent&gt;2&lt;/ram:CalculationPercent&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="398" ht="14" customHeight="1">
+      <c r="A398" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:BasisAmount&gt;11900.00&lt;/ram:BasisAmount&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="399" ht="14" customHeight="1">
+      <c r="A399" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:ActualAmount&gt;238.00&lt;/ram:ActualAmount&gt;       &lt;!-- 2% on 11,900 --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="400" ht="14" customHeight="1">
+      <c r="A400" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:ReasonCode&gt;95&lt;/ram:ReasonCode&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="401" ht="14" customHeight="1">
+      <c r="A401" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:Reason&gt;Annual volume loyalty discount&lt;/ram:Reason&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="402" ht="14" customHeight="1">
+      <c r="A402" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:CategoryTradeTax&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="403" ht="14" customHeight="1">
+      <c r="A403" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:TypeCode&gt;VAT&lt;/ram:TypeCode&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="404" ht="14" customHeight="1">
+      <c r="A404" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:CategoryCode&gt;S&lt;/ram:CategoryCode&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="405" ht="14" customHeight="1">
+      <c r="A405" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:RateApplicablePercent&gt;20.00&lt;/ram:RateApplicablePercent&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="406" ht="14" customHeight="1">
+      <c r="A406" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:CategoryTradeTax&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="407" ht="14" customHeight="1">
+      <c r="A407" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:SpecifiedTradeAllowanceCharge&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="408" ht="14" customHeight="1">
+      <c r="A408" s="38" t="inlineStr"/>
+    </row>
+    <row r="409" ht="14" customHeight="1">
+      <c r="A409" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;!-- Document-level surcharge: travel expenses --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="410" ht="14" customHeight="1">
+      <c r="A410" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:SpecifiedTradeAllowanceCharge&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="411" ht="14" customHeight="1">
+      <c r="A411" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:ChargeIndicator&gt;true&lt;/ram:ChargeIndicator&gt;   &lt;!-- true = surcharge --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="412" ht="14" customHeight="1">
+      <c r="A412" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:ActualAmount&gt;50.00&lt;/ram:ActualAmount&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="413" ht="14" customHeight="1">
+      <c r="A413" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:Reason&gt;Fixed travel expenses&lt;/ram:Reason&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="414" ht="14" customHeight="1">
+      <c r="A414" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:CategoryTradeTax&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="415" ht="14" customHeight="1">
+      <c r="A415" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:TypeCode&gt;VAT&lt;/ram:TypeCode&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="416" ht="14" customHeight="1">
+      <c r="A416" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:CategoryCode&gt;S&lt;/ram:CategoryCode&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="417" ht="14" customHeight="1">
+      <c r="A417" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:RateApplicablePercent&gt;20.00&lt;/ram:RateApplicablePercent&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="418" ht="14" customHeight="1">
+      <c r="A418" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:CategoryTradeTax&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="419" ht="14" customHeight="1">
+      <c r="A419" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:SpecifiedTradeAllowanceCharge&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="420" ht="14" customHeight="1">
+      <c r="A420" s="38" t="inlineStr"/>
+    </row>
+    <row r="421" ht="14" customHeight="1">
+      <c r="A421" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;!-- Logistics charge --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="422" ht="14" customHeight="1">
+      <c r="A422" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:SpecifiedLogisticsServiceCharge&gt;              &lt;!-- (O) EXTENDED --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="423" ht="14" customHeight="1">
+      <c r="A423" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:Description&gt;Express shipping charge&lt;/ram:Description&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="424" ht="14" customHeight="1">
+      <c r="A424" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:AppliedAmount&gt;30.00&lt;/ram:AppliedAmount&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="425" ht="14" customHeight="1">
+      <c r="A425" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:AppliedTradeTax&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="426" ht="14" customHeight="1">
+      <c r="A426" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:TypeCode&gt;VAT&lt;/ram:TypeCode&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="427" ht="14" customHeight="1">
+      <c r="A427" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:CategoryCode&gt;S&lt;/ram:CategoryCode&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="428" ht="14" customHeight="1">
+      <c r="A428" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:RateApplicablePercent&gt;20.00&lt;/ram:RateApplicablePercent&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="429" ht="14" customHeight="1">
+      <c r="A429" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:AppliedTradeTax&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="430" ht="14" customHeight="1">
+      <c r="A430" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:SpecifiedLogisticsServiceCharge&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="431" ht="14" customHeight="1">
+      <c r="A431" s="38" t="inlineStr"/>
+    </row>
+    <row r="432" ht="14" customHeight="1">
+      <c r="A432" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;!-- Payment terms with early-payment discount --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="433" ht="14" customHeight="1">
+      <c r="A433" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:SpecifiedTradePaymentTerms&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="434" ht="14" customHeight="1">
+      <c r="A434" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:Description&gt;Net 30 days. 1% early payment discount if settled within 10 days.&lt;/ram:Description&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="435" ht="14" customHeight="1">
+      <c r="A435" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:DueDateDateTime&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="436" ht="14" customHeight="1">
+      <c r="A436" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;udt:DateTimeString format="102"&gt;20240414&lt;/udt:DateTimeString&gt;  &lt;!-- 30 days after issue --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="437" ht="14" customHeight="1">
+      <c r="A437" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:DueDateDateTime&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="438" ht="14" customHeight="1">
+      <c r="A438" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:ApplicableTradePaymentDiscountTerms&gt;        &lt;!-- EXTENDED --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="439" ht="14" customHeight="1">
+      <c r="A439" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:BasisPeriodMeasure unitCode="DAY"&gt;10&lt;/ram:BasisPeriodMeasure&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="440" ht="14" customHeight="1">
+      <c r="A440" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:BasisAmount&gt;11742.00&lt;/ram:BasisAmount&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="441" ht="14" customHeight="1">
+      <c r="A441" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:CalculationPercent&gt;1&lt;/ram:CalculationPercent&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="442" ht="14" customHeight="1">
+      <c r="A442" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          &lt;ram:ActualDiscountAmount&gt;117.42&lt;/ram:ActualDiscountAmount&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="443" ht="14" customHeight="1">
+      <c r="A443" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;/ram:ApplicableTradePaymentDiscountTerms&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="444" ht="14" customHeight="1">
+      <c r="A444" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:SpecifiedTradePaymentTerms&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="445" ht="14" customHeight="1">
+      <c r="A445" s="38" t="inlineStr"/>
+    </row>
+    <row r="446" ht="14" customHeight="1">
+      <c r="A446" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;!-- ── MONETARY TOTALS ─────────────────────── --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="447" ht="14" customHeight="1">
+      <c r="A447" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:SpecifiedTradeSettlementHeaderMonetarySummation&gt;  &lt;!-- (M) --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="448" ht="14" customHeight="1">
+      <c r="A448" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;!-- LineTotalAmount = Σ line totals = 7600 + 2500 + 1800 = 11,900 --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="449" ht="14" customHeight="1">
+      <c r="A449" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:LineTotalAmount&gt;11900.00&lt;/ram:LineTotalAmount&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="450" ht="14" customHeight="1">
+      <c r="A450" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;!-- ChargeTotalAmount = travel 50 + shipping 30 = 80 --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="451" ht="14" customHeight="1">
+      <c r="A451" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:ChargeTotalAmount&gt;80.00&lt;/ram:ChargeTotalAmount&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="452" ht="14" customHeight="1">
+      <c r="A452" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;!-- AllowanceTotalAmount = document discount 238 --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="453" ht="14" customHeight="1">
+      <c r="A453" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:AllowanceTotalAmount&gt;238.00&lt;/ram:AllowanceTotalAmount&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="454" ht="14" customHeight="1">
+      <c r="A454" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;!-- TaxBasisTotalAmount = 11900 + 80 – 238 = 11,742 --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="455" ht="14" customHeight="1">
+      <c r="A455" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:TaxBasisTotalAmount&gt;11742.00&lt;/ram:TaxBasisTotalAmount&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="456" ht="14" customHeight="1">
+      <c r="A456" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;!-- TaxTotalAmount = (11742 – 1800) × 20% = 1,988.40 --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="457" ht="14" customHeight="1">
+      <c r="A457" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:TaxTotalAmount currencyID="GBP"&gt;1988.40&lt;/ram:TaxTotalAmount&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="458" ht="14" customHeight="1">
+      <c r="A458" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;!-- GrandTotalAmount = 11742 + 1988.40 = 13,730.40 --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="459" ht="14" customHeight="1">
+      <c r="A459" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:GrandTotalAmount&gt;13730.40&lt;/ram:GrandTotalAmount&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="460" ht="14" customHeight="1">
+      <c r="A460" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;!-- Prepayment received --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="461" ht="14" customHeight="1">
+      <c r="A461" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:TotalPrepaidAmount&gt;2000.00&lt;/ram:TotalPrepaidAmount&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="462" ht="14" customHeight="1">
+      <c r="A462" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;!-- Optional rounding --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="463" ht="14" customHeight="1">
+      <c r="A463" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:RoundingAmount&gt;0.00&lt;/ram:RoundingAmount&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="464" ht="14" customHeight="1">
+      <c r="A464" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;!-- DuePayableAmount = 13730.40 – 2000 = 11,730.40 --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="465" ht="14" customHeight="1">
+      <c r="A465" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:DuePayableAmount&gt;11730.40&lt;/ram:DuePayableAmount&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="466" ht="14" customHeight="1">
+      <c r="A466" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:SpecifiedTradeSettlementHeaderMonetarySummation&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="467" ht="14" customHeight="1">
+      <c r="A467" s="38" t="inlineStr"/>
+    </row>
+    <row r="468" ht="14" customHeight="1">
+      <c r="A468" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;!-- Buyer accounting reference (EXTENDED) --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="469" ht="14" customHeight="1">
+      <c r="A469" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;ram:ReceivableSpecifiedTradeAccountingAccount&gt;    &lt;!-- EXTENDED --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="470" ht="14" customHeight="1">
+      <c r="A470" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:ID&gt;AR-411000&lt;/ram:ID&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="471" ht="14" customHeight="1">
+      <c r="A471" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;ram:TypeCode&gt;1&lt;/ram:TypeCode&gt;                   &lt;!-- 1 = general ledger account --&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="472" ht="14" customHeight="1">
+      <c r="A472" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      &lt;/ram:ReceivableSpecifiedTradeAccountingAccount&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="473" ht="14" customHeight="1">
+      <c r="A473" s="38" t="inlineStr">
+        <is>
           <t xml:space="preserve">    &lt;/ram:ApplicableHeaderTradeSettlement&gt;</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="14" customHeight="1">
-      <c r="A82" s="38" t="inlineStr"/>
-    </row>
-    <row r="83" ht="14" customHeight="1">
-      <c r="A83" s="38" t="inlineStr">
+    <row r="474" ht="14" customHeight="1">
+      <c r="A474" s="38" t="inlineStr"/>
+    </row>
+    <row r="475" ht="14" customHeight="1">
+      <c r="A475" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  &lt;/rsm:SupplyChainTradeTransaction&gt;</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="14" customHeight="1">
-      <c r="A84" s="38" t="inlineStr">
+    <row r="476" ht="14" customHeight="1">
+      <c r="A476" s="38" t="inlineStr">
         <is>
           <t>&lt;/rsm:CrossIndustryInvoice&gt;</t>
         </is>
